--- a/Outcome/Publish/figure_data/fig3.xlsx
+++ b/Outcome/Publish/figure_data/fig3.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t xml:space="preserve">AgeGroup</t>
   </si>
@@ -75,9 +75,6 @@
   </si>
   <si>
     <t xml:space="preserve">55-64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TB</t>
   </si>
   <si>
     <t xml:space="preserve">65+</t>
@@ -563,7 +560,7 @@
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>68943</v>
+        <v>67540</v>
       </c>
     </row>
     <row r="6">
@@ -619,7 +616,7 @@
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>256415</v>
+        <v>252060</v>
       </c>
     </row>
     <row r="10">
@@ -675,7 +672,7 @@
         <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>204494</v>
+        <v>202207</v>
       </c>
     </row>
     <row r="14">
@@ -731,7 +728,7 @@
         <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>165535</v>
+        <v>163306</v>
       </c>
     </row>
     <row r="18">
@@ -787,7 +784,7 @@
         <v>8</v>
       </c>
       <c r="D21" t="n">
-        <v>160228</v>
+        <v>155865</v>
       </c>
     </row>
     <row r="22">
@@ -843,7 +840,7 @@
         <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>450105</v>
+        <v>384029</v>
       </c>
     </row>
     <row r="26">
@@ -899,7 +896,7 @@
         <v>8</v>
       </c>
       <c r="D29" t="n">
-        <v>408609</v>
+        <v>314445</v>
       </c>
     </row>
     <row r="30">
@@ -955,7 +952,7 @@
         <v>8</v>
       </c>
       <c r="D33" t="n">
-        <v>344647</v>
+        <v>234645</v>
       </c>
     </row>
     <row r="34">
@@ -1011,7 +1008,7 @@
         <v>8</v>
       </c>
       <c r="D37" t="n">
-        <v>287349</v>
+        <v>185017</v>
       </c>
     </row>
     <row r="38">
@@ -1050,10 +1047,10 @@
         <v>10</v>
       </c>
       <c r="C40" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D40" t="n">
-        <v>49633</v>
+        <v>38384</v>
       </c>
     </row>
     <row r="41">
@@ -1067,12 +1064,12 @@
         <v>8</v>
       </c>
       <c r="D41" t="n">
-        <v>185634</v>
+        <v>128746</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B42" t="n">
         <v>11</v>
@@ -1086,7 +1083,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B43" t="n">
         <v>11</v>
@@ -1100,21 +1097,21 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B44" t="n">
         <v>11</v>
       </c>
       <c r="C44" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D44" t="n">
-        <v>67937</v>
+        <v>23422</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B45" t="n">
         <v>11</v>
@@ -1123,7 +1120,7 @@
         <v>8</v>
       </c>
       <c r="D45" t="n">
-        <v>139714</v>
+        <v>105226</v>
       </c>
     </row>
   </sheetData>
@@ -1145,31 +1142,31 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" t="s">
         <v>22</v>
-      </c>
-      <c r="D1" t="s">
-        <v>23</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
       </c>
       <c r="F1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" t="s">
         <v>24</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>25</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>26</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>27</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>28</v>
-      </c>
-      <c r="K1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2">
@@ -1180,7 +1177,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -1195,7 +1192,7 @@
         <v>2024</v>
       </c>
       <c r="H2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -1213,7 +1210,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -1228,7 +1225,7 @@
         <v>2024</v>
       </c>
       <c r="H3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -1246,7 +1243,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -1261,7 +1258,7 @@
         <v>2024</v>
       </c>
       <c r="H4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -1279,7 +1276,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -1294,7 +1291,7 @@
         <v>2024</v>
       </c>
       <c r="H5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -1312,7 +1309,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -1327,7 +1324,7 @@
         <v>2024</v>
       </c>
       <c r="H6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -1345,7 +1342,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
@@ -1360,7 +1357,7 @@
         <v>2024</v>
       </c>
       <c r="H7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -1378,7 +1375,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
@@ -1393,7 +1390,7 @@
         <v>2024</v>
       </c>
       <c r="H8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -1411,7 +1408,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
@@ -1426,7 +1423,7 @@
         <v>2024</v>
       </c>
       <c r="H9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -1444,7 +1441,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D10" t="n">
         <v>9</v>
@@ -1459,7 +1456,7 @@
         <v>2024</v>
       </c>
       <c r="H10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
@@ -1477,7 +1474,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
@@ -1492,7 +1489,7 @@
         <v>2024</v>
       </c>
       <c r="H11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -1510,7 +1507,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D12" t="n">
         <v>11</v>
@@ -1525,7 +1522,7 @@
         <v>2024</v>
       </c>
       <c r="H12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
@@ -1543,7 +1540,7 @@
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D13" t="n">
         <v>1</v>
@@ -1558,7 +1555,7 @@
         <v>2024</v>
       </c>
       <c r="H13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -1576,7 +1573,7 @@
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D14" t="n">
         <v>2</v>
@@ -1591,7 +1588,7 @@
         <v>2024</v>
       </c>
       <c r="H14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
@@ -1609,7 +1606,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
         <v>3</v>
@@ -1624,7 +1621,7 @@
         <v>2024</v>
       </c>
       <c r="H15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
@@ -1642,7 +1639,7 @@
         <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
         <v>4</v>
@@ -1657,7 +1654,7 @@
         <v>2024</v>
       </c>
       <c r="H16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
@@ -1675,7 +1672,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>5</v>
@@ -1690,7 +1687,7 @@
         <v>2024</v>
       </c>
       <c r="H17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
@@ -1708,7 +1705,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
@@ -1723,7 +1720,7 @@
         <v>2024</v>
       </c>
       <c r="H18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
@@ -1741,7 +1738,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
@@ -1756,7 +1753,7 @@
         <v>2024</v>
       </c>
       <c r="H19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I19" t="n">
         <v>1</v>
@@ -1774,7 +1771,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D20" t="n">
         <v>8</v>
@@ -1789,7 +1786,7 @@
         <v>2024</v>
       </c>
       <c r="H20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
@@ -1807,7 +1804,7 @@
         <v>2</v>
       </c>
       <c r="C21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1822,7 +1819,7 @@
         <v>2024</v>
       </c>
       <c r="H21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
@@ -1840,7 +1837,7 @@
         <v>2</v>
       </c>
       <c r="C22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D22" t="n">
         <v>10</v>
@@ -1855,7 +1852,7 @@
         <v>2024</v>
       </c>
       <c r="H22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
@@ -1873,7 +1870,7 @@
         <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D23" t="n">
         <v>11</v>
@@ -1888,7 +1885,7 @@
         <v>2024</v>
       </c>
       <c r="H23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
@@ -1906,7 +1903,7 @@
         <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D24" t="n">
         <v>1</v>
@@ -1921,7 +1918,7 @@
         <v>2024</v>
       </c>
       <c r="H24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
@@ -1939,7 +1936,7 @@
         <v>3</v>
       </c>
       <c r="C25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D25" t="n">
         <v>2</v>
@@ -1954,7 +1951,7 @@
         <v>2024</v>
       </c>
       <c r="H25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I25" t="n">
         <v>1</v>
@@ -1972,7 +1969,7 @@
         <v>3</v>
       </c>
       <c r="C26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D26" t="n">
         <v>3</v>
@@ -1987,7 +1984,7 @@
         <v>2024</v>
       </c>
       <c r="H26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I26" t="n">
         <v>1</v>
@@ -2005,7 +2002,7 @@
         <v>3</v>
       </c>
       <c r="C27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D27" t="n">
         <v>4</v>
@@ -2020,7 +2017,7 @@
         <v>2024</v>
       </c>
       <c r="H27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I27" t="n">
         <v>1</v>
@@ -2038,7 +2035,7 @@
         <v>3</v>
       </c>
       <c r="C28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D28" t="n">
         <v>5</v>
@@ -2053,7 +2050,7 @@
         <v>2024</v>
       </c>
       <c r="H28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I28" t="n">
         <v>1</v>
@@ -2071,7 +2068,7 @@
         <v>3</v>
       </c>
       <c r="C29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D29" t="n">
         <v>6</v>
@@ -2086,7 +2083,7 @@
         <v>2024</v>
       </c>
       <c r="H29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I29" t="n">
         <v>1</v>
@@ -2104,7 +2101,7 @@
         <v>3</v>
       </c>
       <c r="C30" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D30" t="n">
         <v>7</v>
@@ -2119,7 +2116,7 @@
         <v>2024</v>
       </c>
       <c r="H30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I30" t="n">
         <v>1</v>
@@ -2137,7 +2134,7 @@
         <v>3</v>
       </c>
       <c r="C31" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D31" t="n">
         <v>8</v>
@@ -2152,7 +2149,7 @@
         <v>2024</v>
       </c>
       <c r="H31" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I31" t="n">
         <v>1</v>
@@ -2170,7 +2167,7 @@
         <v>3</v>
       </c>
       <c r="C32" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D32" t="n">
         <v>9</v>
@@ -2185,7 +2182,7 @@
         <v>2024</v>
       </c>
       <c r="H32" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I32" t="n">
         <v>1</v>
@@ -2203,7 +2200,7 @@
         <v>3</v>
       </c>
       <c r="C33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D33" t="n">
         <v>10</v>
@@ -2218,7 +2215,7 @@
         <v>2024</v>
       </c>
       <c r="H33" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I33" t="n">
         <v>1</v>
@@ -2236,7 +2233,7 @@
         <v>3</v>
       </c>
       <c r="C34" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D34" t="n">
         <v>11</v>
@@ -2251,7 +2248,7 @@
         <v>2024</v>
       </c>
       <c r="H34" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I34" t="n">
         <v>1</v>
@@ -2269,7 +2266,7 @@
         <v>4</v>
       </c>
       <c r="C35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D35" t="n">
         <v>1</v>
@@ -2284,7 +2281,7 @@
         <v>2024</v>
       </c>
       <c r="H35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I35" t="n">
         <v>1</v>
@@ -2302,7 +2299,7 @@
         <v>4</v>
       </c>
       <c r="C36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D36" t="n">
         <v>2</v>
@@ -2317,7 +2314,7 @@
         <v>2024</v>
       </c>
       <c r="H36" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I36" t="n">
         <v>1</v>
@@ -2335,7 +2332,7 @@
         <v>4</v>
       </c>
       <c r="C37" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D37" t="n">
         <v>3</v>
@@ -2350,7 +2347,7 @@
         <v>2024</v>
       </c>
       <c r="H37" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I37" t="n">
         <v>1</v>
@@ -2368,7 +2365,7 @@
         <v>4</v>
       </c>
       <c r="C38" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D38" t="n">
         <v>4</v>
@@ -2383,7 +2380,7 @@
         <v>2024</v>
       </c>
       <c r="H38" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I38" t="n">
         <v>1</v>
@@ -2401,7 +2398,7 @@
         <v>4</v>
       </c>
       <c r="C39" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D39" t="n">
         <v>5</v>
@@ -2416,7 +2413,7 @@
         <v>2024</v>
       </c>
       <c r="H39" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I39" t="n">
         <v>1</v>
@@ -2434,7 +2431,7 @@
         <v>4</v>
       </c>
       <c r="C40" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D40" t="n">
         <v>6</v>
@@ -2449,7 +2446,7 @@
         <v>2024</v>
       </c>
       <c r="H40" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I40" t="n">
         <v>1</v>
@@ -2467,7 +2464,7 @@
         <v>4</v>
       </c>
       <c r="C41" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D41" t="n">
         <v>7</v>
@@ -2482,7 +2479,7 @@
         <v>2024</v>
       </c>
       <c r="H41" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I41" t="n">
         <v>1</v>
@@ -2500,7 +2497,7 @@
         <v>4</v>
       </c>
       <c r="C42" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D42" t="n">
         <v>8</v>
@@ -2515,7 +2512,7 @@
         <v>2024</v>
       </c>
       <c r="H42" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I42" t="n">
         <v>1</v>
@@ -2533,7 +2530,7 @@
         <v>4</v>
       </c>
       <c r="C43" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D43" t="n">
         <v>9</v>
@@ -2548,7 +2545,7 @@
         <v>2024</v>
       </c>
       <c r="H43" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I43" t="n">
         <v>1</v>
@@ -2566,7 +2563,7 @@
         <v>4</v>
       </c>
       <c r="C44" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D44" t="n">
         <v>10</v>
@@ -2581,7 +2578,7 @@
         <v>2024</v>
       </c>
       <c r="H44" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I44" t="n">
         <v>1</v>
@@ -2599,7 +2596,7 @@
         <v>4</v>
       </c>
       <c r="C45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D45" t="n">
         <v>11</v>
@@ -2614,7 +2611,7 @@
         <v>2024</v>
       </c>
       <c r="H45" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I45" t="n">
         <v>1</v>
@@ -2632,7 +2629,7 @@
         <v>5</v>
       </c>
       <c r="C46" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D46" t="n">
         <v>1</v>
@@ -2647,7 +2644,7 @@
         <v>2024</v>
       </c>
       <c r="H46" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I46" t="n">
         <v>1</v>
@@ -2665,7 +2662,7 @@
         <v>5</v>
       </c>
       <c r="C47" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D47" t="n">
         <v>2</v>
@@ -2680,7 +2677,7 @@
         <v>2024</v>
       </c>
       <c r="H47" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I47" t="n">
         <v>1</v>
@@ -2698,7 +2695,7 @@
         <v>5</v>
       </c>
       <c r="C48" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D48" t="n">
         <v>3</v>
@@ -2713,7 +2710,7 @@
         <v>2024</v>
       </c>
       <c r="H48" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I48" t="n">
         <v>1</v>
@@ -2731,7 +2728,7 @@
         <v>5</v>
       </c>
       <c r="C49" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D49" t="n">
         <v>4</v>
@@ -2746,7 +2743,7 @@
         <v>2024</v>
       </c>
       <c r="H49" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I49" t="n">
         <v>1</v>
@@ -2764,7 +2761,7 @@
         <v>5</v>
       </c>
       <c r="C50" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D50" t="n">
         <v>5</v>
@@ -2779,7 +2776,7 @@
         <v>2024</v>
       </c>
       <c r="H50" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I50" t="n">
         <v>1</v>
@@ -2797,7 +2794,7 @@
         <v>5</v>
       </c>
       <c r="C51" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D51" t="n">
         <v>6</v>
@@ -2812,7 +2809,7 @@
         <v>2024</v>
       </c>
       <c r="H51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I51" t="n">
         <v>1</v>
@@ -2830,7 +2827,7 @@
         <v>5</v>
       </c>
       <c r="C52" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D52" t="n">
         <v>7</v>
@@ -2845,7 +2842,7 @@
         <v>2024</v>
       </c>
       <c r="H52" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I52" t="n">
         <v>1</v>
@@ -2863,7 +2860,7 @@
         <v>5</v>
       </c>
       <c r="C53" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D53" t="n">
         <v>8</v>
@@ -2878,7 +2875,7 @@
         <v>2024</v>
       </c>
       <c r="H53" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I53" t="n">
         <v>1</v>
@@ -2896,7 +2893,7 @@
         <v>5</v>
       </c>
       <c r="C54" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D54" t="n">
         <v>9</v>
@@ -2911,7 +2908,7 @@
         <v>2024</v>
       </c>
       <c r="H54" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I54" t="n">
         <v>1</v>
@@ -2929,7 +2926,7 @@
         <v>5</v>
       </c>
       <c r="C55" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D55" t="n">
         <v>10</v>
@@ -2944,7 +2941,7 @@
         <v>2024</v>
       </c>
       <c r="H55" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I55" t="n">
         <v>1</v>
@@ -2962,7 +2959,7 @@
         <v>5</v>
       </c>
       <c r="C56" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D56" t="n">
         <v>11</v>
@@ -2977,7 +2974,7 @@
         <v>2024</v>
       </c>
       <c r="H56" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I56" t="n">
         <v>1</v>
@@ -2995,7 +2992,7 @@
         <v>6</v>
       </c>
       <c r="C57" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D57" t="n">
         <v>1</v>
@@ -3010,7 +3007,7 @@
         <v>2024</v>
       </c>
       <c r="H57" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I57" t="n">
         <v>1</v>
@@ -3028,7 +3025,7 @@
         <v>6</v>
       </c>
       <c r="C58" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D58" t="n">
         <v>2</v>
@@ -3043,7 +3040,7 @@
         <v>2024</v>
       </c>
       <c r="H58" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I58" t="n">
         <v>1</v>
@@ -3061,7 +3058,7 @@
         <v>6</v>
       </c>
       <c r="C59" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D59" t="n">
         <v>3</v>
@@ -3076,7 +3073,7 @@
         <v>2024</v>
       </c>
       <c r="H59" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I59" t="n">
         <v>1</v>
@@ -3094,7 +3091,7 @@
         <v>6</v>
       </c>
       <c r="C60" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D60" t="n">
         <v>4</v>
@@ -3109,7 +3106,7 @@
         <v>2024</v>
       </c>
       <c r="H60" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I60" t="n">
         <v>1</v>
@@ -3127,7 +3124,7 @@
         <v>6</v>
       </c>
       <c r="C61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D61" t="n">
         <v>5</v>
@@ -3142,7 +3139,7 @@
         <v>2024</v>
       </c>
       <c r="H61" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I61" t="n">
         <v>1</v>
@@ -3160,7 +3157,7 @@
         <v>6</v>
       </c>
       <c r="C62" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D62" t="n">
         <v>6</v>
@@ -3175,7 +3172,7 @@
         <v>2024</v>
       </c>
       <c r="H62" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I62" t="n">
         <v>1</v>
@@ -3193,7 +3190,7 @@
         <v>6</v>
       </c>
       <c r="C63" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D63" t="n">
         <v>7</v>
@@ -3208,7 +3205,7 @@
         <v>2024</v>
       </c>
       <c r="H63" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I63" t="n">
         <v>1</v>
@@ -3226,7 +3223,7 @@
         <v>6</v>
       </c>
       <c r="C64" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D64" t="n">
         <v>8</v>
@@ -3241,7 +3238,7 @@
         <v>2024</v>
       </c>
       <c r="H64" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I64" t="n">
         <v>1</v>
@@ -3259,7 +3256,7 @@
         <v>6</v>
       </c>
       <c r="C65" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D65" t="n">
         <v>9</v>
@@ -3274,7 +3271,7 @@
         <v>2024</v>
       </c>
       <c r="H65" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I65" t="n">
         <v>1</v>
@@ -3292,7 +3289,7 @@
         <v>6</v>
       </c>
       <c r="C66" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D66" t="n">
         <v>10</v>
@@ -3307,7 +3304,7 @@
         <v>2024</v>
       </c>
       <c r="H66" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I66" t="n">
         <v>1</v>
@@ -3325,7 +3322,7 @@
         <v>6</v>
       </c>
       <c r="C67" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D67" t="n">
         <v>11</v>
@@ -3340,7 +3337,7 @@
         <v>2024</v>
       </c>
       <c r="H67" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I67" t="n">
         <v>1</v>
@@ -3358,7 +3355,7 @@
         <v>7</v>
       </c>
       <c r="C68" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D68" t="n">
         <v>1</v>
@@ -3373,7 +3370,7 @@
         <v>2024</v>
       </c>
       <c r="H68" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I68" t="n">
         <v>1</v>
@@ -3391,7 +3388,7 @@
         <v>7</v>
       </c>
       <c r="C69" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D69" t="n">
         <v>2</v>
@@ -3406,7 +3403,7 @@
         <v>2024</v>
       </c>
       <c r="H69" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I69" t="n">
         <v>1</v>
@@ -3424,7 +3421,7 @@
         <v>7</v>
       </c>
       <c r="C70" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D70" t="n">
         <v>3</v>
@@ -3439,7 +3436,7 @@
         <v>2024</v>
       </c>
       <c r="H70" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I70" t="n">
         <v>1</v>
@@ -3457,7 +3454,7 @@
         <v>7</v>
       </c>
       <c r="C71" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D71" t="n">
         <v>4</v>
@@ -3472,7 +3469,7 @@
         <v>2024</v>
       </c>
       <c r="H71" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I71" t="n">
         <v>1</v>
@@ -3490,7 +3487,7 @@
         <v>7</v>
       </c>
       <c r="C72" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D72" t="n">
         <v>5</v>
@@ -3505,7 +3502,7 @@
         <v>2024</v>
       </c>
       <c r="H72" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I72" t="n">
         <v>1</v>
@@ -3523,7 +3520,7 @@
         <v>7</v>
       </c>
       <c r="C73" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D73" t="n">
         <v>6</v>
@@ -3538,7 +3535,7 @@
         <v>2024</v>
       </c>
       <c r="H73" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I73" t="n">
         <v>1</v>
@@ -3556,7 +3553,7 @@
         <v>7</v>
       </c>
       <c r="C74" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D74" t="n">
         <v>7</v>
@@ -3571,7 +3568,7 @@
         <v>2024</v>
       </c>
       <c r="H74" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I74" t="n">
         <v>1</v>
@@ -3589,7 +3586,7 @@
         <v>7</v>
       </c>
       <c r="C75" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D75" t="n">
         <v>8</v>
@@ -3604,7 +3601,7 @@
         <v>2024</v>
       </c>
       <c r="H75" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I75" t="n">
         <v>1</v>
@@ -3622,7 +3619,7 @@
         <v>7</v>
       </c>
       <c r="C76" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D76" t="n">
         <v>9</v>
@@ -3637,7 +3634,7 @@
         <v>2024</v>
       </c>
       <c r="H76" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I76" t="n">
         <v>1</v>
@@ -3655,7 +3652,7 @@
         <v>7</v>
       </c>
       <c r="C77" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D77" t="n">
         <v>10</v>
@@ -3670,7 +3667,7 @@
         <v>2024</v>
       </c>
       <c r="H77" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I77" t="n">
         <v>1</v>
@@ -3688,7 +3685,7 @@
         <v>7</v>
       </c>
       <c r="C78" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D78" t="n">
         <v>11</v>
@@ -3703,7 +3700,7 @@
         <v>2024</v>
       </c>
       <c r="H78" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I78" t="n">
         <v>1</v>
@@ -3721,7 +3718,7 @@
         <v>8</v>
       </c>
       <c r="C79" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D79" t="n">
         <v>1</v>
@@ -3736,7 +3733,7 @@
         <v>2024</v>
       </c>
       <c r="H79" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I79" t="n">
         <v>1</v>
@@ -3754,7 +3751,7 @@
         <v>8</v>
       </c>
       <c r="C80" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D80" t="n">
         <v>2</v>
@@ -3769,7 +3766,7 @@
         <v>2024</v>
       </c>
       <c r="H80" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I80" t="n">
         <v>1</v>
@@ -3787,7 +3784,7 @@
         <v>8</v>
       </c>
       <c r="C81" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D81" t="n">
         <v>3</v>
@@ -3802,7 +3799,7 @@
         <v>2024</v>
       </c>
       <c r="H81" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I81" t="n">
         <v>1</v>
@@ -3820,7 +3817,7 @@
         <v>8</v>
       </c>
       <c r="C82" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D82" t="n">
         <v>4</v>
@@ -3835,7 +3832,7 @@
         <v>2024</v>
       </c>
       <c r="H82" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I82" t="n">
         <v>1</v>
@@ -3853,7 +3850,7 @@
         <v>8</v>
       </c>
       <c r="C83" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D83" t="n">
         <v>5</v>
@@ -3868,7 +3865,7 @@
         <v>2024</v>
       </c>
       <c r="H83" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I83" t="n">
         <v>1</v>
@@ -3886,7 +3883,7 @@
         <v>8</v>
       </c>
       <c r="C84" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D84" t="n">
         <v>6</v>
@@ -3901,7 +3898,7 @@
         <v>2024</v>
       </c>
       <c r="H84" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I84" t="n">
         <v>1</v>
@@ -3919,7 +3916,7 @@
         <v>8</v>
       </c>
       <c r="C85" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D85" t="n">
         <v>7</v>
@@ -3934,7 +3931,7 @@
         <v>2024</v>
       </c>
       <c r="H85" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I85" t="n">
         <v>1</v>
@@ -3952,7 +3949,7 @@
         <v>8</v>
       </c>
       <c r="C86" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D86" t="n">
         <v>8</v>
@@ -3967,7 +3964,7 @@
         <v>2024</v>
       </c>
       <c r="H86" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I86" t="n">
         <v>1</v>
@@ -3985,7 +3982,7 @@
         <v>8</v>
       </c>
       <c r="C87" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D87" t="n">
         <v>9</v>
@@ -4000,7 +3997,7 @@
         <v>2024</v>
       </c>
       <c r="H87" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I87" t="n">
         <v>1</v>
@@ -4018,7 +4015,7 @@
         <v>8</v>
       </c>
       <c r="C88" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D88" t="n">
         <v>10</v>
@@ -4033,7 +4030,7 @@
         <v>2024</v>
       </c>
       <c r="H88" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I88" t="n">
         <v>1</v>
@@ -4051,7 +4048,7 @@
         <v>8</v>
       </c>
       <c r="C89" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D89" t="n">
         <v>11</v>
@@ -4066,7 +4063,7 @@
         <v>2024</v>
       </c>
       <c r="H89" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I89" t="n">
         <v>1</v>
@@ -4084,7 +4081,7 @@
         <v>9</v>
       </c>
       <c r="C90" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D90" t="n">
         <v>1</v>
@@ -4099,7 +4096,7 @@
         <v>2024</v>
       </c>
       <c r="H90" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I90" t="n">
         <v>1</v>
@@ -4117,7 +4114,7 @@
         <v>9</v>
       </c>
       <c r="C91" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D91" t="n">
         <v>2</v>
@@ -4132,7 +4129,7 @@
         <v>2024</v>
       </c>
       <c r="H91" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I91" t="n">
         <v>1</v>
@@ -4150,7 +4147,7 @@
         <v>9</v>
       </c>
       <c r="C92" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D92" t="n">
         <v>3</v>
@@ -4165,7 +4162,7 @@
         <v>2024</v>
       </c>
       <c r="H92" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I92" t="n">
         <v>1</v>
@@ -4183,7 +4180,7 @@
         <v>9</v>
       </c>
       <c r="C93" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D93" t="n">
         <v>4</v>
@@ -4198,7 +4195,7 @@
         <v>2024</v>
       </c>
       <c r="H93" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I93" t="n">
         <v>1</v>
@@ -4216,7 +4213,7 @@
         <v>9</v>
       </c>
       <c r="C94" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D94" t="n">
         <v>5</v>
@@ -4231,7 +4228,7 @@
         <v>2024</v>
       </c>
       <c r="H94" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I94" t="n">
         <v>1</v>
@@ -4249,7 +4246,7 @@
         <v>9</v>
       </c>
       <c r="C95" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D95" t="n">
         <v>6</v>
@@ -4264,7 +4261,7 @@
         <v>2024</v>
       </c>
       <c r="H95" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I95" t="n">
         <v>1</v>
@@ -4282,7 +4279,7 @@
         <v>9</v>
       </c>
       <c r="C96" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D96" t="n">
         <v>7</v>
@@ -4297,7 +4294,7 @@
         <v>2024</v>
       </c>
       <c r="H96" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I96" t="n">
         <v>1</v>
@@ -4315,7 +4312,7 @@
         <v>9</v>
       </c>
       <c r="C97" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D97" t="n">
         <v>8</v>
@@ -4330,7 +4327,7 @@
         <v>2024</v>
       </c>
       <c r="H97" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I97" t="n">
         <v>1</v>
@@ -4348,7 +4345,7 @@
         <v>9</v>
       </c>
       <c r="C98" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D98" t="n">
         <v>9</v>
@@ -4363,7 +4360,7 @@
         <v>2024</v>
       </c>
       <c r="H98" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I98" t="n">
         <v>1</v>
@@ -4381,7 +4378,7 @@
         <v>9</v>
       </c>
       <c r="C99" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D99" t="n">
         <v>10</v>
@@ -4396,7 +4393,7 @@
         <v>2024</v>
       </c>
       <c r="H99" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I99" t="n">
         <v>1</v>
@@ -4414,7 +4411,7 @@
         <v>9</v>
       </c>
       <c r="C100" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D100" t="n">
         <v>11</v>
@@ -4429,7 +4426,7 @@
         <v>2024</v>
       </c>
       <c r="H100" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I100" t="n">
         <v>1</v>
@@ -4447,7 +4444,7 @@
         <v>10</v>
       </c>
       <c r="C101" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D101" t="n">
         <v>1</v>
@@ -4462,7 +4459,7 @@
         <v>2024</v>
       </c>
       <c r="H101" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I101" t="n">
         <v>1</v>
@@ -4480,7 +4477,7 @@
         <v>10</v>
       </c>
       <c r="C102" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D102" t="n">
         <v>2</v>
@@ -4495,7 +4492,7 @@
         <v>2024</v>
       </c>
       <c r="H102" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I102" t="n">
         <v>1</v>
@@ -4513,7 +4510,7 @@
         <v>10</v>
       </c>
       <c r="C103" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D103" t="n">
         <v>3</v>
@@ -4528,7 +4525,7 @@
         <v>2024</v>
       </c>
       <c r="H103" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I103" t="n">
         <v>1</v>
@@ -4546,7 +4543,7 @@
         <v>10</v>
       </c>
       <c r="C104" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D104" t="n">
         <v>4</v>
@@ -4561,7 +4558,7 @@
         <v>2024</v>
       </c>
       <c r="H104" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I104" t="n">
         <v>1</v>
@@ -4579,7 +4576,7 @@
         <v>10</v>
       </c>
       <c r="C105" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D105" t="n">
         <v>5</v>
@@ -4594,7 +4591,7 @@
         <v>2024</v>
       </c>
       <c r="H105" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I105" t="n">
         <v>1</v>
@@ -4612,7 +4609,7 @@
         <v>10</v>
       </c>
       <c r="C106" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D106" t="n">
         <v>6</v>
@@ -4627,7 +4624,7 @@
         <v>2024</v>
       </c>
       <c r="H106" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I106" t="n">
         <v>1</v>
@@ -4645,7 +4642,7 @@
         <v>10</v>
       </c>
       <c r="C107" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D107" t="n">
         <v>7</v>
@@ -4660,7 +4657,7 @@
         <v>2024</v>
       </c>
       <c r="H107" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I107" t="n">
         <v>1</v>
@@ -4678,7 +4675,7 @@
         <v>10</v>
       </c>
       <c r="C108" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D108" t="n">
         <v>8</v>
@@ -4693,7 +4690,7 @@
         <v>2024</v>
       </c>
       <c r="H108" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I108" t="n">
         <v>1</v>
@@ -4711,7 +4708,7 @@
         <v>10</v>
       </c>
       <c r="C109" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D109" t="n">
         <v>9</v>
@@ -4726,7 +4723,7 @@
         <v>2024</v>
       </c>
       <c r="H109" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I109" t="n">
         <v>1</v>
@@ -4744,7 +4741,7 @@
         <v>10</v>
       </c>
       <c r="C110" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D110" t="n">
         <v>10</v>
@@ -4759,7 +4756,7 @@
         <v>2024</v>
       </c>
       <c r="H110" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I110" t="n">
         <v>1</v>
@@ -4777,7 +4774,7 @@
         <v>10</v>
       </c>
       <c r="C111" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D111" t="n">
         <v>11</v>
@@ -4792,7 +4789,7 @@
         <v>2024</v>
       </c>
       <c r="H111" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I111" t="n">
         <v>1</v>
@@ -4804,13 +4801,13 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B112" t="n">
         <v>11</v>
       </c>
       <c r="C112" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D112" t="n">
         <v>1</v>
@@ -4825,7 +4822,7 @@
         <v>2024</v>
       </c>
       <c r="H112" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I112" t="n">
         <v>1</v>
@@ -4837,13 +4834,13 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B113" t="n">
         <v>11</v>
       </c>
       <c r="C113" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D113" t="n">
         <v>2</v>
@@ -4858,7 +4855,7 @@
         <v>2024</v>
       </c>
       <c r="H113" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I113" t="n">
         <v>1</v>
@@ -4870,13 +4867,13 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B114" t="n">
         <v>11</v>
       </c>
       <c r="C114" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D114" t="n">
         <v>3</v>
@@ -4891,7 +4888,7 @@
         <v>2024</v>
       </c>
       <c r="H114" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I114" t="n">
         <v>1</v>
@@ -4903,13 +4900,13 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B115" t="n">
         <v>11</v>
       </c>
       <c r="C115" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D115" t="n">
         <v>4</v>
@@ -4924,7 +4921,7 @@
         <v>2024</v>
       </c>
       <c r="H115" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I115" t="n">
         <v>1</v>
@@ -4936,13 +4933,13 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B116" t="n">
         <v>11</v>
       </c>
       <c r="C116" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D116" t="n">
         <v>5</v>
@@ -4957,7 +4954,7 @@
         <v>2024</v>
       </c>
       <c r="H116" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I116" t="n">
         <v>1</v>
@@ -4969,13 +4966,13 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B117" t="n">
         <v>11</v>
       </c>
       <c r="C117" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D117" t="n">
         <v>6</v>
@@ -4990,7 +4987,7 @@
         <v>2024</v>
       </c>
       <c r="H117" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I117" t="n">
         <v>1</v>
@@ -5002,13 +4999,13 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B118" t="n">
         <v>11</v>
       </c>
       <c r="C118" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D118" t="n">
         <v>7</v>
@@ -5023,7 +5020,7 @@
         <v>2024</v>
       </c>
       <c r="H118" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I118" t="n">
         <v>1</v>
@@ -5035,13 +5032,13 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B119" t="n">
         <v>11</v>
       </c>
       <c r="C119" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D119" t="n">
         <v>8</v>
@@ -5056,7 +5053,7 @@
         <v>2024</v>
       </c>
       <c r="H119" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I119" t="n">
         <v>1</v>
@@ -5068,13 +5065,13 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B120" t="n">
         <v>11</v>
       </c>
       <c r="C120" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D120" t="n">
         <v>9</v>
@@ -5089,7 +5086,7 @@
         <v>2024</v>
       </c>
       <c r="H120" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I120" t="n">
         <v>1</v>
@@ -5101,13 +5098,13 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B121" t="n">
         <v>11</v>
       </c>
       <c r="C121" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D121" t="n">
         <v>10</v>
@@ -5122,7 +5119,7 @@
         <v>2024</v>
       </c>
       <c r="H121" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I121" t="n">
         <v>1</v>
@@ -5134,13 +5131,13 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B122" t="n">
         <v>11</v>
       </c>
       <c r="C122" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D122" t="n">
         <v>11</v>
@@ -5155,7 +5152,7 @@
         <v>2024</v>
       </c>
       <c r="H122" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I122" t="n">
         <v>1</v>
@@ -5167,13 +5164,13 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B123" t="n">
         <v>12.1</v>
       </c>
       <c r="C123" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D123" t="n">
         <v>1</v>
@@ -5188,7 +5185,7 @@
         <v>2024</v>
       </c>
       <c r="H123" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I123" t="n">
         <v>1</v>
@@ -5200,13 +5197,13 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B124" t="n">
         <v>12.1</v>
       </c>
       <c r="C124" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D124" t="n">
         <v>2</v>
@@ -5221,7 +5218,7 @@
         <v>2024</v>
       </c>
       <c r="H124" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I124" t="n">
         <v>1</v>
@@ -5233,13 +5230,13 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B125" t="n">
         <v>12.1</v>
       </c>
       <c r="C125" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D125" t="n">
         <v>3</v>
@@ -5254,7 +5251,7 @@
         <v>2024</v>
       </c>
       <c r="H125" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I125" t="n">
         <v>1</v>
@@ -5266,13 +5263,13 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B126" t="n">
         <v>12.1</v>
       </c>
       <c r="C126" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D126" t="n">
         <v>4</v>
@@ -5287,7 +5284,7 @@
         <v>2024</v>
       </c>
       <c r="H126" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I126" t="n">
         <v>1</v>
@@ -5299,13 +5296,13 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B127" t="n">
         <v>12.1</v>
       </c>
       <c r="C127" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D127" t="n">
         <v>5</v>
@@ -5320,7 +5317,7 @@
         <v>2024</v>
       </c>
       <c r="H127" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I127" t="n">
         <v>1</v>
@@ -5332,13 +5329,13 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B128" t="n">
         <v>12.1</v>
       </c>
       <c r="C128" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D128" t="n">
         <v>6</v>
@@ -5353,7 +5350,7 @@
         <v>2024</v>
       </c>
       <c r="H128" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I128" t="n">
         <v>1</v>
@@ -5365,13 +5362,13 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B129" t="n">
         <v>12.1</v>
       </c>
       <c r="C129" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D129" t="n">
         <v>7</v>
@@ -5386,7 +5383,7 @@
         <v>2024</v>
       </c>
       <c r="H129" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I129" t="n">
         <v>1</v>
@@ -5398,13 +5395,13 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B130" t="n">
         <v>12.1</v>
       </c>
       <c r="C130" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D130" t="n">
         <v>8</v>
@@ -5419,7 +5416,7 @@
         <v>2024</v>
       </c>
       <c r="H130" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I130" t="n">
         <v>1</v>
@@ -5431,13 +5428,13 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B131" t="n">
         <v>12.1</v>
       </c>
       <c r="C131" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D131" t="n">
         <v>9</v>
@@ -5452,7 +5449,7 @@
         <v>2024</v>
       </c>
       <c r="H131" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I131" t="n">
         <v>1</v>
@@ -5464,13 +5461,13 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B132" t="n">
         <v>12.1</v>
       </c>
       <c r="C132" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D132" t="n">
         <v>10</v>
@@ -5485,7 +5482,7 @@
         <v>2024</v>
       </c>
       <c r="H132" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I132" t="n">
         <v>1</v>
@@ -5497,13 +5494,13 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B133" t="n">
         <v>12.1</v>
       </c>
       <c r="C133" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D133" t="n">
         <v>11</v>
@@ -5518,7 +5515,7 @@
         <v>2024</v>
       </c>
       <c r="H133" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I133" t="n">
         <v>1</v>
@@ -5589,7 +5586,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D4" t="n">
         <v>22</v>
@@ -5606,7 +5603,7 @@
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6">
@@ -5701,7 +5698,7 @@
         <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D12" t="n">
         <v>19</v>
@@ -5830,7 +5827,7 @@
         <v>8</v>
       </c>
       <c r="D21" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22">
@@ -5869,7 +5866,7 @@
         <v>6</v>
       </c>
       <c r="C24" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D24" t="n">
         <v>76</v>
@@ -5886,7 +5883,7 @@
         <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>193</v>
+        <v>169</v>
       </c>
     </row>
     <row r="26">
@@ -5942,7 +5939,7 @@
         <v>8</v>
       </c>
       <c r="D29" t="n">
-        <v>348</v>
+        <v>245</v>
       </c>
     </row>
     <row r="30">
@@ -5967,10 +5964,10 @@
         <v>8</v>
       </c>
       <c r="C31" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="D31" t="n">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="32">
@@ -5984,7 +5981,7 @@
         <v>47</v>
       </c>
       <c r="D32" t="n">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="33">
@@ -5998,7 +5995,7 @@
         <v>8</v>
       </c>
       <c r="D33" t="n">
-        <v>529</v>
+        <v>386</v>
       </c>
     </row>
     <row r="34">
@@ -6023,7 +6020,7 @@
         <v>9</v>
       </c>
       <c r="C35" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D35" t="n">
         <v>200</v>
@@ -6037,7 +6034,7 @@
         <v>9</v>
       </c>
       <c r="C36" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D36" t="n">
         <v>205</v>
@@ -6054,7 +6051,7 @@
         <v>8</v>
       </c>
       <c r="D37" t="n">
-        <v>547</v>
+        <v>392</v>
       </c>
     </row>
     <row r="38">
@@ -6079,7 +6076,7 @@
         <v>10</v>
       </c>
       <c r="C39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D39" t="n">
         <v>139</v>
@@ -6093,7 +6090,7 @@
         <v>10</v>
       </c>
       <c r="C40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D40" t="n">
         <v>239</v>
@@ -6110,12 +6107,12 @@
         <v>8</v>
       </c>
       <c r="D41" t="n">
-        <v>449</v>
+        <v>315</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B42" t="n">
         <v>11</v>
@@ -6129,27 +6126,27 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B43" t="n">
         <v>11</v>
       </c>
       <c r="C43" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D43" t="n">
-        <v>315</v>
+        <v>162</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B44" t="n">
         <v>11</v>
       </c>
       <c r="C44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D44" t="n">
         <v>201</v>
@@ -6157,7 +6154,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B45" t="n">
         <v>11</v>
@@ -6166,7 +6163,7 @@
         <v>8</v>
       </c>
       <c r="D45" t="n">
-        <v>524</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>
@@ -6188,31 +6185,31 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" t="s">
         <v>22</v>
-      </c>
-      <c r="D1" t="s">
-        <v>23</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
       </c>
       <c r="F1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" t="s">
         <v>24</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>25</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>26</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>27</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>28</v>
-      </c>
-      <c r="K1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2">
@@ -6223,7 +6220,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -6238,7 +6235,7 @@
         <v>2024</v>
       </c>
       <c r="H2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -6256,7 +6253,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -6271,7 +6268,7 @@
         <v>2024</v>
       </c>
       <c r="H3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -6289,7 +6286,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -6304,7 +6301,7 @@
         <v>2024</v>
       </c>
       <c r="H4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -6322,7 +6319,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -6337,7 +6334,7 @@
         <v>2024</v>
       </c>
       <c r="H5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -6355,13 +6352,13 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F6" t="n">
         <v>2008</v>
@@ -6370,14 +6367,14 @@
         <v>2024</v>
       </c>
       <c r="H6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
       </c>
       <c r="J6"/>
       <c r="K6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
@@ -6388,13 +6385,13 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F7" t="n">
         <v>2008</v>
@@ -6403,14 +6400,14 @@
         <v>2024</v>
       </c>
       <c r="H7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7"/>
       <c r="K7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
@@ -6421,7 +6418,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
@@ -6436,7 +6433,7 @@
         <v>2024</v>
       </c>
       <c r="H8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -6454,13 +6451,13 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F9"/>
       <c r="G9"/>
@@ -6468,7 +6465,7 @@
       <c r="I9"/>
       <c r="J9"/>
       <c r="K9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
@@ -6479,7 +6476,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D10" t="n">
         <v>9</v>
@@ -6494,7 +6491,7 @@
         <v>2024</v>
       </c>
       <c r="H10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
@@ -6512,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
@@ -6527,7 +6524,7 @@
         <v>2024</v>
       </c>
       <c r="H11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -6545,7 +6542,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D12" t="n">
         <v>11</v>
@@ -6560,7 +6557,7 @@
         <v>2024</v>
       </c>
       <c r="H12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
@@ -6578,7 +6575,7 @@
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D13" t="n">
         <v>1</v>
@@ -6593,7 +6590,7 @@
         <v>2024</v>
       </c>
       <c r="H13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -6611,7 +6608,7 @@
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D14" t="n">
         <v>2</v>
@@ -6626,7 +6623,7 @@
         <v>2024</v>
       </c>
       <c r="H14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
@@ -6644,7 +6641,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
         <v>3</v>
@@ -6659,7 +6656,7 @@
         <v>2024</v>
       </c>
       <c r="H15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
@@ -6677,7 +6674,7 @@
         <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
         <v>4</v>
@@ -6692,7 +6689,7 @@
         <v>2024</v>
       </c>
       <c r="H16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
@@ -6710,13 +6707,13 @@
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>5</v>
       </c>
       <c r="E17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F17" t="n">
         <v>2008</v>
@@ -6725,14 +6722,14 @@
         <v>2024</v>
       </c>
       <c r="H17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
       </c>
       <c r="J17"/>
       <c r="K17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18">
@@ -6743,13 +6740,13 @@
         <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
       </c>
       <c r="E18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F18" t="n">
         <v>2008</v>
@@ -6758,14 +6755,14 @@
         <v>2024</v>
       </c>
       <c r="H18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
       </c>
       <c r="J18"/>
       <c r="K18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19">
@@ -6776,7 +6773,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
@@ -6791,7 +6788,7 @@
         <v>2024</v>
       </c>
       <c r="H19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I19" t="n">
         <v>1</v>
@@ -6809,7 +6806,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D20" t="n">
         <v>8</v>
@@ -6824,7 +6821,7 @@
         <v>2024</v>
       </c>
       <c r="H20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
@@ -6842,13 +6839,13 @@
         <v>2</v>
       </c>
       <c r="C21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
       </c>
       <c r="E21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F21"/>
       <c r="G21"/>
@@ -6856,7 +6853,7 @@
       <c r="I21"/>
       <c r="J21"/>
       <c r="K21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22">
@@ -6867,7 +6864,7 @@
         <v>2</v>
       </c>
       <c r="C22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D22" t="n">
         <v>10</v>
@@ -6882,7 +6879,7 @@
         <v>2024</v>
       </c>
       <c r="H22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
@@ -6900,7 +6897,7 @@
         <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D23" t="n">
         <v>11</v>
@@ -6915,7 +6912,7 @@
         <v>2024</v>
       </c>
       <c r="H23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
@@ -6933,7 +6930,7 @@
         <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D24" t="n">
         <v>1</v>
@@ -6948,7 +6945,7 @@
         <v>2024</v>
       </c>
       <c r="H24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
@@ -6966,7 +6963,7 @@
         <v>3</v>
       </c>
       <c r="C25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D25" t="n">
         <v>2</v>
@@ -6981,7 +6978,7 @@
         <v>2024</v>
       </c>
       <c r="H25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I25" t="n">
         <v>1</v>
@@ -6999,7 +6996,7 @@
         <v>3</v>
       </c>
       <c r="C26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D26" t="n">
         <v>3</v>
@@ -7014,7 +7011,7 @@
         <v>2024</v>
       </c>
       <c r="H26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I26" t="n">
         <v>1</v>
@@ -7032,7 +7029,7 @@
         <v>3</v>
       </c>
       <c r="C27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D27" t="n">
         <v>4</v>
@@ -7047,7 +7044,7 @@
         <v>2024</v>
       </c>
       <c r="H27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I27" t="n">
         <v>1</v>
@@ -7065,7 +7062,7 @@
         <v>3</v>
       </c>
       <c r="C28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D28" t="n">
         <v>5</v>
@@ -7080,7 +7077,7 @@
         <v>2024</v>
       </c>
       <c r="H28" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I28" t="n">
         <v>1</v>
@@ -7098,7 +7095,7 @@
         <v>3</v>
       </c>
       <c r="C29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D29" t="n">
         <v>6</v>
@@ -7113,7 +7110,7 @@
         <v>2024</v>
       </c>
       <c r="H29" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I29" t="n">
         <v>1</v>
@@ -7131,13 +7128,13 @@
         <v>3</v>
       </c>
       <c r="C30" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D30" t="n">
         <v>7</v>
       </c>
       <c r="E30" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F30"/>
       <c r="G30"/>
@@ -7145,7 +7142,7 @@
       <c r="I30"/>
       <c r="J30"/>
       <c r="K30" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31">
@@ -7156,13 +7153,13 @@
         <v>3</v>
       </c>
       <c r="C31" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D31" t="n">
         <v>8</v>
       </c>
       <c r="E31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F31"/>
       <c r="G31"/>
@@ -7170,7 +7167,7 @@
       <c r="I31"/>
       <c r="J31"/>
       <c r="K31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32">
@@ -7181,13 +7178,13 @@
         <v>3</v>
       </c>
       <c r="C32" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D32" t="n">
         <v>9</v>
       </c>
       <c r="E32" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F32"/>
       <c r="G32"/>
@@ -7195,7 +7192,7 @@
       <c r="I32"/>
       <c r="J32"/>
       <c r="K32" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33">
@@ -7206,7 +7203,7 @@
         <v>3</v>
       </c>
       <c r="C33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D33" t="n">
         <v>10</v>
@@ -7221,7 +7218,7 @@
         <v>2024</v>
       </c>
       <c r="H33" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I33" t="n">
         <v>1</v>
@@ -7239,7 +7236,7 @@
         <v>3</v>
       </c>
       <c r="C34" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D34" t="n">
         <v>11</v>
@@ -7254,7 +7251,7 @@
         <v>2024</v>
       </c>
       <c r="H34" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I34" t="n">
         <v>1</v>
@@ -7272,7 +7269,7 @@
         <v>4</v>
       </c>
       <c r="C35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D35" t="n">
         <v>1</v>
@@ -7287,7 +7284,7 @@
         <v>2024</v>
       </c>
       <c r="H35" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I35" t="n">
         <v>1</v>
@@ -7305,7 +7302,7 @@
         <v>4</v>
       </c>
       <c r="C36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D36" t="n">
         <v>2</v>
@@ -7320,7 +7317,7 @@
         <v>2024</v>
       </c>
       <c r="H36" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I36" t="n">
         <v>1</v>
@@ -7338,7 +7335,7 @@
         <v>4</v>
       </c>
       <c r="C37" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D37" t="n">
         <v>3</v>
@@ -7353,7 +7350,7 @@
         <v>2024</v>
       </c>
       <c r="H37" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I37" t="n">
         <v>1</v>
@@ -7371,7 +7368,7 @@
         <v>4</v>
       </c>
       <c r="C38" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D38" t="n">
         <v>4</v>
@@ -7386,7 +7383,7 @@
         <v>2024</v>
       </c>
       <c r="H38" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I38" t="n">
         <v>1</v>
@@ -7404,7 +7401,7 @@
         <v>4</v>
       </c>
       <c r="C39" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D39" t="n">
         <v>5</v>
@@ -7419,7 +7416,7 @@
         <v>2024</v>
       </c>
       <c r="H39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I39" t="n">
         <v>1</v>
@@ -7437,7 +7434,7 @@
         <v>4</v>
       </c>
       <c r="C40" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D40" t="n">
         <v>6</v>
@@ -7452,7 +7449,7 @@
         <v>2024</v>
       </c>
       <c r="H40" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I40" t="n">
         <v>1</v>
@@ -7470,7 +7467,7 @@
         <v>4</v>
       </c>
       <c r="C41" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D41" t="n">
         <v>7</v>
@@ -7485,7 +7482,7 @@
         <v>2024</v>
       </c>
       <c r="H41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I41" t="n">
         <v>1</v>
@@ -7503,7 +7500,7 @@
         <v>4</v>
       </c>
       <c r="C42" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D42" t="n">
         <v>8</v>
@@ -7518,7 +7515,7 @@
         <v>2024</v>
       </c>
       <c r="H42" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I42" t="n">
         <v>1</v>
@@ -7536,7 +7533,7 @@
         <v>4</v>
       </c>
       <c r="C43" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D43" t="n">
         <v>9</v>
@@ -7551,7 +7548,7 @@
         <v>2024</v>
       </c>
       <c r="H43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I43" t="n">
         <v>1</v>
@@ -7569,7 +7566,7 @@
         <v>4</v>
       </c>
       <c r="C44" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D44" t="n">
         <v>10</v>
@@ -7584,7 +7581,7 @@
         <v>2024</v>
       </c>
       <c r="H44" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I44" t="n">
         <v>1</v>
@@ -7602,7 +7599,7 @@
         <v>4</v>
       </c>
       <c r="C45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D45" t="n">
         <v>11</v>
@@ -7617,7 +7614,7 @@
         <v>2024</v>
       </c>
       <c r="H45" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I45" t="n">
         <v>1</v>
@@ -7635,7 +7632,7 @@
         <v>5</v>
       </c>
       <c r="C46" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D46" t="n">
         <v>1</v>
@@ -7650,7 +7647,7 @@
         <v>2024</v>
       </c>
       <c r="H46" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I46" t="n">
         <v>1</v>
@@ -7668,7 +7665,7 @@
         <v>5</v>
       </c>
       <c r="C47" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D47" t="n">
         <v>2</v>
@@ -7683,7 +7680,7 @@
         <v>2024</v>
       </c>
       <c r="H47" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I47" t="n">
         <v>1</v>
@@ -7701,7 +7698,7 @@
         <v>5</v>
       </c>
       <c r="C48" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D48" t="n">
         <v>3</v>
@@ -7716,7 +7713,7 @@
         <v>2024</v>
       </c>
       <c r="H48" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I48" t="n">
         <v>1</v>
@@ -7734,7 +7731,7 @@
         <v>5</v>
       </c>
       <c r="C49" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D49" t="n">
         <v>4</v>
@@ -7749,7 +7746,7 @@
         <v>2024</v>
       </c>
       <c r="H49" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I49" t="n">
         <v>1</v>
@@ -7767,7 +7764,7 @@
         <v>5</v>
       </c>
       <c r="C50" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D50" t="n">
         <v>5</v>
@@ -7782,7 +7779,7 @@
         <v>2024</v>
       </c>
       <c r="H50" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I50" t="n">
         <v>1</v>
@@ -7800,7 +7797,7 @@
         <v>5</v>
       </c>
       <c r="C51" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D51" t="n">
         <v>6</v>
@@ -7815,7 +7812,7 @@
         <v>2024</v>
       </c>
       <c r="H51" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I51" t="n">
         <v>1</v>
@@ -7833,7 +7830,7 @@
         <v>5</v>
       </c>
       <c r="C52" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D52" t="n">
         <v>7</v>
@@ -7848,7 +7845,7 @@
         <v>2024</v>
       </c>
       <c r="H52" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I52" t="n">
         <v>1</v>
@@ -7866,13 +7863,13 @@
         <v>5</v>
       </c>
       <c r="C53" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D53" t="n">
         <v>8</v>
       </c>
       <c r="E53" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F53" t="n">
         <v>2008</v>
@@ -7881,7 +7878,7 @@
         <v>2024</v>
       </c>
       <c r="H53" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
@@ -7899,7 +7896,7 @@
         <v>5</v>
       </c>
       <c r="C54" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D54" t="n">
         <v>9</v>
@@ -7914,7 +7911,7 @@
         <v>2024</v>
       </c>
       <c r="H54" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I54" t="n">
         <v>1</v>
@@ -7932,7 +7929,7 @@
         <v>5</v>
       </c>
       <c r="C55" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D55" t="n">
         <v>10</v>
@@ -7947,7 +7944,7 @@
         <v>2024</v>
       </c>
       <c r="H55" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I55" t="n">
         <v>1</v>
@@ -7965,7 +7962,7 @@
         <v>5</v>
       </c>
       <c r="C56" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D56" t="n">
         <v>11</v>
@@ -7980,7 +7977,7 @@
         <v>2024</v>
       </c>
       <c r="H56" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I56" t="n">
         <v>1</v>
@@ -7998,7 +7995,7 @@
         <v>6</v>
       </c>
       <c r="C57" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D57" t="n">
         <v>1</v>
@@ -8013,7 +8010,7 @@
         <v>2024</v>
       </c>
       <c r="H57" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I57" t="n">
         <v>1</v>
@@ -8031,7 +8028,7 @@
         <v>6</v>
       </c>
       <c r="C58" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D58" t="n">
         <v>2</v>
@@ -8046,7 +8043,7 @@
         <v>2024</v>
       </c>
       <c r="H58" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I58" t="n">
         <v>1</v>
@@ -8064,7 +8061,7 @@
         <v>6</v>
       </c>
       <c r="C59" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D59" t="n">
         <v>3</v>
@@ -8079,7 +8076,7 @@
         <v>2024</v>
       </c>
       <c r="H59" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I59" t="n">
         <v>1</v>
@@ -8097,7 +8094,7 @@
         <v>6</v>
       </c>
       <c r="C60" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D60" t="n">
         <v>4</v>
@@ -8112,7 +8109,7 @@
         <v>2024</v>
       </c>
       <c r="H60" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I60" t="n">
         <v>1</v>
@@ -8130,7 +8127,7 @@
         <v>6</v>
       </c>
       <c r="C61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D61" t="n">
         <v>5</v>
@@ -8145,7 +8142,7 @@
         <v>2024</v>
       </c>
       <c r="H61" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I61" t="n">
         <v>1</v>
@@ -8163,7 +8160,7 @@
         <v>6</v>
       </c>
       <c r="C62" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D62" t="n">
         <v>6</v>
@@ -8178,7 +8175,7 @@
         <v>2024</v>
       </c>
       <c r="H62" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I62" t="n">
         <v>1</v>
@@ -8196,7 +8193,7 @@
         <v>6</v>
       </c>
       <c r="C63" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D63" t="n">
         <v>7</v>
@@ -8211,7 +8208,7 @@
         <v>2024</v>
       </c>
       <c r="H63" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I63" t="n">
         <v>1</v>
@@ -8229,7 +8226,7 @@
         <v>6</v>
       </c>
       <c r="C64" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D64" t="n">
         <v>8</v>
@@ -8244,7 +8241,7 @@
         <v>2024</v>
       </c>
       <c r="H64" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I64" t="n">
         <v>1</v>
@@ -8262,7 +8259,7 @@
         <v>6</v>
       </c>
       <c r="C65" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D65" t="n">
         <v>9</v>
@@ -8277,7 +8274,7 @@
         <v>2024</v>
       </c>
       <c r="H65" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I65" t="n">
         <v>1</v>
@@ -8295,7 +8292,7 @@
         <v>6</v>
       </c>
       <c r="C66" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D66" t="n">
         <v>10</v>
@@ -8310,7 +8307,7 @@
         <v>2024</v>
       </c>
       <c r="H66" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I66" t="n">
         <v>1</v>
@@ -8328,7 +8325,7 @@
         <v>6</v>
       </c>
       <c r="C67" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D67" t="n">
         <v>11</v>
@@ -8343,7 +8340,7 @@
         <v>2024</v>
       </c>
       <c r="H67" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I67" t="n">
         <v>1</v>
@@ -8361,7 +8358,7 @@
         <v>7</v>
       </c>
       <c r="C68" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D68" t="n">
         <v>1</v>
@@ -8376,7 +8373,7 @@
         <v>2024</v>
       </c>
       <c r="H68" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I68" t="n">
         <v>1</v>
@@ -8394,7 +8391,7 @@
         <v>7</v>
       </c>
       <c r="C69" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D69" t="n">
         <v>2</v>
@@ -8409,7 +8406,7 @@
         <v>2024</v>
       </c>
       <c r="H69" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I69" t="n">
         <v>1</v>
@@ -8427,7 +8424,7 @@
         <v>7</v>
       </c>
       <c r="C70" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D70" t="n">
         <v>3</v>
@@ -8442,7 +8439,7 @@
         <v>2024</v>
       </c>
       <c r="H70" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I70" t="n">
         <v>1</v>
@@ -8460,7 +8457,7 @@
         <v>7</v>
       </c>
       <c r="C71" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D71" t="n">
         <v>4</v>
@@ -8475,7 +8472,7 @@
         <v>2024</v>
       </c>
       <c r="H71" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I71" t="n">
         <v>1</v>
@@ -8493,7 +8490,7 @@
         <v>7</v>
       </c>
       <c r="C72" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D72" t="n">
         <v>5</v>
@@ -8508,7 +8505,7 @@
         <v>2024</v>
       </c>
       <c r="H72" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I72" t="n">
         <v>1</v>
@@ -8526,7 +8523,7 @@
         <v>7</v>
       </c>
       <c r="C73" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D73" t="n">
         <v>6</v>
@@ -8541,7 +8538,7 @@
         <v>2024</v>
       </c>
       <c r="H73" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I73" t="n">
         <v>1</v>
@@ -8559,7 +8556,7 @@
         <v>7</v>
       </c>
       <c r="C74" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D74" t="n">
         <v>7</v>
@@ -8574,7 +8571,7 @@
         <v>2024</v>
       </c>
       <c r="H74" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I74" t="n">
         <v>1</v>
@@ -8592,7 +8589,7 @@
         <v>7</v>
       </c>
       <c r="C75" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D75" t="n">
         <v>8</v>
@@ -8607,7 +8604,7 @@
         <v>2024</v>
       </c>
       <c r="H75" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I75" t="n">
         <v>1</v>
@@ -8625,13 +8622,13 @@
         <v>7</v>
       </c>
       <c r="C76" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D76" t="n">
         <v>9</v>
       </c>
       <c r="E76" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F76" t="n">
         <v>2008</v>
@@ -8640,14 +8637,14 @@
         <v>2024</v>
       </c>
       <c r="H76" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I76" t="n">
         <v>1</v>
       </c>
       <c r="J76"/>
       <c r="K76" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="77">
@@ -8658,7 +8655,7 @@
         <v>7</v>
       </c>
       <c r="C77" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D77" t="n">
         <v>10</v>
@@ -8673,7 +8670,7 @@
         <v>2024</v>
       </c>
       <c r="H77" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I77" t="n">
         <v>1</v>
@@ -8691,7 +8688,7 @@
         <v>7</v>
       </c>
       <c r="C78" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D78" t="n">
         <v>11</v>
@@ -8706,7 +8703,7 @@
         <v>2024</v>
       </c>
       <c r="H78" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I78" t="n">
         <v>1</v>
@@ -8724,7 +8721,7 @@
         <v>8</v>
       </c>
       <c r="C79" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D79" t="n">
         <v>1</v>
@@ -8739,7 +8736,7 @@
         <v>2024</v>
       </c>
       <c r="H79" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I79" t="n">
         <v>1</v>
@@ -8757,7 +8754,7 @@
         <v>8</v>
       </c>
       <c r="C80" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D80" t="n">
         <v>2</v>
@@ -8772,7 +8769,7 @@
         <v>2024</v>
       </c>
       <c r="H80" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I80" t="n">
         <v>1</v>
@@ -8790,7 +8787,7 @@
         <v>8</v>
       </c>
       <c r="C81" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D81" t="n">
         <v>3</v>
@@ -8805,7 +8802,7 @@
         <v>2024</v>
       </c>
       <c r="H81" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I81" t="n">
         <v>1</v>
@@ -8823,13 +8820,13 @@
         <v>8</v>
       </c>
       <c r="C82" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D82" t="n">
         <v>4</v>
       </c>
       <c r="E82" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F82" t="n">
         <v>2008</v>
@@ -8838,14 +8835,14 @@
         <v>2024</v>
       </c>
       <c r="H82" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I82" t="n">
         <v>1</v>
       </c>
       <c r="J82"/>
       <c r="K82" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="83">
@@ -8856,7 +8853,7 @@
         <v>8</v>
       </c>
       <c r="C83" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D83" t="n">
         <v>5</v>
@@ -8871,7 +8868,7 @@
         <v>2024</v>
       </c>
       <c r="H83" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I83" t="n">
         <v>1</v>
@@ -8889,7 +8886,7 @@
         <v>8</v>
       </c>
       <c r="C84" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D84" t="n">
         <v>6</v>
@@ -8904,7 +8901,7 @@
         <v>2024</v>
       </c>
       <c r="H84" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I84" t="n">
         <v>1</v>
@@ -8922,7 +8919,7 @@
         <v>8</v>
       </c>
       <c r="C85" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D85" t="n">
         <v>7</v>
@@ -8937,7 +8934,7 @@
         <v>2024</v>
       </c>
       <c r="H85" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I85" t="n">
         <v>1</v>
@@ -8955,7 +8952,7 @@
         <v>8</v>
       </c>
       <c r="C86" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D86" t="n">
         <v>8</v>
@@ -8970,7 +8967,7 @@
         <v>2024</v>
       </c>
       <c r="H86" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I86" t="n">
         <v>1</v>
@@ -8988,13 +8985,13 @@
         <v>8</v>
       </c>
       <c r="C87" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D87" t="n">
         <v>9</v>
       </c>
       <c r="E87" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F87" t="n">
         <v>2008</v>
@@ -9003,14 +9000,14 @@
         <v>2024</v>
       </c>
       <c r="H87" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I87" t="n">
         <v>1</v>
       </c>
       <c r="J87"/>
       <c r="K87" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="88">
@@ -9021,7 +9018,7 @@
         <v>8</v>
       </c>
       <c r="C88" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D88" t="n">
         <v>10</v>
@@ -9036,7 +9033,7 @@
         <v>2024</v>
       </c>
       <c r="H88" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I88" t="n">
         <v>1</v>
@@ -9054,7 +9051,7 @@
         <v>8</v>
       </c>
       <c r="C89" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D89" t="n">
         <v>11</v>
@@ -9069,7 +9066,7 @@
         <v>2024</v>
       </c>
       <c r="H89" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I89" t="n">
         <v>1</v>
@@ -9087,7 +9084,7 @@
         <v>9</v>
       </c>
       <c r="C90" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D90" t="n">
         <v>1</v>
@@ -9102,7 +9099,7 @@
         <v>2024</v>
       </c>
       <c r="H90" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I90" t="n">
         <v>1</v>
@@ -9120,7 +9117,7 @@
         <v>9</v>
       </c>
       <c r="C91" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D91" t="n">
         <v>2</v>
@@ -9135,7 +9132,7 @@
         <v>2024</v>
       </c>
       <c r="H91" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I91" t="n">
         <v>1</v>
@@ -9153,7 +9150,7 @@
         <v>9</v>
       </c>
       <c r="C92" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D92" t="n">
         <v>3</v>
@@ -9168,7 +9165,7 @@
         <v>2024</v>
       </c>
       <c r="H92" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I92" t="n">
         <v>1</v>
@@ -9186,13 +9183,13 @@
         <v>9</v>
       </c>
       <c r="C93" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D93" t="n">
         <v>4</v>
       </c>
       <c r="E93" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F93" t="n">
         <v>2008</v>
@@ -9201,14 +9198,14 @@
         <v>2024</v>
       </c>
       <c r="H93" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I93" t="n">
         <v>1</v>
       </c>
       <c r="J93"/>
       <c r="K93" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="94">
@@ -9219,7 +9216,7 @@
         <v>9</v>
       </c>
       <c r="C94" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D94" t="n">
         <v>5</v>
@@ -9234,7 +9231,7 @@
         <v>2024</v>
       </c>
       <c r="H94" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I94" t="n">
         <v>1</v>
@@ -9252,7 +9249,7 @@
         <v>9</v>
       </c>
       <c r="C95" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D95" t="n">
         <v>6</v>
@@ -9267,7 +9264,7 @@
         <v>2024</v>
       </c>
       <c r="H95" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I95" t="n">
         <v>1</v>
@@ -9285,7 +9282,7 @@
         <v>9</v>
       </c>
       <c r="C96" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D96" t="n">
         <v>7</v>
@@ -9300,7 +9297,7 @@
         <v>2024</v>
       </c>
       <c r="H96" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I96" t="n">
         <v>1</v>
@@ -9318,7 +9315,7 @@
         <v>9</v>
       </c>
       <c r="C97" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D97" t="n">
         <v>8</v>
@@ -9333,7 +9330,7 @@
         <v>2024</v>
       </c>
       <c r="H97" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I97" t="n">
         <v>1</v>
@@ -9351,13 +9348,13 @@
         <v>9</v>
       </c>
       <c r="C98" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D98" t="n">
         <v>9</v>
       </c>
       <c r="E98" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F98" t="n">
         <v>2008</v>
@@ -9366,14 +9363,14 @@
         <v>2024</v>
       </c>
       <c r="H98" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I98" t="n">
         <v>1</v>
       </c>
       <c r="J98"/>
       <c r="K98" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="99">
@@ -9384,7 +9381,7 @@
         <v>9</v>
       </c>
       <c r="C99" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D99" t="n">
         <v>10</v>
@@ -9399,7 +9396,7 @@
         <v>2024</v>
       </c>
       <c r="H99" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I99" t="n">
         <v>1</v>
@@ -9417,7 +9414,7 @@
         <v>9</v>
       </c>
       <c r="C100" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D100" t="n">
         <v>11</v>
@@ -9432,7 +9429,7 @@
         <v>2024</v>
       </c>
       <c r="H100" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I100" t="n">
         <v>1</v>
@@ -9450,7 +9447,7 @@
         <v>10</v>
       </c>
       <c r="C101" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D101" t="n">
         <v>1</v>
@@ -9465,7 +9462,7 @@
         <v>2024</v>
       </c>
       <c r="H101" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I101" t="n">
         <v>1</v>
@@ -9483,7 +9480,7 @@
         <v>10</v>
       </c>
       <c r="C102" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D102" t="n">
         <v>2</v>
@@ -9498,7 +9495,7 @@
         <v>2024</v>
       </c>
       <c r="H102" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I102" t="n">
         <v>1</v>
@@ -9516,7 +9513,7 @@
         <v>10</v>
       </c>
       <c r="C103" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D103" t="n">
         <v>3</v>
@@ -9531,7 +9528,7 @@
         <v>2024</v>
       </c>
       <c r="H103" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I103" t="n">
         <v>1</v>
@@ -9549,13 +9546,13 @@
         <v>10</v>
       </c>
       <c r="C104" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D104" t="n">
         <v>4</v>
       </c>
       <c r="E104" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F104" t="n">
         <v>2008</v>
@@ -9564,14 +9561,14 @@
         <v>2024</v>
       </c>
       <c r="H104" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I104" t="n">
         <v>1</v>
       </c>
       <c r="J104"/>
       <c r="K104" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="105">
@@ -9582,7 +9579,7 @@
         <v>10</v>
       </c>
       <c r="C105" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D105" t="n">
         <v>5</v>
@@ -9597,7 +9594,7 @@
         <v>2024</v>
       </c>
       <c r="H105" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I105" t="n">
         <v>1</v>
@@ -9615,7 +9612,7 @@
         <v>10</v>
       </c>
       <c r="C106" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D106" t="n">
         <v>6</v>
@@ -9630,7 +9627,7 @@
         <v>2024</v>
       </c>
       <c r="H106" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I106" t="n">
         <v>1</v>
@@ -9648,7 +9645,7 @@
         <v>10</v>
       </c>
       <c r="C107" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D107" t="n">
         <v>7</v>
@@ -9663,7 +9660,7 @@
         <v>2024</v>
       </c>
       <c r="H107" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I107" t="n">
         <v>1</v>
@@ -9681,7 +9678,7 @@
         <v>10</v>
       </c>
       <c r="C108" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D108" t="n">
         <v>8</v>
@@ -9696,7 +9693,7 @@
         <v>2024</v>
       </c>
       <c r="H108" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I108" t="n">
         <v>1</v>
@@ -9714,7 +9711,7 @@
         <v>10</v>
       </c>
       <c r="C109" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D109" t="n">
         <v>9</v>
@@ -9729,7 +9726,7 @@
         <v>2024</v>
       </c>
       <c r="H109" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I109" t="n">
         <v>1</v>
@@ -9747,7 +9744,7 @@
         <v>10</v>
       </c>
       <c r="C110" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D110" t="n">
         <v>10</v>
@@ -9762,7 +9759,7 @@
         <v>2024</v>
       </c>
       <c r="H110" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I110" t="n">
         <v>1</v>
@@ -9780,7 +9777,7 @@
         <v>10</v>
       </c>
       <c r="C111" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D111" t="n">
         <v>11</v>
@@ -9795,7 +9792,7 @@
         <v>2024</v>
       </c>
       <c r="H111" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I111" t="n">
         <v>1</v>
@@ -9807,13 +9804,13 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B112" t="n">
         <v>11</v>
       </c>
       <c r="C112" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D112" t="n">
         <v>1</v>
@@ -9828,7 +9825,7 @@
         <v>2024</v>
       </c>
       <c r="H112" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I112" t="n">
         <v>1</v>
@@ -9840,13 +9837,13 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B113" t="n">
         <v>11</v>
       </c>
       <c r="C113" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D113" t="n">
         <v>2</v>
@@ -9861,7 +9858,7 @@
         <v>2024</v>
       </c>
       <c r="H113" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I113" t="n">
         <v>1</v>
@@ -9873,13 +9870,13 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B114" t="n">
         <v>11</v>
       </c>
       <c r="C114" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D114" t="n">
         <v>3</v>
@@ -9894,7 +9891,7 @@
         <v>2024</v>
       </c>
       <c r="H114" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I114" t="n">
         <v>1</v>
@@ -9906,13 +9903,13 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B115" t="n">
         <v>11</v>
       </c>
       <c r="C115" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D115" t="n">
         <v>4</v>
@@ -9927,7 +9924,7 @@
         <v>2024</v>
       </c>
       <c r="H115" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I115" t="n">
         <v>1</v>
@@ -9939,13 +9936,13 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B116" t="n">
         <v>11</v>
       </c>
       <c r="C116" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D116" t="n">
         <v>5</v>
@@ -9960,7 +9957,7 @@
         <v>2024</v>
       </c>
       <c r="H116" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I116" t="n">
         <v>1</v>
@@ -9972,13 +9969,13 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B117" t="n">
         <v>11</v>
       </c>
       <c r="C117" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D117" t="n">
         <v>6</v>
@@ -9993,7 +9990,7 @@
         <v>2024</v>
       </c>
       <c r="H117" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I117" t="n">
         <v>1</v>
@@ -10005,13 +10002,13 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B118" t="n">
         <v>11</v>
       </c>
       <c r="C118" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D118" t="n">
         <v>7</v>
@@ -10026,7 +10023,7 @@
         <v>2024</v>
       </c>
       <c r="H118" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I118" t="n">
         <v>1</v>
@@ -10038,13 +10035,13 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B119" t="n">
         <v>11</v>
       </c>
       <c r="C119" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D119" t="n">
         <v>8</v>
@@ -10059,7 +10056,7 @@
         <v>2024</v>
       </c>
       <c r="H119" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I119" t="n">
         <v>1</v>
@@ -10071,13 +10068,13 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B120" t="n">
         <v>11</v>
       </c>
       <c r="C120" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D120" t="n">
         <v>9</v>
@@ -10092,7 +10089,7 @@
         <v>2024</v>
       </c>
       <c r="H120" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I120" t="n">
         <v>1</v>
@@ -10104,13 +10101,13 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B121" t="n">
         <v>11</v>
       </c>
       <c r="C121" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D121" t="n">
         <v>10</v>
@@ -10125,7 +10122,7 @@
         <v>2024</v>
       </c>
       <c r="H121" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I121" t="n">
         <v>1</v>
@@ -10137,13 +10134,13 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B122" t="n">
         <v>11</v>
       </c>
       <c r="C122" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D122" t="n">
         <v>11</v>
@@ -10158,7 +10155,7 @@
         <v>2024</v>
       </c>
       <c r="H122" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I122" t="n">
         <v>1</v>
@@ -10170,13 +10167,13 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B123" t="n">
         <v>12.1</v>
       </c>
       <c r="C123" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D123" t="n">
         <v>1</v>
@@ -10191,7 +10188,7 @@
         <v>2024</v>
       </c>
       <c r="H123" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I123" t="n">
         <v>1</v>
@@ -10203,13 +10200,13 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B124" t="n">
         <v>12.1</v>
       </c>
       <c r="C124" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D124" t="n">
         <v>2</v>
@@ -10224,7 +10221,7 @@
         <v>2024</v>
       </c>
       <c r="H124" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I124" t="n">
         <v>1</v>
@@ -10236,13 +10233,13 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B125" t="n">
         <v>12.1</v>
       </c>
       <c r="C125" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D125" t="n">
         <v>3</v>
@@ -10257,7 +10254,7 @@
         <v>2024</v>
       </c>
       <c r="H125" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I125" t="n">
         <v>1</v>
@@ -10269,13 +10266,13 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B126" t="n">
         <v>12.1</v>
       </c>
       <c r="C126" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D126" t="n">
         <v>4</v>
@@ -10290,7 +10287,7 @@
         <v>2024</v>
       </c>
       <c r="H126" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I126" t="n">
         <v>1</v>
@@ -10302,13 +10299,13 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B127" t="n">
         <v>12.1</v>
       </c>
       <c r="C127" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D127" t="n">
         <v>5</v>
@@ -10323,7 +10320,7 @@
         <v>2024</v>
       </c>
       <c r="H127" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I127" t="n">
         <v>1</v>
@@ -10335,13 +10332,13 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B128" t="n">
         <v>12.1</v>
       </c>
       <c r="C128" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D128" t="n">
         <v>6</v>
@@ -10356,7 +10353,7 @@
         <v>2024</v>
       </c>
       <c r="H128" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I128" t="n">
         <v>1</v>
@@ -10368,13 +10365,13 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B129" t="n">
         <v>12.1</v>
       </c>
       <c r="C129" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D129" t="n">
         <v>7</v>
@@ -10389,7 +10386,7 @@
         <v>2024</v>
       </c>
       <c r="H129" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I129" t="n">
         <v>1</v>
@@ -10401,13 +10398,13 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B130" t="n">
         <v>12.1</v>
       </c>
       <c r="C130" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D130" t="n">
         <v>8</v>
@@ -10422,7 +10419,7 @@
         <v>2024</v>
       </c>
       <c r="H130" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I130" t="n">
         <v>1</v>
@@ -10434,13 +10431,13 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B131" t="n">
         <v>12.1</v>
       </c>
       <c r="C131" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D131" t="n">
         <v>9</v>
@@ -10455,7 +10452,7 @@
         <v>2024</v>
       </c>
       <c r="H131" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I131" t="n">
         <v>1</v>
@@ -10467,13 +10464,13 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B132" t="n">
         <v>12.1</v>
       </c>
       <c r="C132" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D132" t="n">
         <v>10</v>
@@ -10488,7 +10485,7 @@
         <v>2024</v>
       </c>
       <c r="H132" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I132" t="n">
         <v>1</v>
@@ -10500,13 +10497,13 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B133" t="n">
         <v>12.1</v>
       </c>
       <c r="C133" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D133" t="n">
         <v>11</v>
@@ -10521,7 +10518,7 @@
         <v>2024</v>
       </c>
       <c r="H133" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I133" t="n">
         <v>1</v>

--- a/Outcome/Publish/figure_data/fig3.xlsx
+++ b/Outcome/Publish/figure_data/fig3.xlsx
@@ -6370,7 +6370,7 @@
         <v>30</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6"/>
       <c r="K6" t="s">
@@ -6403,7 +6403,7 @@
         <v>30</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7"/>
       <c r="K7" t="s">
@@ -6725,7 +6725,7 @@
         <v>30</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17"/>
       <c r="K17" t="s">
@@ -6758,7 +6758,7 @@
         <v>30</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18"/>
       <c r="K18" t="s">
@@ -8637,7 +8637,7 @@
         <v>2024</v>
       </c>
       <c r="H76" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I76" t="n">
         <v>1</v>
@@ -8835,7 +8835,7 @@
         <v>2024</v>
       </c>
       <c r="H82" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I82" t="n">
         <v>1</v>
@@ -9000,7 +9000,7 @@
         <v>2024</v>
       </c>
       <c r="H87" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I87" t="n">
         <v>1</v>
@@ -9198,7 +9198,7 @@
         <v>2024</v>
       </c>
       <c r="H93" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I93" t="n">
         <v>1</v>
@@ -9363,7 +9363,7 @@
         <v>2024</v>
       </c>
       <c r="H98" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I98" t="n">
         <v>1</v>
@@ -9561,7 +9561,7 @@
         <v>2024</v>
       </c>
       <c r="H104" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I104" t="n">
         <v>1</v>

--- a/Outcome/Publish/figure_data/fig3.xlsx
+++ b/Outcome/Publish/figure_data/fig3.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t xml:space="preserve">AgeGroup</t>
   </si>
@@ -56,7 +56,19 @@
     <t xml:space="preserve">10-14</t>
   </si>
   <si>
-    <t xml:space="preserve">15+</t>
+    <t xml:space="preserve">15-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40-59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60+</t>
   </si>
   <si>
     <t xml:space="preserve">Year_group</t>
@@ -65,19 +77,7 @@
     <t xml:space="preserve">Year_mark</t>
   </si>
   <si>
-    <t xml:space="preserve">YearStart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YearEnd</t>
-  </si>
-  <si>
     <t xml:space="preserve">Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forecasting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Note</t>
   </si>
   <si>
     <t xml:space="preserve">Outcome_Fill</t>
@@ -125,10 +125,13 @@
     <t xml:space="preserve">Diphtheria</t>
   </si>
   <si>
-    <t xml:space="preserve">Melioidosis</t>
+    <t xml:space="preserve">Encephalitis</t>
   </si>
   <si>
     <t xml:space="preserve">Leptospirosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melioidosis</t>
   </si>
 </sst>
 </file>
@@ -482,7 +485,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>1247891</v>
+        <v>1257443.09356982</v>
       </c>
     </row>
     <row r="3">
@@ -496,7 +499,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>671957</v>
+        <v>653657.716757474</v>
       </c>
     </row>
     <row r="4">
@@ -510,7 +513,7 @@
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>790093</v>
+        <v>778335.599275723</v>
       </c>
     </row>
     <row r="5">
@@ -524,7 +527,7 @@
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>209354</v>
+        <v>197386.92128657</v>
       </c>
     </row>
     <row r="6">
@@ -538,7 +541,7 @@
         <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>230254</v>
+        <v>212736.999401967</v>
       </c>
     </row>
     <row r="7">
@@ -552,7 +555,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>188283</v>
+        <v>207210.406276195</v>
       </c>
     </row>
     <row r="8">
@@ -566,7 +569,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>659472</v>
+        <v>673512.419055442</v>
       </c>
     </row>
     <row r="9">
@@ -580,7 +583,7 @@
         <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>188810</v>
+        <v>195085.354133745</v>
       </c>
     </row>
     <row r="10">
@@ -594,7 +597,7 @@
         <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>184338</v>
+        <v>193350.729009513</v>
       </c>
     </row>
     <row r="11">
@@ -608,7 +611,7 @@
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>194713</v>
+        <v>216915.906481217</v>
       </c>
     </row>
     <row r="12">
@@ -622,7 +625,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>83368</v>
+        <v>85546.1079870612</v>
       </c>
     </row>
     <row r="13">
@@ -636,7 +639,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>502476</v>
+        <v>506614.23767102</v>
       </c>
     </row>
     <row r="14">
@@ -650,7 +653,7 @@
         <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>314137</v>
+        <v>316456.043334976</v>
       </c>
     </row>
     <row r="15">
@@ -664,7 +667,7 @@
         <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>148282</v>
+        <v>150953.40760811</v>
       </c>
     </row>
     <row r="16">
@@ -678,7 +681,7 @@
         <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>93190</v>
+        <v>94047.6998937327</v>
       </c>
     </row>
     <row r="17">
@@ -692,7 +695,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>2566009</v>
+        <v>52052.7920691823</v>
       </c>
     </row>
     <row r="18">
@@ -706,7 +709,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>2033031</v>
+        <v>247009.701346544</v>
       </c>
     </row>
     <row r="19">
@@ -720,7 +723,7 @@
         <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>872018</v>
+        <v>228775.52818226</v>
       </c>
     </row>
     <row r="20">
@@ -734,7 +737,7 @@
         <v>8</v>
       </c>
       <c r="D20" t="n">
-        <v>316525</v>
+        <v>80702.3493339277</v>
       </c>
     </row>
     <row r="21">
@@ -748,7 +751,217 @@
         <v>9</v>
       </c>
       <c r="D21" t="n">
-        <v>1215171</v>
+        <v>131606.237402122</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>291134.379172665</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" t="n">
+        <v>929183.598146722</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" t="n">
+        <v>441897.75352447</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" t="n">
+        <v>5</v>
+      </c>
+      <c r="C25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" t="n">
+        <v>183796.656320851</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" t="n">
+        <v>552840.334759543</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="n">
+        <v>6</v>
+      </c>
+      <c r="C27" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27" t="n">
+        <v>627996.515626952</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="n">
+        <v>6</v>
+      </c>
+      <c r="C28" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28" t="n">
+        <v>574225.006020735</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="n">
+        <v>6</v>
+      </c>
+      <c r="C29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" t="n">
+        <v>153375.300212957</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="n">
+        <v>6</v>
+      </c>
+      <c r="C30" t="s">
+        <v>16</v>
+      </c>
+      <c r="D30" t="n">
+        <v>62047.7405690359</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="n">
+        <v>6</v>
+      </c>
+      <c r="C31" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" t="n">
+        <v>339761.998668834</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32" t="n">
+        <v>7</v>
+      </c>
+      <c r="C32" t="s">
+        <v>5</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1610710.70529812</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33" t="n">
+        <v>7</v>
+      </c>
+      <c r="C33" t="s">
+        <v>6</v>
+      </c>
+      <c r="D33" t="n">
+        <v>282733.321002064</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34" t="n">
+        <v>7</v>
+      </c>
+      <c r="C34" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" t="n">
+        <v>48021.1745600166</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>17</v>
+      </c>
+      <c r="B35" t="n">
+        <v>7</v>
+      </c>
+      <c r="C35" t="s">
+        <v>16</v>
+      </c>
+      <c r="D35" t="n">
+        <v>24796.6774320023</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" t="n">
+        <v>7</v>
+      </c>
+      <c r="C36" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" t="n">
+        <v>157837.588608428</v>
       </c>
     </row>
   </sheetData>
@@ -770,30 +983,18 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -813,20 +1014,10 @@
       <c r="E2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G2" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2"/>
-      <c r="K2" t="s">
+      <c r="F2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -846,20 +1037,10 @@
       <c r="E3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3"/>
-      <c r="K3" t="s">
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -879,20 +1060,10 @@
       <c r="E4" t="s">
         <v>5</v>
       </c>
-      <c r="F4" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4"/>
-      <c r="K4" t="s">
+      <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" t="s">
         <v>5</v>
       </c>
     </row>
@@ -912,20 +1083,10 @@
       <c r="E5" t="s">
         <v>5</v>
       </c>
-      <c r="F5" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5"/>
-      <c r="K5" t="s">
+      <c r="F5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -945,20 +1106,10 @@
       <c r="E6" t="s">
         <v>5</v>
       </c>
-      <c r="F6" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6"/>
-      <c r="K6" t="s">
+      <c r="F6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" t="s">
         <v>5</v>
       </c>
     </row>
@@ -978,20 +1129,10 @@
       <c r="E7" t="s">
         <v>5</v>
       </c>
-      <c r="F7" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7"/>
-      <c r="K7" t="s">
+      <c r="F7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1011,20 +1152,10 @@
       <c r="E8" t="s">
         <v>5</v>
       </c>
-      <c r="F8" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8"/>
-      <c r="K8" t="s">
+      <c r="F8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1042,23 +1173,13 @@
         <v>8</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H9" t="s">
-        <v>23</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9"/>
-      <c r="K9" t="s">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="F9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -1077,29 +1198,19 @@
       <c r="E10" t="s">
         <v>6</v>
       </c>
-      <c r="F10" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10"/>
-      <c r="K10" t="s">
+      <c r="F10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="s">
         <v>22</v>
@@ -1108,31 +1219,21 @@
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11"/>
-      <c r="K11" t="s">
-        <v>8</v>
+        <v>11</v>
+      </c>
+      <c r="F11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" t="s">
         <v>24</v>
@@ -1141,31 +1242,21 @@
         <v>2</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G12" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H12" t="s">
-        <v>23</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12"/>
-      <c r="K12" t="s">
-        <v>8</v>
+        <v>11</v>
+      </c>
+      <c r="F12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" t="s">
         <v>25</v>
@@ -1176,29 +1267,19 @@
       <c r="E13" t="s">
         <v>11</v>
       </c>
-      <c r="F13" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H13" t="s">
+      <c r="F13" t="s">
         <v>32</v>
       </c>
-      <c r="I13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13"/>
-      <c r="K13" t="s">
+      <c r="G13" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" t="s">
         <v>26</v>
@@ -1207,31 +1288,21 @@
         <v>4</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H14" t="s">
-        <v>23</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14"/>
-      <c r="K14" t="s">
-        <v>8</v>
+        <v>11</v>
+      </c>
+      <c r="F14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15" t="s">
         <v>27</v>
@@ -1242,29 +1313,19 @@
       <c r="E15" t="s">
         <v>6</v>
       </c>
-      <c r="F15" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H15" t="s">
-        <v>23</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15"/>
-      <c r="K15" t="s">
+      <c r="F15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="s">
         <v>28</v>
@@ -1275,29 +1336,19 @@
       <c r="E16" t="s">
         <v>6</v>
       </c>
-      <c r="F16" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H16" t="s">
-        <v>23</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16"/>
-      <c r="K16" t="s">
+      <c r="F16" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="s">
         <v>29</v>
@@ -1306,31 +1357,21 @@
         <v>7</v>
       </c>
       <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17"/>
-      <c r="K17" t="s">
-        <v>6</v>
+        <v>11</v>
+      </c>
+      <c r="F17" t="s">
+        <v>32</v>
+      </c>
+      <c r="G17" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="s">
         <v>30</v>
@@ -1341,29 +1382,19 @@
       <c r="E18" t="s">
         <v>6</v>
       </c>
-      <c r="F18" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G18" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H18" t="s">
-        <v>23</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18"/>
-      <c r="K18" t="s">
+      <c r="F18" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" t="s">
         <v>31</v>
@@ -1374,29 +1405,19 @@
       <c r="E19" t="s">
         <v>6</v>
       </c>
-      <c r="F19" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G19" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H19" t="s">
-        <v>23</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19"/>
-      <c r="K19" t="s">
+      <c r="F19" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C20" t="s">
         <v>22</v>
@@ -1407,29 +1428,19 @@
       <c r="E20" t="s">
         <v>11</v>
       </c>
-      <c r="F20" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G20" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H20" t="s">
+      <c r="F20" t="s">
         <v>32</v>
       </c>
-      <c r="I20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20"/>
-      <c r="K20" t="s">
+      <c r="G20" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C21" t="s">
         <v>24</v>
@@ -1440,29 +1451,19 @@
       <c r="E21" t="s">
         <v>11</v>
       </c>
-      <c r="F21" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G21" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H21" t="s">
+      <c r="F21" t="s">
         <v>32</v>
       </c>
-      <c r="I21" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21"/>
-      <c r="K21" t="s">
+      <c r="G21" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C22" t="s">
         <v>25</v>
@@ -1473,29 +1474,19 @@
       <c r="E22" t="s">
         <v>11</v>
       </c>
-      <c r="F22" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G22" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H22" t="s">
+      <c r="F22" t="s">
         <v>32</v>
       </c>
-      <c r="I22" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22"/>
-      <c r="K22" t="s">
+      <c r="G22" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C23" t="s">
         <v>26</v>
@@ -1506,29 +1497,19 @@
       <c r="E23" t="s">
         <v>11</v>
       </c>
-      <c r="F23" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G23" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H23" t="s">
+      <c r="F23" t="s">
         <v>32</v>
       </c>
-      <c r="I23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23"/>
-      <c r="K23" t="s">
+      <c r="G23" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C24" t="s">
         <v>27</v>
@@ -1539,29 +1520,19 @@
       <c r="E24" t="s">
         <v>6</v>
       </c>
-      <c r="F24" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G24" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H24" t="s">
-        <v>23</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24"/>
-      <c r="K24" t="s">
+      <c r="F24" t="s">
+        <v>23</v>
+      </c>
+      <c r="G24" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C25" t="s">
         <v>28</v>
@@ -1570,31 +1541,21 @@
         <v>6</v>
       </c>
       <c r="E25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G25" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H25" t="s">
-        <v>23</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25"/>
-      <c r="K25" t="s">
-        <v>6</v>
+        <v>11</v>
+      </c>
+      <c r="F25" t="s">
+        <v>32</v>
+      </c>
+      <c r="G25" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C26" t="s">
         <v>29</v>
@@ -1605,29 +1566,19 @@
       <c r="E26" t="s">
         <v>11</v>
       </c>
-      <c r="F26" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G26" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H26" t="s">
+      <c r="F26" t="s">
         <v>32</v>
       </c>
-      <c r="I26" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26"/>
-      <c r="K26" t="s">
+      <c r="G26" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C27" t="s">
         <v>30</v>
@@ -1638,29 +1589,19 @@
       <c r="E27" t="s">
         <v>6</v>
       </c>
-      <c r="F27" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G27" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H27" t="s">
-        <v>23</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27"/>
-      <c r="K27" t="s">
+      <c r="F27" t="s">
+        <v>23</v>
+      </c>
+      <c r="G27" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C28" t="s">
         <v>31</v>
@@ -1671,29 +1612,19 @@
       <c r="E28" t="s">
         <v>6</v>
       </c>
-      <c r="F28" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G28" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H28" t="s">
-        <v>23</v>
-      </c>
-      <c r="I28" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28"/>
-      <c r="K28" t="s">
+      <c r="F28" t="s">
+        <v>23</v>
+      </c>
+      <c r="G28" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C29" t="s">
         <v>22</v>
@@ -1702,31 +1633,21 @@
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G29" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H29" t="s">
-        <v>23</v>
-      </c>
-      <c r="I29" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29"/>
-      <c r="K29" t="s">
-        <v>5</v>
+        <v>11</v>
+      </c>
+      <c r="F29" t="s">
+        <v>32</v>
+      </c>
+      <c r="G29" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C30" t="s">
         <v>24</v>
@@ -1735,31 +1656,21 @@
         <v>2</v>
       </c>
       <c r="E30" t="s">
-        <v>5</v>
-      </c>
-      <c r="F30" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G30" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H30" t="s">
-        <v>23</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30"/>
-      <c r="K30" t="s">
-        <v>5</v>
+        <v>11</v>
+      </c>
+      <c r="F30" t="s">
+        <v>32</v>
+      </c>
+      <c r="G30" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C31" t="s">
         <v>25</v>
@@ -1768,31 +1679,21 @@
         <v>3</v>
       </c>
       <c r="E31" t="s">
-        <v>5</v>
-      </c>
-      <c r="F31" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G31" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H31" t="s">
-        <v>23</v>
-      </c>
-      <c r="I31" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31"/>
-      <c r="K31" t="s">
-        <v>5</v>
+        <v>11</v>
+      </c>
+      <c r="F31" t="s">
+        <v>32</v>
+      </c>
+      <c r="G31" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C32" t="s">
         <v>26</v>
@@ -1801,31 +1702,21 @@
         <v>4</v>
       </c>
       <c r="E32" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G32" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H32" t="s">
-        <v>23</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32"/>
-      <c r="K32" t="s">
-        <v>5</v>
+        <v>11</v>
+      </c>
+      <c r="F32" t="s">
+        <v>32</v>
+      </c>
+      <c r="G32" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C33" t="s">
         <v>27</v>
@@ -1834,31 +1725,21 @@
         <v>5</v>
       </c>
       <c r="E33" t="s">
-        <v>5</v>
-      </c>
-      <c r="F33" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G33" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H33" t="s">
-        <v>23</v>
-      </c>
-      <c r="I33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33"/>
-      <c r="K33" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="F33" t="s">
+        <v>23</v>
+      </c>
+      <c r="G33" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C34" t="s">
         <v>28</v>
@@ -1869,29 +1750,19 @@
       <c r="E34" t="s">
         <v>6</v>
       </c>
-      <c r="F34" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G34" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H34" t="s">
-        <v>23</v>
-      </c>
-      <c r="I34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34"/>
-      <c r="K34" t="s">
+      <c r="F34" t="s">
+        <v>23</v>
+      </c>
+      <c r="G34" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C35" t="s">
         <v>29</v>
@@ -1902,29 +1773,19 @@
       <c r="E35" t="s">
         <v>5</v>
       </c>
-      <c r="F35" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G35" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H35" t="s">
-        <v>23</v>
-      </c>
-      <c r="I35" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35"/>
-      <c r="K35" t="s">
+      <c r="F35" t="s">
+        <v>23</v>
+      </c>
+      <c r="G35" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C36" t="s">
         <v>30</v>
@@ -1935,29 +1796,19 @@
       <c r="E36" t="s">
         <v>6</v>
       </c>
-      <c r="F36" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G36" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H36" t="s">
-        <v>23</v>
-      </c>
-      <c r="I36" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36"/>
-      <c r="K36" t="s">
+      <c r="F36" t="s">
+        <v>23</v>
+      </c>
+      <c r="G36" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C37" t="s">
         <v>31</v>
@@ -1968,29 +1819,19 @@
       <c r="E37" t="s">
         <v>6</v>
       </c>
-      <c r="F37" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G37" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H37" t="s">
-        <v>23</v>
-      </c>
-      <c r="I37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37"/>
-      <c r="K37" t="s">
+      <c r="F37" t="s">
+        <v>23</v>
+      </c>
+      <c r="G37" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B38" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="C38" t="s">
         <v>22</v>
@@ -2001,29 +1842,19 @@
       <c r="E38" t="s">
         <v>5</v>
       </c>
-      <c r="F38" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G38" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H38" t="s">
-        <v>23</v>
-      </c>
-      <c r="I38" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38"/>
-      <c r="K38" t="s">
+      <c r="F38" t="s">
+        <v>23</v>
+      </c>
+      <c r="G38" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B39" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="C39" t="s">
         <v>24</v>
@@ -2034,29 +1865,19 @@
       <c r="E39" t="s">
         <v>5</v>
       </c>
-      <c r="F39" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G39" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H39" t="s">
-        <v>23</v>
-      </c>
-      <c r="I39" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39"/>
-      <c r="K39" t="s">
+      <c r="F39" t="s">
+        <v>23</v>
+      </c>
+      <c r="G39" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B40" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="C40" t="s">
         <v>25</v>
@@ -2067,29 +1888,19 @@
       <c r="E40" t="s">
         <v>5</v>
       </c>
-      <c r="F40" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G40" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H40" t="s">
-        <v>23</v>
-      </c>
-      <c r="I40" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40"/>
-      <c r="K40" t="s">
+      <c r="F40" t="s">
+        <v>23</v>
+      </c>
+      <c r="G40" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B41" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="C41" t="s">
         <v>26</v>
@@ -2100,29 +1911,19 @@
       <c r="E41" t="s">
         <v>5</v>
       </c>
-      <c r="F41" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G41" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H41" t="s">
-        <v>23</v>
-      </c>
-      <c r="I41" t="n">
-        <v>1</v>
-      </c>
-      <c r="J41"/>
-      <c r="K41" t="s">
+      <c r="F41" t="s">
+        <v>23</v>
+      </c>
+      <c r="G41" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B42" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="C42" t="s">
         <v>27</v>
@@ -2133,29 +1934,19 @@
       <c r="E42" t="s">
         <v>5</v>
       </c>
-      <c r="F42" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G42" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H42" t="s">
-        <v>23</v>
-      </c>
-      <c r="I42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J42"/>
-      <c r="K42" t="s">
+      <c r="F42" t="s">
+        <v>23</v>
+      </c>
+      <c r="G42" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B43" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="C43" t="s">
         <v>28</v>
@@ -2164,31 +1955,21 @@
         <v>6</v>
       </c>
       <c r="E43" t="s">
-        <v>6</v>
-      </c>
-      <c r="F43" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G43" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H43" t="s">
-        <v>23</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43"/>
-      <c r="K43" t="s">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="F43" t="s">
+        <v>23</v>
+      </c>
+      <c r="G43" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B44" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="C44" t="s">
         <v>29</v>
@@ -2199,29 +1980,19 @@
       <c r="E44" t="s">
         <v>5</v>
       </c>
-      <c r="F44" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G44" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H44" t="s">
-        <v>23</v>
-      </c>
-      <c r="I44" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44"/>
-      <c r="K44" t="s">
+      <c r="F44" t="s">
+        <v>23</v>
+      </c>
+      <c r="G44" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B45" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="C45" t="s">
         <v>30</v>
@@ -2230,31 +2001,21 @@
         <v>8</v>
       </c>
       <c r="E45" t="s">
-        <v>6</v>
-      </c>
-      <c r="F45" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G45" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H45" t="s">
-        <v>23</v>
-      </c>
-      <c r="I45" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45"/>
-      <c r="K45" t="s">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="F45" t="s">
+        <v>23</v>
+      </c>
+      <c r="G45" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B46" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="C46" t="s">
         <v>31</v>
@@ -2265,20 +2026,631 @@
       <c r="E46" t="s">
         <v>6</v>
       </c>
-      <c r="F46" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G46" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H46" t="s">
-        <v>23</v>
-      </c>
-      <c r="I46" t="n">
+      <c r="F46" t="s">
+        <v>23</v>
+      </c>
+      <c r="G46" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>10</v>
+      </c>
+      <c r="B47" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" t="s">
+        <v>22</v>
+      </c>
+      <c r="D47" t="n">
         <v>1</v>
       </c>
-      <c r="J46"/>
-      <c r="K46" t="s">
+      <c r="E47" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" t="s">
+        <v>23</v>
+      </c>
+      <c r="G47" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>10</v>
+      </c>
+      <c r="B48" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" t="s">
+        <v>24</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2</v>
+      </c>
+      <c r="E48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" t="s">
+        <v>23</v>
+      </c>
+      <c r="G48" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>10</v>
+      </c>
+      <c r="B49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C49" t="s">
+        <v>25</v>
+      </c>
+      <c r="D49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" t="s">
+        <v>11</v>
+      </c>
+      <c r="F49" t="s">
+        <v>32</v>
+      </c>
+      <c r="G49" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>10</v>
+      </c>
+      <c r="B50" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" t="s">
+        <v>26</v>
+      </c>
+      <c r="D50" t="n">
+        <v>4</v>
+      </c>
+      <c r="E50" t="s">
+        <v>8</v>
+      </c>
+      <c r="F50" t="s">
+        <v>23</v>
+      </c>
+      <c r="G50" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>10</v>
+      </c>
+      <c r="B51" t="n">
+        <v>2</v>
+      </c>
+      <c r="C51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D51" t="n">
+        <v>5</v>
+      </c>
+      <c r="E51" t="s">
+        <v>6</v>
+      </c>
+      <c r="F51" t="s">
+        <v>23</v>
+      </c>
+      <c r="G51" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>10</v>
+      </c>
+      <c r="B52" t="n">
+        <v>2</v>
+      </c>
+      <c r="C52" t="s">
+        <v>28</v>
+      </c>
+      <c r="D52" t="n">
+        <v>6</v>
+      </c>
+      <c r="E52" t="s">
+        <v>6</v>
+      </c>
+      <c r="F52" t="s">
+        <v>23</v>
+      </c>
+      <c r="G52" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>10</v>
+      </c>
+      <c r="B53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C53" t="s">
+        <v>29</v>
+      </c>
+      <c r="D53" t="n">
+        <v>7</v>
+      </c>
+      <c r="E53" t="s">
+        <v>6</v>
+      </c>
+      <c r="F53" t="s">
+        <v>23</v>
+      </c>
+      <c r="G53" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>10</v>
+      </c>
+      <c r="B54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C54" t="s">
+        <v>30</v>
+      </c>
+      <c r="D54" t="n">
+        <v>8</v>
+      </c>
+      <c r="E54" t="s">
+        <v>6</v>
+      </c>
+      <c r="F54" t="s">
+        <v>23</v>
+      </c>
+      <c r="G54" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>10</v>
+      </c>
+      <c r="B55" t="n">
+        <v>2</v>
+      </c>
+      <c r="C55" t="s">
+        <v>31</v>
+      </c>
+      <c r="D55" t="n">
+        <v>9</v>
+      </c>
+      <c r="E55" t="s">
+        <v>6</v>
+      </c>
+      <c r="F55" t="s">
+        <v>23</v>
+      </c>
+      <c r="G55" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>17</v>
+      </c>
+      <c r="B56" t="n">
+        <v>7</v>
+      </c>
+      <c r="C56" t="s">
+        <v>22</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="s">
+        <v>5</v>
+      </c>
+      <c r="F56" t="s">
+        <v>23</v>
+      </c>
+      <c r="G56" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>17</v>
+      </c>
+      <c r="B57" t="n">
+        <v>7</v>
+      </c>
+      <c r="C57" t="s">
+        <v>24</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2</v>
+      </c>
+      <c r="E57" t="s">
+        <v>5</v>
+      </c>
+      <c r="F57" t="s">
+        <v>23</v>
+      </c>
+      <c r="G57" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>17</v>
+      </c>
+      <c r="B58" t="n">
+        <v>7</v>
+      </c>
+      <c r="C58" t="s">
+        <v>25</v>
+      </c>
+      <c r="D58" t="n">
+        <v>3</v>
+      </c>
+      <c r="E58" t="s">
+        <v>5</v>
+      </c>
+      <c r="F58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G58" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>17</v>
+      </c>
+      <c r="B59" t="n">
+        <v>7</v>
+      </c>
+      <c r="C59" t="s">
+        <v>26</v>
+      </c>
+      <c r="D59" t="n">
+        <v>4</v>
+      </c>
+      <c r="E59" t="s">
+        <v>5</v>
+      </c>
+      <c r="F59" t="s">
+        <v>23</v>
+      </c>
+      <c r="G59" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>17</v>
+      </c>
+      <c r="B60" t="n">
+        <v>7</v>
+      </c>
+      <c r="C60" t="s">
+        <v>27</v>
+      </c>
+      <c r="D60" t="n">
+        <v>5</v>
+      </c>
+      <c r="E60" t="s">
+        <v>5</v>
+      </c>
+      <c r="F60" t="s">
+        <v>23</v>
+      </c>
+      <c r="G60" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>17</v>
+      </c>
+      <c r="B61" t="n">
+        <v>7</v>
+      </c>
+      <c r="C61" t="s">
+        <v>28</v>
+      </c>
+      <c r="D61" t="n">
+        <v>6</v>
+      </c>
+      <c r="E61" t="s">
+        <v>5</v>
+      </c>
+      <c r="F61" t="s">
+        <v>23</v>
+      </c>
+      <c r="G61" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>17</v>
+      </c>
+      <c r="B62" t="n">
+        <v>7</v>
+      </c>
+      <c r="C62" t="s">
+        <v>29</v>
+      </c>
+      <c r="D62" t="n">
+        <v>7</v>
+      </c>
+      <c r="E62" t="s">
+        <v>5</v>
+      </c>
+      <c r="F62" t="s">
+        <v>23</v>
+      </c>
+      <c r="G62" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>17</v>
+      </c>
+      <c r="B63" t="n">
+        <v>7</v>
+      </c>
+      <c r="C63" t="s">
+        <v>30</v>
+      </c>
+      <c r="D63" t="n">
+        <v>8</v>
+      </c>
+      <c r="E63" t="s">
+        <v>5</v>
+      </c>
+      <c r="F63" t="s">
+        <v>23</v>
+      </c>
+      <c r="G63" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>17</v>
+      </c>
+      <c r="B64" t="n">
+        <v>7</v>
+      </c>
+      <c r="C64" t="s">
+        <v>31</v>
+      </c>
+      <c r="D64" t="n">
+        <v>9</v>
+      </c>
+      <c r="E64" t="s">
+        <v>5</v>
+      </c>
+      <c r="F64" t="s">
+        <v>23</v>
+      </c>
+      <c r="G64" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>33</v>
+      </c>
+      <c r="B65" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C65" t="s">
+        <v>22</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="s">
+        <v>5</v>
+      </c>
+      <c r="F65" t="s">
+        <v>23</v>
+      </c>
+      <c r="G65" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>33</v>
+      </c>
+      <c r="B66" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C66" t="s">
+        <v>24</v>
+      </c>
+      <c r="D66" t="n">
+        <v>2</v>
+      </c>
+      <c r="E66" t="s">
+        <v>5</v>
+      </c>
+      <c r="F66" t="s">
+        <v>23</v>
+      </c>
+      <c r="G66" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>33</v>
+      </c>
+      <c r="B67" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C67" t="s">
+        <v>25</v>
+      </c>
+      <c r="D67" t="n">
+        <v>3</v>
+      </c>
+      <c r="E67" t="s">
+        <v>5</v>
+      </c>
+      <c r="F67" t="s">
+        <v>23</v>
+      </c>
+      <c r="G67" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>33</v>
+      </c>
+      <c r="B68" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C68" t="s">
+        <v>26</v>
+      </c>
+      <c r="D68" t="n">
+        <v>4</v>
+      </c>
+      <c r="E68" t="s">
+        <v>5</v>
+      </c>
+      <c r="F68" t="s">
+        <v>23</v>
+      </c>
+      <c r="G68" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>33</v>
+      </c>
+      <c r="B69" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C69" t="s">
+        <v>27</v>
+      </c>
+      <c r="D69" t="n">
+        <v>5</v>
+      </c>
+      <c r="E69" t="s">
+        <v>5</v>
+      </c>
+      <c r="F69" t="s">
+        <v>23</v>
+      </c>
+      <c r="G69" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>33</v>
+      </c>
+      <c r="B70" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C70" t="s">
+        <v>28</v>
+      </c>
+      <c r="D70" t="n">
+        <v>6</v>
+      </c>
+      <c r="E70" t="s">
+        <v>6</v>
+      </c>
+      <c r="F70" t="s">
+        <v>23</v>
+      </c>
+      <c r="G70" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>33</v>
+      </c>
+      <c r="B71" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C71" t="s">
+        <v>29</v>
+      </c>
+      <c r="D71" t="n">
+        <v>7</v>
+      </c>
+      <c r="E71" t="s">
+        <v>5</v>
+      </c>
+      <c r="F71" t="s">
+        <v>23</v>
+      </c>
+      <c r="G71" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>33</v>
+      </c>
+      <c r="B72" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C72" t="s">
+        <v>30</v>
+      </c>
+      <c r="D72" t="n">
+        <v>8</v>
+      </c>
+      <c r="E72" t="s">
+        <v>6</v>
+      </c>
+      <c r="F72" t="s">
+        <v>23</v>
+      </c>
+      <c r="G72" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>33</v>
+      </c>
+      <c r="B73" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C73" t="s">
+        <v>31</v>
+      </c>
+      <c r="D73" t="n">
+        <v>9</v>
+      </c>
+      <c r="E73" t="s">
+        <v>6</v>
+      </c>
+      <c r="F73" t="s">
+        <v>23</v>
+      </c>
+      <c r="G73" t="s">
         <v>6</v>
       </c>
     </row>
@@ -2318,7 +2690,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>452</v>
+        <v>336.080851276617</v>
       </c>
     </row>
     <row r="3">
@@ -2332,7 +2704,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>52</v>
+        <v>40.4357357286305</v>
       </c>
     </row>
     <row r="4">
@@ -2346,7 +2718,7 @@
         <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>148</v>
+        <v>169.699817591538</v>
       </c>
     </row>
     <row r="5">
@@ -2360,7 +2732,7 @@
         <v>34</v>
       </c>
       <c r="D5" t="n">
-        <v>40</v>
+        <v>40.0655660144784</v>
       </c>
     </row>
     <row r="6">
@@ -2374,7 +2746,7 @@
         <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>165</v>
+        <v>151.588995415245</v>
       </c>
     </row>
     <row r="7">
@@ -2388,7 +2760,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>54</v>
+        <v>123.433050356455</v>
       </c>
     </row>
     <row r="8">
@@ -2402,7 +2774,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>31</v>
+        <v>35.5613447848116</v>
       </c>
     </row>
     <row r="9">
@@ -2416,7 +2788,7 @@
         <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>213</v>
+        <v>202.728745098835</v>
       </c>
     </row>
     <row r="10">
@@ -2444,7 +2816,7 @@
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>40</v>
+        <v>57.0283032288794</v>
       </c>
     </row>
     <row r="12">
@@ -2458,7 +2830,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>54</v>
+        <v>80.9761478966684</v>
       </c>
     </row>
     <row r="13">
@@ -2472,7 +2844,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>20</v>
+        <v>28.3782590097662</v>
       </c>
     </row>
     <row r="14">
@@ -2486,7 +2858,7 @@
         <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>252</v>
+        <v>205.745763807094</v>
       </c>
     </row>
     <row r="15">
@@ -2500,7 +2872,7 @@
         <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>13</v>
+        <v>13.8959828324155</v>
       </c>
     </row>
     <row r="16">
@@ -2514,7 +2886,7 @@
         <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>51</v>
+        <v>56.1379357256746</v>
       </c>
     </row>
     <row r="17">
@@ -2528,7 +2900,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>11705</v>
+        <v>66.3469031230314</v>
       </c>
     </row>
     <row r="18">
@@ -2539,10 +2911,10 @@
         <v>4</v>
       </c>
       <c r="C18" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>911</v>
+        <v>27.5016333122411</v>
       </c>
     </row>
     <row r="19">
@@ -2553,10 +2925,10 @@
         <v>4</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>861</v>
+        <v>181.560075908497</v>
       </c>
     </row>
     <row r="20">
@@ -2567,10 +2939,10 @@
         <v>4</v>
       </c>
       <c r="C20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D20" t="n">
-        <v>1038</v>
+        <v>22.2289033646727</v>
       </c>
     </row>
     <row r="21">
@@ -2584,7 +2956,217 @@
         <v>9</v>
       </c>
       <c r="D21" t="n">
-        <v>1547</v>
+        <v>45.2428639016647</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>638.968665995045</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" t="n">
+        <v>189.98485059482</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" t="n">
+        <v>463.168177197315</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" t="n">
+        <v>5</v>
+      </c>
+      <c r="C25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25" t="n">
+        <v>211.095224336815</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" t="n">
+        <v>329.667836240939</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="n">
+        <v>6</v>
+      </c>
+      <c r="C27" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2446.43752319239</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="n">
+        <v>6</v>
+      </c>
+      <c r="C28" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28" t="n">
+        <v>229.986626985974</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="n">
+        <v>6</v>
+      </c>
+      <c r="C29" t="s">
+        <v>37</v>
+      </c>
+      <c r="D29" t="n">
+        <v>384.713255981969</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="n">
+        <v>6</v>
+      </c>
+      <c r="C30" t="s">
+        <v>38</v>
+      </c>
+      <c r="D30" t="n">
+        <v>505.262578811219</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="n">
+        <v>6</v>
+      </c>
+      <c r="C31" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" t="n">
+        <v>499.355662017509</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32" t="n">
+        <v>7</v>
+      </c>
+      <c r="C32" t="s">
+        <v>5</v>
+      </c>
+      <c r="D32" t="n">
+        <v>8580.75685815979</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33" t="n">
+        <v>7</v>
+      </c>
+      <c r="C33" t="s">
+        <v>6</v>
+      </c>
+      <c r="D33" t="n">
+        <v>269.151549583756</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34" t="n">
+        <v>7</v>
+      </c>
+      <c r="C34" t="s">
+        <v>37</v>
+      </c>
+      <c r="D34" t="n">
+        <v>229.268770857761</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>17</v>
+      </c>
+      <c r="B35" t="n">
+        <v>7</v>
+      </c>
+      <c r="C35" t="s">
+        <v>38</v>
+      </c>
+      <c r="D35" t="n">
+        <v>391.243936788619</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" t="n">
+        <v>7</v>
+      </c>
+      <c r="C36" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" t="n">
+        <v>400.301604878861</v>
       </c>
     </row>
   </sheetData>
@@ -2606,30 +3188,18 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2649,20 +3219,10 @@
       <c r="E2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G2" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2"/>
-      <c r="K2" t="s">
+      <c r="F2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2682,20 +3242,10 @@
       <c r="E3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3"/>
-      <c r="K3" t="s">
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2715,20 +3265,10 @@
       <c r="E4" t="s">
         <v>5</v>
       </c>
-      <c r="F4" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4"/>
-      <c r="K4" t="s">
+      <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2748,20 +3288,10 @@
       <c r="E5" t="s">
         <v>5</v>
       </c>
-      <c r="F5" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5"/>
-      <c r="K5" t="s">
+      <c r="F5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2781,20 +3311,10 @@
       <c r="E6" t="s">
         <v>5</v>
       </c>
-      <c r="F6" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6"/>
-      <c r="K6" t="s">
+      <c r="F6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2814,20 +3334,10 @@
       <c r="E7" t="s">
         <v>34</v>
       </c>
-      <c r="F7" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7"/>
-      <c r="K7" t="s">
+      <c r="F7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2847,20 +3357,10 @@
       <c r="E8" t="s">
         <v>11</v>
       </c>
-      <c r="F8" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H8" t="s">
+      <c r="F8" t="s">
         <v>32</v>
       </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8"/>
-      <c r="K8" t="s">
+      <c r="G8" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2880,20 +3380,10 @@
       <c r="E9" t="s">
         <v>11</v>
       </c>
-      <c r="F9" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H9" t="s">
+      <c r="F9" t="s">
         <v>32</v>
       </c>
-      <c r="I9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9"/>
-      <c r="K9" t="s">
+      <c r="G9" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2913,29 +3403,19 @@
       <c r="E10" t="s">
         <v>5</v>
       </c>
-      <c r="F10" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10"/>
-      <c r="K10" t="s">
+      <c r="F10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="s">
         <v>22</v>
@@ -2946,29 +3426,19 @@
       <c r="E11" t="s">
         <v>11</v>
       </c>
-      <c r="F11" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H11" t="s">
+      <c r="F11" t="s">
         <v>32</v>
       </c>
-      <c r="I11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11"/>
-      <c r="K11" t="s">
+      <c r="G11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" t="s">
         <v>24</v>
@@ -2979,29 +3449,19 @@
       <c r="E12" t="s">
         <v>11</v>
       </c>
-      <c r="F12" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G12" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H12" t="s">
+      <c r="F12" t="s">
         <v>32</v>
       </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12"/>
-      <c r="K12" t="s">
+      <c r="G12" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" t="s">
         <v>25</v>
@@ -3012,29 +3472,19 @@
       <c r="E13" t="s">
         <v>11</v>
       </c>
-      <c r="F13" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H13" t="s">
+      <c r="F13" t="s">
         <v>32</v>
       </c>
-      <c r="I13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13"/>
-      <c r="K13" t="s">
+      <c r="G13" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" t="s">
         <v>26</v>
@@ -3045,29 +3495,19 @@
       <c r="E14" t="s">
         <v>11</v>
       </c>
-      <c r="F14" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H14" t="s">
+      <c r="F14" t="s">
         <v>32</v>
       </c>
-      <c r="I14" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14"/>
-      <c r="K14" t="s">
+      <c r="G14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15" t="s">
         <v>27</v>
@@ -3078,29 +3518,19 @@
       <c r="E15" t="s">
         <v>11</v>
       </c>
-      <c r="F15" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H15" t="s">
+      <c r="F15" t="s">
         <v>32</v>
       </c>
-      <c r="I15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15"/>
-      <c r="K15" t="s">
+      <c r="G15" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="s">
         <v>28</v>
@@ -3111,29 +3541,19 @@
       <c r="E16" t="s">
         <v>11</v>
       </c>
-      <c r="F16" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H16" t="s">
+      <c r="F16" t="s">
         <v>32</v>
       </c>
-      <c r="I16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16"/>
-      <c r="K16" t="s">
+      <c r="G16" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="s">
         <v>29</v>
@@ -3144,29 +3564,19 @@
       <c r="E17" t="s">
         <v>11</v>
       </c>
-      <c r="F17" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H17" t="s">
+      <c r="F17" t="s">
         <v>32</v>
       </c>
-      <c r="I17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17"/>
-      <c r="K17" t="s">
+      <c r="G17" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="s">
         <v>30</v>
@@ -3177,29 +3587,19 @@
       <c r="E18" t="s">
         <v>11</v>
       </c>
-      <c r="F18" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G18" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H18" t="s">
+      <c r="F18" t="s">
         <v>32</v>
       </c>
-      <c r="I18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18"/>
-      <c r="K18" t="s">
+      <c r="G18" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" t="s">
         <v>31</v>
@@ -3210,29 +3610,19 @@
       <c r="E19" t="s">
         <v>11</v>
       </c>
-      <c r="F19" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G19" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H19" t="s">
+      <c r="F19" t="s">
         <v>32</v>
       </c>
-      <c r="I19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19"/>
-      <c r="K19" t="s">
+      <c r="G19" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C20" t="s">
         <v>22</v>
@@ -3243,29 +3633,19 @@
       <c r="E20" t="s">
         <v>11</v>
       </c>
-      <c r="F20" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G20" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H20" t="s">
+      <c r="F20" t="s">
         <v>32</v>
       </c>
-      <c r="I20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20"/>
-      <c r="K20" t="s">
+      <c r="G20" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C21" t="s">
         <v>24</v>
@@ -3276,29 +3656,19 @@
       <c r="E21" t="s">
         <v>11</v>
       </c>
-      <c r="F21" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G21" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H21" t="s">
+      <c r="F21" t="s">
         <v>32</v>
       </c>
-      <c r="I21" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21"/>
-      <c r="K21" t="s">
+      <c r="G21" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C22" t="s">
         <v>25</v>
@@ -3309,29 +3679,19 @@
       <c r="E22" t="s">
         <v>11</v>
       </c>
-      <c r="F22" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G22" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H22" t="s">
+      <c r="F22" t="s">
         <v>32</v>
       </c>
-      <c r="I22" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22"/>
-      <c r="K22" t="s">
+      <c r="G22" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C23" t="s">
         <v>26</v>
@@ -3342,29 +3702,19 @@
       <c r="E23" t="s">
         <v>11</v>
       </c>
-      <c r="F23" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G23" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H23" t="s">
+      <c r="F23" t="s">
         <v>32</v>
       </c>
-      <c r="I23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23"/>
-      <c r="K23" t="s">
+      <c r="G23" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C24" t="s">
         <v>27</v>
@@ -3375,29 +3725,19 @@
       <c r="E24" t="s">
         <v>11</v>
       </c>
-      <c r="F24" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G24" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H24" t="s">
+      <c r="F24" t="s">
         <v>32</v>
       </c>
-      <c r="I24" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24"/>
-      <c r="K24" t="s">
+      <c r="G24" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C25" t="s">
         <v>28</v>
@@ -3408,29 +3748,19 @@
       <c r="E25" t="s">
         <v>11</v>
       </c>
-      <c r="F25" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G25" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H25" t="s">
+      <c r="F25" t="s">
         <v>32</v>
       </c>
-      <c r="I25" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25"/>
-      <c r="K25" t="s">
+      <c r="G25" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C26" t="s">
         <v>29</v>
@@ -3441,29 +3771,19 @@
       <c r="E26" t="s">
         <v>11</v>
       </c>
-      <c r="F26" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G26" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H26" t="s">
+      <c r="F26" t="s">
         <v>32</v>
       </c>
-      <c r="I26" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26"/>
-      <c r="K26" t="s">
+      <c r="G26" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C27" t="s">
         <v>30</v>
@@ -3474,29 +3794,19 @@
       <c r="E27" t="s">
         <v>11</v>
       </c>
-      <c r="F27" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G27" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H27" t="s">
+      <c r="F27" t="s">
         <v>32</v>
       </c>
-      <c r="I27" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27"/>
-      <c r="K27" t="s">
+      <c r="G27" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C28" t="s">
         <v>31</v>
@@ -3507,29 +3817,19 @@
       <c r="E28" t="s">
         <v>11</v>
       </c>
-      <c r="F28" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G28" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H28" t="s">
+      <c r="F28" t="s">
         <v>32</v>
       </c>
-      <c r="I28" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28"/>
-      <c r="K28" t="s">
+      <c r="G28" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C29" t="s">
         <v>22</v>
@@ -3540,29 +3840,19 @@
       <c r="E29" t="s">
         <v>5</v>
       </c>
-      <c r="F29" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G29" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H29" t="s">
-        <v>23</v>
-      </c>
-      <c r="I29" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29"/>
-      <c r="K29" t="s">
+      <c r="F29" t="s">
+        <v>23</v>
+      </c>
+      <c r="G29" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C30" t="s">
         <v>24</v>
@@ -3573,29 +3863,19 @@
       <c r="E30" t="s">
         <v>5</v>
       </c>
-      <c r="F30" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G30" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H30" t="s">
-        <v>23</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30"/>
-      <c r="K30" t="s">
+      <c r="F30" t="s">
+        <v>23</v>
+      </c>
+      <c r="G30" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C31" t="s">
         <v>25</v>
@@ -3606,29 +3886,19 @@
       <c r="E31" t="s">
         <v>5</v>
       </c>
-      <c r="F31" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G31" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H31" t="s">
-        <v>23</v>
-      </c>
-      <c r="I31" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31"/>
-      <c r="K31" t="s">
+      <c r="F31" t="s">
+        <v>23</v>
+      </c>
+      <c r="G31" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C32" t="s">
         <v>26</v>
@@ -3639,29 +3909,19 @@
       <c r="E32" t="s">
         <v>5</v>
       </c>
-      <c r="F32" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G32" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H32" t="s">
-        <v>23</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32"/>
-      <c r="K32" t="s">
+      <c r="F32" t="s">
+        <v>23</v>
+      </c>
+      <c r="G32" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C33" t="s">
         <v>27</v>
@@ -3670,31 +3930,21 @@
         <v>5</v>
       </c>
       <c r="E33" t="s">
-        <v>5</v>
-      </c>
-      <c r="F33" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G33" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H33" t="s">
-        <v>23</v>
-      </c>
-      <c r="I33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33"/>
-      <c r="K33" t="s">
-        <v>5</v>
+        <v>11</v>
+      </c>
+      <c r="F33" t="s">
+        <v>32</v>
+      </c>
+      <c r="G33" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C34" t="s">
         <v>28</v>
@@ -3703,31 +3953,21 @@
         <v>6</v>
       </c>
       <c r="E34" t="s">
-        <v>5</v>
-      </c>
-      <c r="F34" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G34" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H34" t="s">
-        <v>23</v>
-      </c>
-      <c r="I34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34"/>
-      <c r="K34" t="s">
-        <v>5</v>
+        <v>11</v>
+      </c>
+      <c r="F34" t="s">
+        <v>32</v>
+      </c>
+      <c r="G34" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C35" t="s">
         <v>29</v>
@@ -3738,29 +3978,19 @@
       <c r="E35" t="s">
         <v>5</v>
       </c>
-      <c r="F35" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G35" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H35" t="s">
-        <v>23</v>
-      </c>
-      <c r="I35" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35"/>
-      <c r="K35" t="s">
+      <c r="F35" t="s">
+        <v>23</v>
+      </c>
+      <c r="G35" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C36" t="s">
         <v>30</v>
@@ -3769,31 +3999,21 @@
         <v>8</v>
       </c>
       <c r="E36" t="s">
-        <v>5</v>
-      </c>
-      <c r="F36" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G36" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H36" t="s">
-        <v>23</v>
-      </c>
-      <c r="I36" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36"/>
-      <c r="K36" t="s">
-        <v>5</v>
+        <v>11</v>
+      </c>
+      <c r="F36" t="s">
+        <v>32</v>
+      </c>
+      <c r="G36" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C37" t="s">
         <v>31</v>
@@ -3804,29 +4024,19 @@
       <c r="E37" t="s">
         <v>5</v>
       </c>
-      <c r="F37" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G37" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H37" t="s">
-        <v>23</v>
-      </c>
-      <c r="I37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37"/>
-      <c r="K37" t="s">
+      <c r="F37" t="s">
+        <v>23</v>
+      </c>
+      <c r="G37" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B38" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="C38" t="s">
         <v>22</v>
@@ -3837,29 +4047,19 @@
       <c r="E38" t="s">
         <v>5</v>
       </c>
-      <c r="F38" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G38" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H38" t="s">
-        <v>23</v>
-      </c>
-      <c r="I38" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38"/>
-      <c r="K38" t="s">
+      <c r="F38" t="s">
+        <v>23</v>
+      </c>
+      <c r="G38" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B39" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="C39" t="s">
         <v>24</v>
@@ -3870,29 +4070,19 @@
       <c r="E39" t="s">
         <v>5</v>
       </c>
-      <c r="F39" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G39" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H39" t="s">
-        <v>23</v>
-      </c>
-      <c r="I39" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39"/>
-      <c r="K39" t="s">
+      <c r="F39" t="s">
+        <v>23</v>
+      </c>
+      <c r="G39" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B40" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="C40" t="s">
         <v>25</v>
@@ -3903,29 +4093,19 @@
       <c r="E40" t="s">
         <v>5</v>
       </c>
-      <c r="F40" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G40" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H40" t="s">
-        <v>23</v>
-      </c>
-      <c r="I40" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40"/>
-      <c r="K40" t="s">
+      <c r="F40" t="s">
+        <v>23</v>
+      </c>
+      <c r="G40" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B41" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="C41" t="s">
         <v>26</v>
@@ -3936,29 +4116,19 @@
       <c r="E41" t="s">
         <v>5</v>
       </c>
-      <c r="F41" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G41" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H41" t="s">
-        <v>23</v>
-      </c>
-      <c r="I41" t="n">
-        <v>1</v>
-      </c>
-      <c r="J41"/>
-      <c r="K41" t="s">
+      <c r="F41" t="s">
+        <v>23</v>
+      </c>
+      <c r="G41" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B42" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="C42" t="s">
         <v>27</v>
@@ -3969,29 +4139,19 @@
       <c r="E42" t="s">
         <v>5</v>
       </c>
-      <c r="F42" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G42" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H42" t="s">
-        <v>23</v>
-      </c>
-      <c r="I42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J42"/>
-      <c r="K42" t="s">
+      <c r="F42" t="s">
+        <v>23</v>
+      </c>
+      <c r="G42" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B43" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="C43" t="s">
         <v>28</v>
@@ -4002,29 +4162,19 @@
       <c r="E43" t="s">
         <v>5</v>
       </c>
-      <c r="F43" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G43" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H43" t="s">
-        <v>23</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43"/>
-      <c r="K43" t="s">
+      <c r="F43" t="s">
+        <v>23</v>
+      </c>
+      <c r="G43" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B44" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="C44" t="s">
         <v>29</v>
@@ -4035,29 +4185,19 @@
       <c r="E44" t="s">
         <v>5</v>
       </c>
-      <c r="F44" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G44" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H44" t="s">
-        <v>23</v>
-      </c>
-      <c r="I44" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44"/>
-      <c r="K44" t="s">
+      <c r="F44" t="s">
+        <v>23</v>
+      </c>
+      <c r="G44" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B45" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="C45" t="s">
         <v>30</v>
@@ -4068,29 +4208,19 @@
       <c r="E45" t="s">
         <v>5</v>
       </c>
-      <c r="F45" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G45" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H45" t="s">
-        <v>23</v>
-      </c>
-      <c r="I45" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45"/>
-      <c r="K45" t="s">
+      <c r="F45" t="s">
+        <v>23</v>
+      </c>
+      <c r="G45" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B46" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="C46" t="s">
         <v>31</v>
@@ -4101,20 +4231,631 @@
       <c r="E46" t="s">
         <v>5</v>
       </c>
-      <c r="F46" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G46" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H46" t="s">
-        <v>23</v>
-      </c>
-      <c r="I46" t="n">
+      <c r="F46" t="s">
+        <v>23</v>
+      </c>
+      <c r="G46" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>10</v>
+      </c>
+      <c r="B47" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" t="s">
+        <v>22</v>
+      </c>
+      <c r="D47" t="n">
         <v>1</v>
       </c>
-      <c r="J46"/>
-      <c r="K46" t="s">
+      <c r="E47" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" t="s">
+        <v>23</v>
+      </c>
+      <c r="G47" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>10</v>
+      </c>
+      <c r="B48" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" t="s">
+        <v>24</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2</v>
+      </c>
+      <c r="E48" t="s">
+        <v>11</v>
+      </c>
+      <c r="F48" t="s">
+        <v>32</v>
+      </c>
+      <c r="G48" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>10</v>
+      </c>
+      <c r="B49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C49" t="s">
+        <v>25</v>
+      </c>
+      <c r="D49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" t="s">
+        <v>11</v>
+      </c>
+      <c r="F49" t="s">
+        <v>32</v>
+      </c>
+      <c r="G49" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>10</v>
+      </c>
+      <c r="B50" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" t="s">
+        <v>26</v>
+      </c>
+      <c r="D50" t="n">
+        <v>4</v>
+      </c>
+      <c r="E50" t="s">
+        <v>11</v>
+      </c>
+      <c r="F50" t="s">
+        <v>32</v>
+      </c>
+      <c r="G50" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>10</v>
+      </c>
+      <c r="B51" t="n">
+        <v>2</v>
+      </c>
+      <c r="C51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D51" t="n">
+        <v>5</v>
+      </c>
+      <c r="E51" t="s">
+        <v>11</v>
+      </c>
+      <c r="F51" t="s">
+        <v>32</v>
+      </c>
+      <c r="G51" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>10</v>
+      </c>
+      <c r="B52" t="n">
+        <v>2</v>
+      </c>
+      <c r="C52" t="s">
+        <v>28</v>
+      </c>
+      <c r="D52" t="n">
+        <v>6</v>
+      </c>
+      <c r="E52" t="s">
+        <v>11</v>
+      </c>
+      <c r="F52" t="s">
+        <v>32</v>
+      </c>
+      <c r="G52" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>10</v>
+      </c>
+      <c r="B53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C53" t="s">
+        <v>29</v>
+      </c>
+      <c r="D53" t="n">
+        <v>7</v>
+      </c>
+      <c r="E53" t="s">
+        <v>11</v>
+      </c>
+      <c r="F53" t="s">
+        <v>32</v>
+      </c>
+      <c r="G53" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>10</v>
+      </c>
+      <c r="B54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C54" t="s">
+        <v>30</v>
+      </c>
+      <c r="D54" t="n">
+        <v>8</v>
+      </c>
+      <c r="E54" t="s">
+        <v>11</v>
+      </c>
+      <c r="F54" t="s">
+        <v>32</v>
+      </c>
+      <c r="G54" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>10</v>
+      </c>
+      <c r="B55" t="n">
+        <v>2</v>
+      </c>
+      <c r="C55" t="s">
+        <v>31</v>
+      </c>
+      <c r="D55" t="n">
+        <v>9</v>
+      </c>
+      <c r="E55" t="s">
+        <v>11</v>
+      </c>
+      <c r="F55" t="s">
+        <v>32</v>
+      </c>
+      <c r="G55" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>17</v>
+      </c>
+      <c r="B56" t="n">
+        <v>7</v>
+      </c>
+      <c r="C56" t="s">
+        <v>22</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="s">
+        <v>5</v>
+      </c>
+      <c r="F56" t="s">
+        <v>23</v>
+      </c>
+      <c r="G56" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>17</v>
+      </c>
+      <c r="B57" t="n">
+        <v>7</v>
+      </c>
+      <c r="C57" t="s">
+        <v>24</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2</v>
+      </c>
+      <c r="E57" t="s">
+        <v>5</v>
+      </c>
+      <c r="F57" t="s">
+        <v>23</v>
+      </c>
+      <c r="G57" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>17</v>
+      </c>
+      <c r="B58" t="n">
+        <v>7</v>
+      </c>
+      <c r="C58" t="s">
+        <v>25</v>
+      </c>
+      <c r="D58" t="n">
+        <v>3</v>
+      </c>
+      <c r="E58" t="s">
+        <v>5</v>
+      </c>
+      <c r="F58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G58" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>17</v>
+      </c>
+      <c r="B59" t="n">
+        <v>7</v>
+      </c>
+      <c r="C59" t="s">
+        <v>26</v>
+      </c>
+      <c r="D59" t="n">
+        <v>4</v>
+      </c>
+      <c r="E59" t="s">
+        <v>5</v>
+      </c>
+      <c r="F59" t="s">
+        <v>23</v>
+      </c>
+      <c r="G59" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>17</v>
+      </c>
+      <c r="B60" t="n">
+        <v>7</v>
+      </c>
+      <c r="C60" t="s">
+        <v>27</v>
+      </c>
+      <c r="D60" t="n">
+        <v>5</v>
+      </c>
+      <c r="E60" t="s">
+        <v>5</v>
+      </c>
+      <c r="F60" t="s">
+        <v>23</v>
+      </c>
+      <c r="G60" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>17</v>
+      </c>
+      <c r="B61" t="n">
+        <v>7</v>
+      </c>
+      <c r="C61" t="s">
+        <v>28</v>
+      </c>
+      <c r="D61" t="n">
+        <v>6</v>
+      </c>
+      <c r="E61" t="s">
+        <v>5</v>
+      </c>
+      <c r="F61" t="s">
+        <v>23</v>
+      </c>
+      <c r="G61" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>17</v>
+      </c>
+      <c r="B62" t="n">
+        <v>7</v>
+      </c>
+      <c r="C62" t="s">
+        <v>29</v>
+      </c>
+      <c r="D62" t="n">
+        <v>7</v>
+      </c>
+      <c r="E62" t="s">
+        <v>5</v>
+      </c>
+      <c r="F62" t="s">
+        <v>23</v>
+      </c>
+      <c r="G62" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>17</v>
+      </c>
+      <c r="B63" t="n">
+        <v>7</v>
+      </c>
+      <c r="C63" t="s">
+        <v>30</v>
+      </c>
+      <c r="D63" t="n">
+        <v>8</v>
+      </c>
+      <c r="E63" t="s">
+        <v>5</v>
+      </c>
+      <c r="F63" t="s">
+        <v>23</v>
+      </c>
+      <c r="G63" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>17</v>
+      </c>
+      <c r="B64" t="n">
+        <v>7</v>
+      </c>
+      <c r="C64" t="s">
+        <v>31</v>
+      </c>
+      <c r="D64" t="n">
+        <v>9</v>
+      </c>
+      <c r="E64" t="s">
+        <v>5</v>
+      </c>
+      <c r="F64" t="s">
+        <v>23</v>
+      </c>
+      <c r="G64" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>33</v>
+      </c>
+      <c r="B65" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C65" t="s">
+        <v>22</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="s">
+        <v>5</v>
+      </c>
+      <c r="F65" t="s">
+        <v>23</v>
+      </c>
+      <c r="G65" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>33</v>
+      </c>
+      <c r="B66" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C66" t="s">
+        <v>24</v>
+      </c>
+      <c r="D66" t="n">
+        <v>2</v>
+      </c>
+      <c r="E66" t="s">
+        <v>5</v>
+      </c>
+      <c r="F66" t="s">
+        <v>23</v>
+      </c>
+      <c r="G66" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>33</v>
+      </c>
+      <c r="B67" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C67" t="s">
+        <v>25</v>
+      </c>
+      <c r="D67" t="n">
+        <v>3</v>
+      </c>
+      <c r="E67" t="s">
+        <v>5</v>
+      </c>
+      <c r="F67" t="s">
+        <v>23</v>
+      </c>
+      <c r="G67" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>33</v>
+      </c>
+      <c r="B68" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C68" t="s">
+        <v>26</v>
+      </c>
+      <c r="D68" t="n">
+        <v>4</v>
+      </c>
+      <c r="E68" t="s">
+        <v>5</v>
+      </c>
+      <c r="F68" t="s">
+        <v>23</v>
+      </c>
+      <c r="G68" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>33</v>
+      </c>
+      <c r="B69" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C69" t="s">
+        <v>27</v>
+      </c>
+      <c r="D69" t="n">
+        <v>5</v>
+      </c>
+      <c r="E69" t="s">
+        <v>5</v>
+      </c>
+      <c r="F69" t="s">
+        <v>23</v>
+      </c>
+      <c r="G69" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>33</v>
+      </c>
+      <c r="B70" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C70" t="s">
+        <v>28</v>
+      </c>
+      <c r="D70" t="n">
+        <v>6</v>
+      </c>
+      <c r="E70" t="s">
+        <v>5</v>
+      </c>
+      <c r="F70" t="s">
+        <v>23</v>
+      </c>
+      <c r="G70" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>33</v>
+      </c>
+      <c r="B71" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C71" t="s">
+        <v>29</v>
+      </c>
+      <c r="D71" t="n">
+        <v>7</v>
+      </c>
+      <c r="E71" t="s">
+        <v>5</v>
+      </c>
+      <c r="F71" t="s">
+        <v>23</v>
+      </c>
+      <c r="G71" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>33</v>
+      </c>
+      <c r="B72" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C72" t="s">
+        <v>30</v>
+      </c>
+      <c r="D72" t="n">
+        <v>8</v>
+      </c>
+      <c r="E72" t="s">
+        <v>5</v>
+      </c>
+      <c r="F72" t="s">
+        <v>23</v>
+      </c>
+      <c r="G72" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>33</v>
+      </c>
+      <c r="B73" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C73" t="s">
+        <v>31</v>
+      </c>
+      <c r="D73" t="n">
+        <v>9</v>
+      </c>
+      <c r="E73" t="s">
+        <v>5</v>
+      </c>
+      <c r="F73" t="s">
+        <v>23</v>
+      </c>
+      <c r="G73" t="s">
         <v>5</v>
       </c>
     </row>

--- a/Outcome/Publish/figure_data/fig3.xlsx
+++ b/Outcome/Publish/figure_data/fig3.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t xml:space="preserve">AgeGroup</t>
   </si>
@@ -41,9 +41,6 @@
     <t xml:space="preserve">HFMD</t>
   </si>
   <si>
-    <t xml:space="preserve">Chickenpox</t>
-  </si>
-  <si>
     <t xml:space="preserve">Others</t>
   </si>
   <si>
@@ -56,6 +53,9 @@
     <t xml:space="preserve">10-14</t>
   </si>
   <si>
+    <t xml:space="preserve">Chickenpox</t>
+  </si>
+  <si>
     <t xml:space="preserve">15-19</t>
   </si>
   <si>
@@ -63,9 +63,6 @@
   </si>
   <si>
     <t xml:space="preserve">40-59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HBV</t>
   </si>
   <si>
     <t xml:space="preserve">60+</t>
@@ -119,19 +116,13 @@
     <t xml:space="preserve">Total</t>
   </si>
   <si>
-    <t xml:space="preserve">Measles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diphtheria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Encephalitis</t>
-  </si>
-  <si>
     <t xml:space="preserve">Leptospirosis</t>
   </si>
   <si>
     <t xml:space="preserve">Melioidosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Measles</t>
   </si>
 </sst>
 </file>
@@ -527,161 +518,161 @@
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>197386.92128657</v>
+        <v>410123.920688537</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>212736.999401967</v>
+        <v>207210.406276195</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>207210.406276195</v>
+        <v>673512.419055442</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" t="n">
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>673512.419055442</v>
+        <v>195085.354133745</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" t="n">
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>195085.354133745</v>
+        <v>410266.63549073</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>193350.729009513</v>
+        <v>506614.23767102</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>216915.906481217</v>
+        <v>316456.043334976</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="n">
         <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D12" t="n">
-        <v>85546.1079870612</v>
+        <v>150953.40760811</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="n">
         <v>3</v>
       </c>
       <c r="C13" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>506614.23767102</v>
+        <v>179593.807880794</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>316456.043334976</v>
+        <v>247009.701346544</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>150953.40760811</v>
+        <v>228775.52818226</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" t="s">
         <v>12</v>
       </c>
-      <c r="B16" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" t="s">
-        <v>9</v>
-      </c>
       <c r="D16" t="n">
-        <v>94047.6998937327</v>
+        <v>80702.3493339277</v>
       </c>
     </row>
     <row r="17">
@@ -692,276 +683,178 @@
         <v>4</v>
       </c>
       <c r="C17" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>52052.7920691823</v>
+        <v>183659.029471305</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>247009.701346544</v>
+        <v>291134.379172665</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C19" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>228775.52818226</v>
+        <v>929183.598146722</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C20" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D20" t="n">
-        <v>80702.3493339277</v>
+        <v>441897.75352447</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D21" t="n">
-        <v>131606.237402122</v>
+        <v>736636.991080393</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C22" t="s">
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>291134.379172665</v>
+        <v>627996.515626952</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C23" t="s">
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>929183.598146722</v>
+        <v>574225.006020735</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D24" t="n">
-        <v>441897.75352447</v>
+        <v>153375.300212957</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C25" t="s">
         <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>183796.656320851</v>
+        <v>401809.73923787</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C26" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>552840.334759543</v>
+        <v>1610710.70529812</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C27" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>627996.515626952</v>
+        <v>282733.321002064</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C28" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D28" t="n">
-        <v>574225.006020735</v>
+        <v>48021.1745600166</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C29" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D29" t="n">
-        <v>153375.300212957</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" t="n">
-        <v>6</v>
-      </c>
-      <c r="C30" t="s">
-        <v>16</v>
-      </c>
-      <c r="D30" t="n">
-        <v>62047.7405690359</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" t="n">
-        <v>6</v>
-      </c>
-      <c r="C31" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" t="n">
-        <v>339761.998668834</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>17</v>
-      </c>
-      <c r="B32" t="n">
-        <v>7</v>
-      </c>
-      <c r="C32" t="s">
-        <v>5</v>
-      </c>
-      <c r="D32" t="n">
-        <v>1610710.70529812</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>17</v>
-      </c>
-      <c r="B33" t="n">
-        <v>7</v>
-      </c>
-      <c r="C33" t="s">
-        <v>6</v>
-      </c>
-      <c r="D33" t="n">
-        <v>282733.321002064</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>17</v>
-      </c>
-      <c r="B34" t="n">
-        <v>7</v>
-      </c>
-      <c r="C34" t="s">
-        <v>11</v>
-      </c>
-      <c r="D34" t="n">
-        <v>48021.1745600166</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>17</v>
-      </c>
-      <c r="B35" t="n">
-        <v>7</v>
-      </c>
-      <c r="C35" t="s">
-        <v>16</v>
-      </c>
-      <c r="D35" t="n">
-        <v>24796.6774320023</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>17</v>
-      </c>
-      <c r="B36" t="n">
-        <v>7</v>
-      </c>
-      <c r="C36" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" t="n">
-        <v>157837.588608428</v>
+        <v>182634.26604043</v>
       </c>
     </row>
   </sheetData>
@@ -983,19 +876,19 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" t="s">
         <v>18</v>
-      </c>
-      <c r="D1" t="s">
-        <v>19</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
       </c>
       <c r="F1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" t="s">
         <v>20</v>
-      </c>
-      <c r="G1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2">
@@ -1006,7 +899,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -1015,7 +908,7 @@
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G2" t="s">
         <v>5</v>
@@ -1029,7 +922,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -1038,7 +931,7 @@
         <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G3" t="s">
         <v>5</v>
@@ -1052,7 +945,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -1061,7 +954,7 @@
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G4" t="s">
         <v>5</v>
@@ -1075,7 +968,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -1084,7 +977,7 @@
         <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G5" t="s">
         <v>5</v>
@@ -1098,7 +991,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -1107,7 +1000,7 @@
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G6" t="s">
         <v>5</v>
@@ -1121,7 +1014,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
@@ -1130,7 +1023,7 @@
         <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G7" t="s">
         <v>5</v>
@@ -1144,7 +1037,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
@@ -1153,7 +1046,7 @@
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G8" t="s">
         <v>5</v>
@@ -1167,7 +1060,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
@@ -1176,7 +1069,7 @@
         <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G9" t="s">
         <v>5</v>
@@ -1190,7 +1083,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D10" t="n">
         <v>9</v>
@@ -1199,7 +1092,7 @@
         <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G10" t="s">
         <v>6</v>
@@ -1207,105 +1100,105 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="n">
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="n">
         <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D12" t="n">
         <v>2</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="n">
         <v>3</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D13" t="n">
         <v>3</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="n">
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D14" t="n">
         <v>4</v>
       </c>
       <c r="E14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="n">
         <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D15" t="n">
         <v>5</v>
@@ -1314,7 +1207,7 @@
         <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G15" t="s">
         <v>6</v>
@@ -1322,13 +1215,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" t="n">
         <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D16" t="n">
         <v>6</v>
@@ -1337,7 +1230,7 @@
         <v>6</v>
       </c>
       <c r="F16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G16" t="s">
         <v>6</v>
@@ -1345,36 +1238,36 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" t="n">
         <v>3</v>
       </c>
       <c r="C17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17" t="n">
         <v>7</v>
       </c>
       <c r="E17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" t="n">
         <v>3</v>
       </c>
       <c r="C18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18" t="n">
         <v>8</v>
@@ -1383,7 +1276,7 @@
         <v>6</v>
       </c>
       <c r="F18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G18" t="s">
         <v>6</v>
@@ -1391,13 +1284,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" t="n">
         <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
@@ -1406,7 +1299,7 @@
         <v>6</v>
       </c>
       <c r="F19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G19" t="s">
         <v>6</v>
@@ -1420,19 +1313,19 @@
         <v>4</v>
       </c>
       <c r="C20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -1443,19 +1336,19 @@
         <v>4</v>
       </c>
       <c r="C21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D21" t="n">
         <v>2</v>
       </c>
       <c r="E21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
@@ -1466,19 +1359,19 @@
         <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D22" t="n">
         <v>3</v>
       </c>
       <c r="E22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
@@ -1489,19 +1382,19 @@
         <v>4</v>
       </c>
       <c r="C23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D23" t="n">
         <v>4</v>
       </c>
       <c r="E23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -1512,7 +1405,7 @@
         <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D24" t="n">
         <v>5</v>
@@ -1521,7 +1414,7 @@
         <v>6</v>
       </c>
       <c r="F24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G24" t="s">
         <v>6</v>
@@ -1535,19 +1428,19 @@
         <v>4</v>
       </c>
       <c r="C25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D25" t="n">
         <v>6</v>
       </c>
       <c r="E25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
@@ -1558,19 +1451,19 @@
         <v>4</v>
       </c>
       <c r="C26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D26" t="n">
         <v>7</v>
       </c>
       <c r="E26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
@@ -1581,7 +1474,7 @@
         <v>4</v>
       </c>
       <c r="C27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D27" t="n">
         <v>8</v>
@@ -1590,7 +1483,7 @@
         <v>6</v>
       </c>
       <c r="F27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G27" t="s">
         <v>6</v>
@@ -1604,7 +1497,7 @@
         <v>4</v>
       </c>
       <c r="C28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D28" t="n">
         <v>9</v>
@@ -1613,7 +1506,7 @@
         <v>6</v>
       </c>
       <c r="F28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G28" t="s">
         <v>6</v>
@@ -1627,19 +1520,19 @@
         <v>5</v>
       </c>
       <c r="C29" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D29" t="n">
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30">
@@ -1650,19 +1543,19 @@
         <v>5</v>
       </c>
       <c r="C30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D30" t="n">
         <v>2</v>
       </c>
       <c r="E30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31">
@@ -1673,19 +1566,19 @@
         <v>5</v>
       </c>
       <c r="C31" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D31" t="n">
         <v>3</v>
       </c>
       <c r="E31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32">
@@ -1696,19 +1589,19 @@
         <v>5</v>
       </c>
       <c r="C32" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D32" t="n">
         <v>4</v>
       </c>
       <c r="E32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F32" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33">
@@ -1719,7 +1612,7 @@
         <v>5</v>
       </c>
       <c r="C33" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D33" t="n">
         <v>5</v>
@@ -1728,7 +1621,7 @@
         <v>6</v>
       </c>
       <c r="F33" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G33" t="s">
         <v>6</v>
@@ -1742,7 +1635,7 @@
         <v>5</v>
       </c>
       <c r="C34" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D34" t="n">
         <v>6</v>
@@ -1751,7 +1644,7 @@
         <v>6</v>
       </c>
       <c r="F34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G34" t="s">
         <v>6</v>
@@ -1765,7 +1658,7 @@
         <v>5</v>
       </c>
       <c r="C35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D35" t="n">
         <v>7</v>
@@ -1774,7 +1667,7 @@
         <v>5</v>
       </c>
       <c r="F35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G35" t="s">
         <v>5</v>
@@ -1788,7 +1681,7 @@
         <v>5</v>
       </c>
       <c r="C36" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D36" t="n">
         <v>8</v>
@@ -1797,7 +1690,7 @@
         <v>6</v>
       </c>
       <c r="F36" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G36" t="s">
         <v>6</v>
@@ -1811,7 +1704,7 @@
         <v>5</v>
       </c>
       <c r="C37" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D37" t="n">
         <v>9</v>
@@ -1820,7 +1713,7 @@
         <v>6</v>
       </c>
       <c r="F37" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G37" t="s">
         <v>6</v>
@@ -1834,7 +1727,7 @@
         <v>6</v>
       </c>
       <c r="C38" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D38" t="n">
         <v>1</v>
@@ -1843,7 +1736,7 @@
         <v>5</v>
       </c>
       <c r="F38" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G38" t="s">
         <v>5</v>
@@ -1857,7 +1750,7 @@
         <v>6</v>
       </c>
       <c r="C39" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D39" t="n">
         <v>2</v>
@@ -1866,7 +1759,7 @@
         <v>5</v>
       </c>
       <c r="F39" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G39" t="s">
         <v>5</v>
@@ -1880,7 +1773,7 @@
         <v>6</v>
       </c>
       <c r="C40" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D40" t="n">
         <v>3</v>
@@ -1889,7 +1782,7 @@
         <v>5</v>
       </c>
       <c r="F40" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G40" t="s">
         <v>5</v>
@@ -1903,7 +1796,7 @@
         <v>6</v>
       </c>
       <c r="C41" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D41" t="n">
         <v>4</v>
@@ -1912,7 +1805,7 @@
         <v>5</v>
       </c>
       <c r="F41" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G41" t="s">
         <v>5</v>
@@ -1926,7 +1819,7 @@
         <v>6</v>
       </c>
       <c r="C42" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D42" t="n">
         <v>5</v>
@@ -1935,7 +1828,7 @@
         <v>5</v>
       </c>
       <c r="F42" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G42" t="s">
         <v>5</v>
@@ -1949,7 +1842,7 @@
         <v>6</v>
       </c>
       <c r="C43" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D43" t="n">
         <v>6</v>
@@ -1958,7 +1851,7 @@
         <v>5</v>
       </c>
       <c r="F43" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G43" t="s">
         <v>5</v>
@@ -1972,7 +1865,7 @@
         <v>6</v>
       </c>
       <c r="C44" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D44" t="n">
         <v>7</v>
@@ -1981,7 +1874,7 @@
         <v>5</v>
       </c>
       <c r="F44" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G44" t="s">
         <v>5</v>
@@ -1995,7 +1888,7 @@
         <v>6</v>
       </c>
       <c r="C45" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D45" t="n">
         <v>8</v>
@@ -2004,7 +1897,7 @@
         <v>5</v>
       </c>
       <c r="F45" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G45" t="s">
         <v>5</v>
@@ -2018,7 +1911,7 @@
         <v>6</v>
       </c>
       <c r="C46" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D46" t="n">
         <v>9</v>
@@ -2027,7 +1920,7 @@
         <v>6</v>
       </c>
       <c r="F46" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G46" t="s">
         <v>6</v>
@@ -2035,105 +1928,105 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B47" t="n">
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D47" t="n">
         <v>1</v>
       </c>
       <c r="E47" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F47" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G47" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B48" t="n">
         <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D48" t="n">
         <v>2</v>
       </c>
       <c r="E48" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F48" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G48" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B49" t="n">
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D49" t="n">
         <v>3</v>
       </c>
       <c r="E49" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F49" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G49" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B50" t="n">
         <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D50" t="n">
         <v>4</v>
       </c>
       <c r="E50" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F50" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G50" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B51" t="n">
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D51" t="n">
         <v>5</v>
@@ -2142,7 +2035,7 @@
         <v>6</v>
       </c>
       <c r="F51" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G51" t="s">
         <v>6</v>
@@ -2150,13 +2043,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B52" t="n">
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D52" t="n">
         <v>6</v>
@@ -2165,7 +2058,7 @@
         <v>6</v>
       </c>
       <c r="F52" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G52" t="s">
         <v>6</v>
@@ -2173,13 +2066,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B53" t="n">
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D53" t="n">
         <v>7</v>
@@ -2188,7 +2081,7 @@
         <v>6</v>
       </c>
       <c r="F53" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G53" t="s">
         <v>6</v>
@@ -2196,13 +2089,13 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B54" t="n">
         <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D54" t="n">
         <v>8</v>
@@ -2211,7 +2104,7 @@
         <v>6</v>
       </c>
       <c r="F54" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G54" t="s">
         <v>6</v>
@@ -2219,13 +2112,13 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B55" t="n">
         <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D55" t="n">
         <v>9</v>
@@ -2234,7 +2127,7 @@
         <v>6</v>
       </c>
       <c r="F55" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G55" t="s">
         <v>6</v>
@@ -2242,13 +2135,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B56" t="n">
         <v>7</v>
       </c>
       <c r="C56" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D56" t="n">
         <v>1</v>
@@ -2257,7 +2150,7 @@
         <v>5</v>
       </c>
       <c r="F56" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G56" t="s">
         <v>5</v>
@@ -2265,13 +2158,13 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B57" t="n">
         <v>7</v>
       </c>
       <c r="C57" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D57" t="n">
         <v>2</v>
@@ -2280,7 +2173,7 @@
         <v>5</v>
       </c>
       <c r="F57" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G57" t="s">
         <v>5</v>
@@ -2288,13 +2181,13 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B58" t="n">
         <v>7</v>
       </c>
       <c r="C58" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D58" t="n">
         <v>3</v>
@@ -2303,7 +2196,7 @@
         <v>5</v>
       </c>
       <c r="F58" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G58" t="s">
         <v>5</v>
@@ -2311,13 +2204,13 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B59" t="n">
         <v>7</v>
       </c>
       <c r="C59" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D59" t="n">
         <v>4</v>
@@ -2326,7 +2219,7 @@
         <v>5</v>
       </c>
       <c r="F59" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G59" t="s">
         <v>5</v>
@@ -2334,13 +2227,13 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B60" t="n">
         <v>7</v>
       </c>
       <c r="C60" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D60" t="n">
         <v>5</v>
@@ -2349,7 +2242,7 @@
         <v>5</v>
       </c>
       <c r="F60" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G60" t="s">
         <v>5</v>
@@ -2357,13 +2250,13 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B61" t="n">
         <v>7</v>
       </c>
       <c r="C61" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D61" t="n">
         <v>6</v>
@@ -2372,7 +2265,7 @@
         <v>5</v>
       </c>
       <c r="F61" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G61" t="s">
         <v>5</v>
@@ -2380,13 +2273,13 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B62" t="n">
         <v>7</v>
       </c>
       <c r="C62" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D62" t="n">
         <v>7</v>
@@ -2395,7 +2288,7 @@
         <v>5</v>
       </c>
       <c r="F62" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G62" t="s">
         <v>5</v>
@@ -2403,13 +2296,13 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B63" t="n">
         <v>7</v>
       </c>
       <c r="C63" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D63" t="n">
         <v>8</v>
@@ -2418,7 +2311,7 @@
         <v>5</v>
       </c>
       <c r="F63" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G63" t="s">
         <v>5</v>
@@ -2426,13 +2319,13 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B64" t="n">
         <v>7</v>
       </c>
       <c r="C64" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D64" t="n">
         <v>9</v>
@@ -2441,7 +2334,7 @@
         <v>5</v>
       </c>
       <c r="F64" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G64" t="s">
         <v>5</v>
@@ -2449,13 +2342,13 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B65" t="n">
         <v>8.2</v>
       </c>
       <c r="C65" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D65" t="n">
         <v>1</v>
@@ -2464,7 +2357,7 @@
         <v>5</v>
       </c>
       <c r="F65" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G65" t="s">
         <v>5</v>
@@ -2472,13 +2365,13 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B66" t="n">
         <v>8.2</v>
       </c>
       <c r="C66" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D66" t="n">
         <v>2</v>
@@ -2487,7 +2380,7 @@
         <v>5</v>
       </c>
       <c r="F66" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G66" t="s">
         <v>5</v>
@@ -2495,13 +2388,13 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B67" t="n">
         <v>8.2</v>
       </c>
       <c r="C67" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D67" t="n">
         <v>3</v>
@@ -2510,7 +2403,7 @@
         <v>5</v>
       </c>
       <c r="F67" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G67" t="s">
         <v>5</v>
@@ -2518,13 +2411,13 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B68" t="n">
         <v>8.2</v>
       </c>
       <c r="C68" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D68" t="n">
         <v>4</v>
@@ -2533,7 +2426,7 @@
         <v>5</v>
       </c>
       <c r="F68" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G68" t="s">
         <v>5</v>
@@ -2541,13 +2434,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B69" t="n">
         <v>8.2</v>
       </c>
       <c r="C69" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D69" t="n">
         <v>5</v>
@@ -2556,7 +2449,7 @@
         <v>5</v>
       </c>
       <c r="F69" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G69" t="s">
         <v>5</v>
@@ -2564,13 +2457,13 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B70" t="n">
         <v>8.2</v>
       </c>
       <c r="C70" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D70" t="n">
         <v>6</v>
@@ -2579,7 +2472,7 @@
         <v>6</v>
       </c>
       <c r="F70" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G70" t="s">
         <v>6</v>
@@ -2587,13 +2480,13 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B71" t="n">
         <v>8.2</v>
       </c>
       <c r="C71" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D71" t="n">
         <v>7</v>
@@ -2602,7 +2495,7 @@
         <v>5</v>
       </c>
       <c r="F71" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G71" t="s">
         <v>5</v>
@@ -2610,13 +2503,13 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B72" t="n">
         <v>8.2</v>
       </c>
       <c r="C72" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D72" t="n">
         <v>8</v>
@@ -2625,7 +2518,7 @@
         <v>6</v>
       </c>
       <c r="F72" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G72" t="s">
         <v>6</v>
@@ -2633,13 +2526,13 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B73" t="n">
         <v>8.2</v>
       </c>
       <c r="C73" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D73" t="n">
         <v>9</v>
@@ -2648,7 +2541,7 @@
         <v>6</v>
       </c>
       <c r="F73" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G73" t="s">
         <v>6</v>
@@ -2715,7 +2608,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
         <v>169.699817591538</v>
@@ -2729,164 +2622,164 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>40.0655660144784</v>
+        <v>191.654561429724</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>151.588995415245</v>
+        <v>123.433050356455</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>123.433050356455</v>
+        <v>35.5613447848116</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" t="n">
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>35.5613447848116</v>
+        <v>202.728745098835</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" t="n">
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>202.728745098835</v>
+        <v>75.0283032288795</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>18</v>
+        <v>80.9761478966684</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>57.0283032288794</v>
+        <v>28.3782590097662</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="n">
         <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>80.9761478966684</v>
+        <v>205.745763807094</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="n">
         <v>3</v>
       </c>
       <c r="C13" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>28.3782590097662</v>
+        <v>70.03391855809</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>205.745763807094</v>
+        <v>66.3469031230314</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>13.8959828324155</v>
+        <v>27.5016333122411</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>56.1379357256746</v>
+        <v>181.560075908497</v>
       </c>
     </row>
     <row r="17">
@@ -2897,276 +2790,178 @@
         <v>4</v>
       </c>
       <c r="C17" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>66.3469031230314</v>
+        <v>67.4717672663374</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>27.5016333122411</v>
+        <v>638.968665995045</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>181.560075908497</v>
+        <v>463.168177197315</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C20" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D20" t="n">
-        <v>22.2289033646727</v>
+        <v>211.095224336815</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D21" t="n">
-        <v>45.2428639016647</v>
+        <v>519.652686835759</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C22" t="s">
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>638.968665995045</v>
+        <v>2446.43752319239</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C23" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="D23" t="n">
-        <v>189.98485059482</v>
+        <v>384.713255981969</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C24" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D24" t="n">
-        <v>463.168177197315</v>
+        <v>505.262578811219</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C25" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>211.095224336815</v>
+        <v>729.342289003483</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C26" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>329.667836240939</v>
+        <v>8580.75685815979</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C27" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>2446.43752319239</v>
+        <v>269.151549583756</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C28" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="D28" t="n">
-        <v>229.986626985974</v>
+        <v>391.243936788619</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C29" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D29" t="n">
-        <v>384.713255981969</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" t="n">
-        <v>6</v>
-      </c>
-      <c r="C30" t="s">
-        <v>38</v>
-      </c>
-      <c r="D30" t="n">
-        <v>505.262578811219</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" t="n">
-        <v>6</v>
-      </c>
-      <c r="C31" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" t="n">
-        <v>499.355662017509</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>17</v>
-      </c>
-      <c r="B32" t="n">
-        <v>7</v>
-      </c>
-      <c r="C32" t="s">
-        <v>5</v>
-      </c>
-      <c r="D32" t="n">
-        <v>8580.75685815979</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>17</v>
-      </c>
-      <c r="B33" t="n">
-        <v>7</v>
-      </c>
-      <c r="C33" t="s">
-        <v>6</v>
-      </c>
-      <c r="D33" t="n">
-        <v>269.151549583756</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>17</v>
-      </c>
-      <c r="B34" t="n">
-        <v>7</v>
-      </c>
-      <c r="C34" t="s">
-        <v>37</v>
-      </c>
-      <c r="D34" t="n">
-        <v>229.268770857761</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>17</v>
-      </c>
-      <c r="B35" t="n">
-        <v>7</v>
-      </c>
-      <c r="C35" t="s">
-        <v>38</v>
-      </c>
-      <c r="D35" t="n">
-        <v>391.243936788619</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>17</v>
-      </c>
-      <c r="B36" t="n">
-        <v>7</v>
-      </c>
-      <c r="C36" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" t="n">
-        <v>400.301604878861</v>
+        <v>629.570375736621</v>
       </c>
     </row>
   </sheetData>
@@ -3188,19 +2983,19 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" t="s">
         <v>18</v>
-      </c>
-      <c r="D1" t="s">
-        <v>19</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
       </c>
       <c r="F1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" t="s">
         <v>20</v>
-      </c>
-      <c r="G1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2">
@@ -3211,7 +3006,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -3220,7 +3015,7 @@
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G2" t="s">
         <v>5</v>
@@ -3234,7 +3029,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -3243,7 +3038,7 @@
         <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G3" t="s">
         <v>5</v>
@@ -3257,7 +3052,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -3266,7 +3061,7 @@
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G4" t="s">
         <v>5</v>
@@ -3280,7 +3075,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -3289,7 +3084,7 @@
         <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G5" t="s">
         <v>5</v>
@@ -3303,7 +3098,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -3312,7 +3107,7 @@
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G6" t="s">
         <v>5</v>
@@ -3326,19 +3121,19 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G7" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -3349,19 +3144,19 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -3372,19 +3167,19 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -3395,7 +3190,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D10" t="n">
         <v>9</v>
@@ -3404,7 +3199,7 @@
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G10" t="s">
         <v>5</v>
@@ -3412,209 +3207,209 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="n">
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="n">
         <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D12" t="n">
         <v>2</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="n">
         <v>3</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D13" t="n">
         <v>3</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="n">
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D14" t="n">
         <v>4</v>
       </c>
       <c r="E14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="n">
         <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D15" t="n">
         <v>5</v>
       </c>
       <c r="E15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" t="n">
         <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D16" t="n">
         <v>6</v>
       </c>
       <c r="E16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" t="n">
         <v>3</v>
       </c>
       <c r="C17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17" t="n">
         <v>7</v>
       </c>
       <c r="E17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" t="n">
         <v>3</v>
       </c>
       <c r="C18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18" t="n">
         <v>8</v>
       </c>
       <c r="E18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" t="n">
         <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
       </c>
       <c r="E19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -3625,19 +3420,19 @@
         <v>4</v>
       </c>
       <c r="C20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -3648,19 +3443,19 @@
         <v>4</v>
       </c>
       <c r="C21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D21" t="n">
         <v>2</v>
       </c>
       <c r="E21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
@@ -3671,19 +3466,19 @@
         <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D22" t="n">
         <v>3</v>
       </c>
       <c r="E22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
@@ -3694,19 +3489,19 @@
         <v>4</v>
       </c>
       <c r="C23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D23" t="n">
         <v>4</v>
       </c>
       <c r="E23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -3717,19 +3512,19 @@
         <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D24" t="n">
         <v>5</v>
       </c>
       <c r="E24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25">
@@ -3740,19 +3535,19 @@
         <v>4</v>
       </c>
       <c r="C25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D25" t="n">
         <v>6</v>
       </c>
       <c r="E25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
@@ -3763,19 +3558,19 @@
         <v>4</v>
       </c>
       <c r="C26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D26" t="n">
         <v>7</v>
       </c>
       <c r="E26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
@@ -3786,19 +3581,19 @@
         <v>4</v>
       </c>
       <c r="C27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D27" t="n">
         <v>8</v>
       </c>
       <c r="E27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28">
@@ -3809,19 +3604,19 @@
         <v>4</v>
       </c>
       <c r="C28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D28" t="n">
         <v>9</v>
       </c>
       <c r="E28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
@@ -3832,7 +3627,7 @@
         <v>5</v>
       </c>
       <c r="C29" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D29" t="n">
         <v>1</v>
@@ -3841,7 +3636,7 @@
         <v>5</v>
       </c>
       <c r="F29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G29" t="s">
         <v>5</v>
@@ -3855,7 +3650,7 @@
         <v>5</v>
       </c>
       <c r="C30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D30" t="n">
         <v>2</v>
@@ -3864,7 +3659,7 @@
         <v>5</v>
       </c>
       <c r="F30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G30" t="s">
         <v>5</v>
@@ -3878,7 +3673,7 @@
         <v>5</v>
       </c>
       <c r="C31" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D31" t="n">
         <v>3</v>
@@ -3887,7 +3682,7 @@
         <v>5</v>
       </c>
       <c r="F31" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G31" t="s">
         <v>5</v>
@@ -3901,7 +3696,7 @@
         <v>5</v>
       </c>
       <c r="C32" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D32" t="n">
         <v>4</v>
@@ -3910,7 +3705,7 @@
         <v>5</v>
       </c>
       <c r="F32" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G32" t="s">
         <v>5</v>
@@ -3924,19 +3719,19 @@
         <v>5</v>
       </c>
       <c r="C33" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D33" t="n">
         <v>5</v>
       </c>
       <c r="E33" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G33" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34">
@@ -3947,19 +3742,19 @@
         <v>5</v>
       </c>
       <c r="C34" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D34" t="n">
         <v>6</v>
       </c>
       <c r="E34" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F34" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G34" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35">
@@ -3970,7 +3765,7 @@
         <v>5</v>
       </c>
       <c r="C35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D35" t="n">
         <v>7</v>
@@ -3979,7 +3774,7 @@
         <v>5</v>
       </c>
       <c r="F35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G35" t="s">
         <v>5</v>
@@ -3993,19 +3788,19 @@
         <v>5</v>
       </c>
       <c r="C36" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D36" t="n">
         <v>8</v>
       </c>
       <c r="E36" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G36" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
@@ -4016,7 +3811,7 @@
         <v>5</v>
       </c>
       <c r="C37" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D37" t="n">
         <v>9</v>
@@ -4025,7 +3820,7 @@
         <v>5</v>
       </c>
       <c r="F37" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G37" t="s">
         <v>5</v>
@@ -4039,7 +3834,7 @@
         <v>6</v>
       </c>
       <c r="C38" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D38" t="n">
         <v>1</v>
@@ -4048,7 +3843,7 @@
         <v>5</v>
       </c>
       <c r="F38" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G38" t="s">
         <v>5</v>
@@ -4062,7 +3857,7 @@
         <v>6</v>
       </c>
       <c r="C39" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D39" t="n">
         <v>2</v>
@@ -4071,7 +3866,7 @@
         <v>5</v>
       </c>
       <c r="F39" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G39" t="s">
         <v>5</v>
@@ -4085,7 +3880,7 @@
         <v>6</v>
       </c>
       <c r="C40" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D40" t="n">
         <v>3</v>
@@ -4094,7 +3889,7 @@
         <v>5</v>
       </c>
       <c r="F40" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G40" t="s">
         <v>5</v>
@@ -4108,7 +3903,7 @@
         <v>6</v>
       </c>
       <c r="C41" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D41" t="n">
         <v>4</v>
@@ -4117,7 +3912,7 @@
         <v>5</v>
       </c>
       <c r="F41" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G41" t="s">
         <v>5</v>
@@ -4131,7 +3926,7 @@
         <v>6</v>
       </c>
       <c r="C42" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D42" t="n">
         <v>5</v>
@@ -4140,7 +3935,7 @@
         <v>5</v>
       </c>
       <c r="F42" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G42" t="s">
         <v>5</v>
@@ -4154,7 +3949,7 @@
         <v>6</v>
       </c>
       <c r="C43" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D43" t="n">
         <v>6</v>
@@ -4163,7 +3958,7 @@
         <v>5</v>
       </c>
       <c r="F43" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G43" t="s">
         <v>5</v>
@@ -4177,7 +3972,7 @@
         <v>6</v>
       </c>
       <c r="C44" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D44" t="n">
         <v>7</v>
@@ -4186,7 +3981,7 @@
         <v>5</v>
       </c>
       <c r="F44" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G44" t="s">
         <v>5</v>
@@ -4200,7 +3995,7 @@
         <v>6</v>
       </c>
       <c r="C45" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D45" t="n">
         <v>8</v>
@@ -4209,7 +4004,7 @@
         <v>5</v>
       </c>
       <c r="F45" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G45" t="s">
         <v>5</v>
@@ -4223,7 +4018,7 @@
         <v>6</v>
       </c>
       <c r="C46" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D46" t="n">
         <v>9</v>
@@ -4232,7 +4027,7 @@
         <v>5</v>
       </c>
       <c r="F46" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G46" t="s">
         <v>5</v>
@@ -4240,13 +4035,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B47" t="n">
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D47" t="n">
         <v>1</v>
@@ -4255,7 +4050,7 @@
         <v>5</v>
       </c>
       <c r="F47" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G47" t="s">
         <v>5</v>
@@ -4263,197 +4058,197 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B48" t="n">
         <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D48" t="n">
         <v>2</v>
       </c>
       <c r="E48" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F48" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G48" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B49" t="n">
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D49" t="n">
         <v>3</v>
       </c>
       <c r="E49" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F49" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G49" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B50" t="n">
         <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D50" t="n">
         <v>4</v>
       </c>
       <c r="E50" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F50" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G50" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B51" t="n">
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D51" t="n">
         <v>5</v>
       </c>
       <c r="E51" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F51" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G51" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B52" t="n">
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D52" t="n">
         <v>6</v>
       </c>
       <c r="E52" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F52" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G52" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B53" t="n">
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D53" t="n">
         <v>7</v>
       </c>
       <c r="E53" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F53" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G53" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B54" t="n">
         <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D54" t="n">
         <v>8</v>
       </c>
       <c r="E54" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F54" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G54" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B55" t="n">
         <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D55" t="n">
         <v>9</v>
       </c>
       <c r="E55" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F55" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G55" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B56" t="n">
         <v>7</v>
       </c>
       <c r="C56" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D56" t="n">
         <v>1</v>
@@ -4462,7 +4257,7 @@
         <v>5</v>
       </c>
       <c r="F56" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G56" t="s">
         <v>5</v>
@@ -4470,13 +4265,13 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B57" t="n">
         <v>7</v>
       </c>
       <c r="C57" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D57" t="n">
         <v>2</v>
@@ -4485,7 +4280,7 @@
         <v>5</v>
       </c>
       <c r="F57" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G57" t="s">
         <v>5</v>
@@ -4493,13 +4288,13 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B58" t="n">
         <v>7</v>
       </c>
       <c r="C58" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D58" t="n">
         <v>3</v>
@@ -4508,7 +4303,7 @@
         <v>5</v>
       </c>
       <c r="F58" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G58" t="s">
         <v>5</v>
@@ -4516,13 +4311,13 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B59" t="n">
         <v>7</v>
       </c>
       <c r="C59" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D59" t="n">
         <v>4</v>
@@ -4531,7 +4326,7 @@
         <v>5</v>
       </c>
       <c r="F59" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G59" t="s">
         <v>5</v>
@@ -4539,13 +4334,13 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B60" t="n">
         <v>7</v>
       </c>
       <c r="C60" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D60" t="n">
         <v>5</v>
@@ -4554,7 +4349,7 @@
         <v>5</v>
       </c>
       <c r="F60" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G60" t="s">
         <v>5</v>
@@ -4562,13 +4357,13 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B61" t="n">
         <v>7</v>
       </c>
       <c r="C61" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D61" t="n">
         <v>6</v>
@@ -4577,7 +4372,7 @@
         <v>5</v>
       </c>
       <c r="F61" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G61" t="s">
         <v>5</v>
@@ -4585,13 +4380,13 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B62" t="n">
         <v>7</v>
       </c>
       <c r="C62" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D62" t="n">
         <v>7</v>
@@ -4600,7 +4395,7 @@
         <v>5</v>
       </c>
       <c r="F62" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G62" t="s">
         <v>5</v>
@@ -4608,13 +4403,13 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B63" t="n">
         <v>7</v>
       </c>
       <c r="C63" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D63" t="n">
         <v>8</v>
@@ -4623,7 +4418,7 @@
         <v>5</v>
       </c>
       <c r="F63" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G63" t="s">
         <v>5</v>
@@ -4631,13 +4426,13 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B64" t="n">
         <v>7</v>
       </c>
       <c r="C64" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D64" t="n">
         <v>9</v>
@@ -4646,7 +4441,7 @@
         <v>5</v>
       </c>
       <c r="F64" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G64" t="s">
         <v>5</v>
@@ -4654,13 +4449,13 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B65" t="n">
         <v>8.2</v>
       </c>
       <c r="C65" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D65" t="n">
         <v>1</v>
@@ -4669,7 +4464,7 @@
         <v>5</v>
       </c>
       <c r="F65" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G65" t="s">
         <v>5</v>
@@ -4677,13 +4472,13 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B66" t="n">
         <v>8.2</v>
       </c>
       <c r="C66" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D66" t="n">
         <v>2</v>
@@ -4692,7 +4487,7 @@
         <v>5</v>
       </c>
       <c r="F66" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G66" t="s">
         <v>5</v>
@@ -4700,13 +4495,13 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B67" t="n">
         <v>8.2</v>
       </c>
       <c r="C67" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D67" t="n">
         <v>3</v>
@@ -4715,7 +4510,7 @@
         <v>5</v>
       </c>
       <c r="F67" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G67" t="s">
         <v>5</v>
@@ -4723,13 +4518,13 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B68" t="n">
         <v>8.2</v>
       </c>
       <c r="C68" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D68" t="n">
         <v>4</v>
@@ -4738,7 +4533,7 @@
         <v>5</v>
       </c>
       <c r="F68" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G68" t="s">
         <v>5</v>
@@ -4746,13 +4541,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B69" t="n">
         <v>8.2</v>
       </c>
       <c r="C69" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D69" t="n">
         <v>5</v>
@@ -4761,7 +4556,7 @@
         <v>5</v>
       </c>
       <c r="F69" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G69" t="s">
         <v>5</v>
@@ -4769,13 +4564,13 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B70" t="n">
         <v>8.2</v>
       </c>
       <c r="C70" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D70" t="n">
         <v>6</v>
@@ -4784,7 +4579,7 @@
         <v>5</v>
       </c>
       <c r="F70" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G70" t="s">
         <v>5</v>
@@ -4792,13 +4587,13 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B71" t="n">
         <v>8.2</v>
       </c>
       <c r="C71" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D71" t="n">
         <v>7</v>
@@ -4807,7 +4602,7 @@
         <v>5</v>
       </c>
       <c r="F71" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G71" t="s">
         <v>5</v>
@@ -4815,13 +4610,13 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B72" t="n">
         <v>8.2</v>
       </c>
       <c r="C72" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D72" t="n">
         <v>8</v>
@@ -4830,7 +4625,7 @@
         <v>5</v>
       </c>
       <c r="F72" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G72" t="s">
         <v>5</v>
@@ -4838,13 +4633,13 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B73" t="n">
         <v>8.2</v>
       </c>
       <c r="C73" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D73" t="n">
         <v>9</v>
@@ -4853,7 +4648,7 @@
         <v>5</v>
       </c>
       <c r="F73" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G73" t="s">
         <v>5</v>

--- a/Outcome/Publish/figure_data/fig3.xlsx
+++ b/Outcome/Publish/figure_data/fig3.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="92">
   <si>
     <t xml:space="preserve">Group</t>
   </si>
@@ -207,6 +207,9 @@
     <t xml:space="preserve">StartDate</t>
   </si>
   <si>
+    <t xml:space="preserve">Status</t>
+  </si>
+  <si>
     <t xml:space="preserve">type</t>
   </si>
   <si>
@@ -216,94 +219,107 @@
     <t xml:space="preserve">Period</t>
   </si>
   <si>
+    <t xml:space="preserve">Debt Repaid</t>
+  </si>
+  <si>
     <t xml:space="preserve">Recovery</t>
   </si>
   <si>
-    <t xml:space="preserve">34 months</t>
+    <t xml:space="preserve">34m</t>
   </si>
   <si>
     <t xml:space="preserve">Balance</t>
   </si>
   <si>
-    <t xml:space="preserve">61 months</t>
+    <t xml:space="preserve">61m</t>
   </si>
   <si>
-    <t xml:space="preserve">43 months</t>
+    <t xml:space="preserve">Recovered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43m</t>
   </si>
   <si>
     <t xml:space="preserve">Not balanced</t>
   </si>
   <si>
+    <t xml:space="preserve">Suppressed</t>
+  </si>
+  <si>
     <t xml:space="preserve">Not recovered</t>
   </si>
   <si>
-    <t xml:space="preserve">56 months</t>
+    <t xml:space="preserve">58m</t>
   </si>
   <si>
-    <t xml:space="preserve">35 months</t>
+    <t xml:space="preserve">35m</t>
   </si>
   <si>
-    <t xml:space="preserve">27 months</t>
+    <t xml:space="preserve">No Deficit</t>
   </si>
   <si>
-    <t xml:space="preserve">32 months</t>
+    <t xml:space="preserve">No deficit</t>
   </si>
   <si>
-    <t xml:space="preserve">33 months</t>
+    <t xml:space="preserve">27m</t>
   </si>
   <si>
-    <t xml:space="preserve">7 months</t>
+    <t xml:space="preserve">32m</t>
   </si>
   <si>
-    <t xml:space="preserve">41 months</t>
+    <t xml:space="preserve">28m</t>
   </si>
   <si>
-    <t xml:space="preserve">4 months</t>
+    <t xml:space="preserve">33m</t>
   </si>
   <si>
-    <t xml:space="preserve">6 months</t>
+    <t xml:space="preserve">41m</t>
   </si>
   <si>
-    <t xml:space="preserve">9 months</t>
+    <t xml:space="preserve">5m</t>
   </si>
   <si>
-    <t xml:space="preserve">29 months</t>
+    <t xml:space="preserve">6m</t>
   </si>
   <si>
-    <t xml:space="preserve">36 months</t>
+    <t xml:space="preserve">9m</t>
   </si>
   <si>
-    <t xml:space="preserve">30 months</t>
+    <t xml:space="preserve">29m</t>
   </si>
   <si>
-    <t xml:space="preserve">54 months</t>
+    <t xml:space="preserve">36m</t>
   </si>
   <si>
-    <t xml:space="preserve">0 months</t>
+    <t xml:space="preserve">31m</t>
   </si>
   <si>
-    <t xml:space="preserve">52 months</t>
+    <t xml:space="preserve">30m</t>
   </si>
   <si>
-    <t xml:space="preserve">40 months</t>
+    <t xml:space="preserve">54m</t>
   </si>
   <si>
-    <t xml:space="preserve">51 months</t>
+    <t xml:space="preserve">46m</t>
   </si>
   <si>
-    <t xml:space="preserve">44 months</t>
+    <t xml:space="preserve">52m</t>
   </si>
   <si>
-    <t xml:space="preserve">28 months</t>
+    <t xml:space="preserve">56m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48m</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -340,7 +356,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -47615,6 +47631,9 @@
       <c r="E1" t="s">
         <v>58</v>
       </c>
+      <c r="F1" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
@@ -47624,13 +47643,16 @@
         <v>43831</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D2" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" s="1" t="n">
         <v>44866</v>
       </c>
-      <c r="E2" t="s">
-        <v>60</v>
+      <c r="F2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="3">
@@ -47641,13 +47663,16 @@
         <v>43831</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D3" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" s="1" t="n">
         <v>45689</v>
       </c>
-      <c r="E3" t="s">
-        <v>62</v>
+      <c r="F3" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="4">
@@ -47658,13 +47683,16 @@
         <v>43831</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D4" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="D4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" s="1" t="n">
         <v>45139</v>
       </c>
-      <c r="E4" t="s">
-        <v>63</v>
+      <c r="F4" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="5">
@@ -47675,13 +47703,16 @@
         <v>43831</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D5" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="D5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="E5" t="s">
-        <v>64</v>
+      <c r="F5" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="6">
@@ -47692,13 +47723,16 @@
         <v>43831</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D6" s="1" t="n">
+        <v>68</v>
+      </c>
+      <c r="D6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="E6" t="s">
-        <v>65</v>
+      <c r="F6" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="7">
@@ -47709,13 +47743,16 @@
         <v>43831</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" s="1" t="n">
+        <v>68</v>
+      </c>
+      <c r="D7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E7" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="E7" t="s">
-        <v>64</v>
+      <c r="F7" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="8">
@@ -47726,13 +47763,16 @@
         <v>43831</v>
       </c>
       <c r="C8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45536</v>
-      </c>
-      <c r="E8" t="s">
-        <v>66</v>
+        <v>65</v>
+      </c>
+      <c r="D8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>45597</v>
+      </c>
+      <c r="F8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="9">
@@ -47743,13 +47783,16 @@
         <v>43831</v>
       </c>
       <c r="C9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D9" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="D9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E9" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="E9" t="s">
-        <v>64</v>
+      <c r="F9" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="10">
@@ -47760,13 +47803,16 @@
         <v>43831</v>
       </c>
       <c r="C10" t="s">
-        <v>59</v>
-      </c>
-      <c r="D10" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="D10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="1" t="n">
         <v>45689</v>
       </c>
-      <c r="E10" t="s">
-        <v>62</v>
+      <c r="F10" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="11">
@@ -47777,13 +47823,16 @@
         <v>43831</v>
       </c>
       <c r="C11" t="s">
-        <v>61</v>
-      </c>
-      <c r="D11" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="D11" t="s">
+        <v>63</v>
+      </c>
+      <c r="E11" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="E11" t="s">
-        <v>64</v>
+      <c r="F11" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="12">
@@ -47794,13 +47843,16 @@
         <v>43831</v>
       </c>
       <c r="C12" t="s">
-        <v>59</v>
-      </c>
-      <c r="D12" s="1" t="n">
+        <v>68</v>
+      </c>
+      <c r="D12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="E12" t="s">
-        <v>65</v>
+      <c r="F12" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -47811,13 +47863,16 @@
         <v>43831</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
-      </c>
-      <c r="D13" s="1" t="n">
+        <v>68</v>
+      </c>
+      <c r="D13" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="E13" t="s">
-        <v>64</v>
+      <c r="F13" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="14">
@@ -47828,13 +47883,16 @@
         <v>43831</v>
       </c>
       <c r="C14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D14" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="D14" t="s">
+        <v>61</v>
+      </c>
+      <c r="E14" s="1" t="n">
         <v>44896</v>
       </c>
-      <c r="E14" t="s">
-        <v>67</v>
+      <c r="F14" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="15">
@@ -47845,13 +47903,16 @@
         <v>43831</v>
       </c>
       <c r="C15" t="s">
-        <v>61</v>
-      </c>
-      <c r="D15" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="D15" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="E15" t="s">
-        <v>64</v>
+      <c r="F15" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="16">
@@ -47862,13 +47923,16 @@
         <v>43831</v>
       </c>
       <c r="C16" t="s">
-        <v>59</v>
-      </c>
-      <c r="D16" s="1" t="n">
+        <v>72</v>
+      </c>
+      <c r="D16" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="E16" t="s">
-        <v>65</v>
+      <c r="F16" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="17">
@@ -47879,13 +47943,16 @@
         <v>43831</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
-      </c>
-      <c r="D17" s="1" t="n">
+        <v>72</v>
+      </c>
+      <c r="D17" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="E17" t="s">
-        <v>64</v>
+      <c r="F17" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -47896,13 +47963,16 @@
         <v>43831</v>
       </c>
       <c r="C18" t="s">
-        <v>59</v>
-      </c>
-      <c r="D18" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E18" s="1" t="n">
         <v>44652</v>
       </c>
-      <c r="E18" t="s">
-        <v>68</v>
+      <c r="F18" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="19">
@@ -47913,13 +47983,16 @@
         <v>43831</v>
       </c>
       <c r="C19" t="s">
-        <v>61</v>
-      </c>
-      <c r="D19" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D19" t="s">
+        <v>63</v>
+      </c>
+      <c r="E19" s="1" t="n">
         <v>44805</v>
       </c>
-      <c r="E19" t="s">
-        <v>69</v>
+      <c r="F19" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="20">
@@ -47930,13 +48003,16 @@
         <v>43831</v>
       </c>
       <c r="C20" t="s">
-        <v>59</v>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>44652</v>
-      </c>
-      <c r="E20" t="s">
-        <v>68</v>
+        <v>60</v>
+      </c>
+      <c r="D20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>44682</v>
+      </c>
+      <c r="F20" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="21">
@@ -47947,13 +48023,16 @@
         <v>43831</v>
       </c>
       <c r="C21" t="s">
-        <v>61</v>
-      </c>
-      <c r="D21" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D21" t="s">
+        <v>63</v>
+      </c>
+      <c r="E21" s="1" t="n">
         <v>44835</v>
       </c>
-      <c r="E21" t="s">
-        <v>70</v>
+      <c r="F21" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="22">
@@ -47964,13 +48043,16 @@
         <v>43831</v>
       </c>
       <c r="C22" t="s">
-        <v>59</v>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>44044</v>
-      </c>
-      <c r="E22" t="s">
-        <v>71</v>
+        <v>60</v>
+      </c>
+      <c r="D22" t="s">
+        <v>61</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>44682</v>
+      </c>
+      <c r="F22" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="23">
@@ -47981,13 +48063,16 @@
         <v>43831</v>
       </c>
       <c r="C23" t="s">
-        <v>61</v>
-      </c>
-      <c r="D23" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D23" t="s">
+        <v>63</v>
+      </c>
+      <c r="E23" s="1" t="n">
         <v>45078</v>
       </c>
-      <c r="E23" t="s">
-        <v>72</v>
+      <c r="F23" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="24">
@@ -47998,13 +48083,16 @@
         <v>43831</v>
       </c>
       <c r="C24" t="s">
-        <v>59</v>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>43952</v>
-      </c>
-      <c r="E24" t="s">
-        <v>73</v>
+        <v>60</v>
+      </c>
+      <c r="D24" t="s">
+        <v>61</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>43983</v>
+      </c>
+      <c r="F24" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="25">
@@ -48015,13 +48103,16 @@
         <v>43831</v>
       </c>
       <c r="C25" t="s">
-        <v>61</v>
-      </c>
-      <c r="D25" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D25" t="s">
+        <v>63</v>
+      </c>
+      <c r="E25" s="1" t="n">
         <v>44013</v>
       </c>
-      <c r="E25" t="s">
-        <v>74</v>
+      <c r="F25" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="26">
@@ -48032,13 +48123,16 @@
         <v>43831</v>
       </c>
       <c r="C26" t="s">
-        <v>59</v>
-      </c>
-      <c r="D26" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D26" t="s">
+        <v>61</v>
+      </c>
+      <c r="E26" s="1" t="n">
         <v>44105</v>
       </c>
-      <c r="E26" t="s">
-        <v>75</v>
+      <c r="F26" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="27">
@@ -48049,13 +48143,16 @@
         <v>43831</v>
       </c>
       <c r="C27" t="s">
-        <v>61</v>
-      </c>
-      <c r="D27" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D27" t="s">
+        <v>63</v>
+      </c>
+      <c r="E27" s="1" t="n">
         <v>44805</v>
       </c>
-      <c r="E27" t="s">
-        <v>69</v>
+      <c r="F27" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="28">
@@ -48066,13 +48163,16 @@
         <v>43831</v>
       </c>
       <c r="C28" t="s">
-        <v>59</v>
-      </c>
-      <c r="D28" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D28" t="s">
+        <v>61</v>
+      </c>
+      <c r="E28" s="1" t="n">
         <v>44713</v>
       </c>
-      <c r="E28" t="s">
-        <v>76</v>
+      <c r="F28" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="29">
@@ -48083,13 +48183,16 @@
         <v>43831</v>
       </c>
       <c r="C29" t="s">
-        <v>61</v>
-      </c>
-      <c r="D29" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D29" t="s">
+        <v>63</v>
+      </c>
+      <c r="E29" s="1" t="n">
         <v>44927</v>
       </c>
-      <c r="E29" t="s">
-        <v>77</v>
+      <c r="F29" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="30">
@@ -48100,13 +48203,16 @@
         <v>43831</v>
       </c>
       <c r="C30" t="s">
-        <v>59</v>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>44713</v>
-      </c>
-      <c r="E30" t="s">
-        <v>76</v>
+        <v>65</v>
+      </c>
+      <c r="D30" t="s">
+        <v>61</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>44774</v>
+      </c>
+      <c r="F30" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="31">
@@ -48117,13 +48223,16 @@
         <v>43831</v>
       </c>
       <c r="C31" t="s">
-        <v>61</v>
-      </c>
-      <c r="D31" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="D31" t="s">
+        <v>63</v>
+      </c>
+      <c r="E31" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="E31" t="s">
-        <v>64</v>
+      <c r="F31" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="32">
@@ -48134,13 +48243,16 @@
         <v>43831</v>
       </c>
       <c r="C32" t="s">
-        <v>59</v>
-      </c>
-      <c r="D32" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D32" t="s">
+        <v>61</v>
+      </c>
+      <c r="E32" s="1" t="n">
         <v>44743</v>
       </c>
-      <c r="E32" t="s">
-        <v>78</v>
+      <c r="F32" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="33">
@@ -48151,13 +48263,16 @@
         <v>43831</v>
       </c>
       <c r="C33" t="s">
-        <v>61</v>
-      </c>
-      <c r="D33" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D33" t="s">
+        <v>63</v>
+      </c>
+      <c r="E33" s="1" t="n">
         <v>45474</v>
       </c>
-      <c r="E33" t="s">
-        <v>79</v>
+      <c r="F33" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="34">
@@ -48168,13 +48283,16 @@
         <v>43831</v>
       </c>
       <c r="C34" t="s">
-        <v>59</v>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>43831</v>
-      </c>
-      <c r="E34" t="s">
-        <v>80</v>
+        <v>65</v>
+      </c>
+      <c r="D34" t="s">
+        <v>61</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>45231</v>
+      </c>
+      <c r="F34" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="35">
@@ -48185,13 +48303,16 @@
         <v>43831</v>
       </c>
       <c r="C35" t="s">
-        <v>61</v>
-      </c>
-      <c r="D35" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="D35" t="s">
+        <v>63</v>
+      </c>
+      <c r="E35" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="E35" t="s">
-        <v>64</v>
+      <c r="F35" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="36">
@@ -48202,13 +48323,16 @@
         <v>43831</v>
       </c>
       <c r="C36" t="s">
-        <v>59</v>
-      </c>
-      <c r="D36" s="1" t="n">
-        <v>44866</v>
-      </c>
-      <c r="E36" t="s">
         <v>60</v>
+      </c>
+      <c r="D36" t="s">
+        <v>61</v>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="F36" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="37">
@@ -48219,13 +48343,16 @@
         <v>43831</v>
       </c>
       <c r="C37" t="s">
-        <v>61</v>
-      </c>
-      <c r="D37" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D37" t="s">
+        <v>63</v>
+      </c>
+      <c r="E37" s="1" t="n">
         <v>45689</v>
       </c>
-      <c r="E37" t="s">
-        <v>62</v>
+      <c r="F37" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="38">
@@ -48236,13 +48363,16 @@
         <v>43831</v>
       </c>
       <c r="C38" t="s">
-        <v>59</v>
-      </c>
-      <c r="D38" s="1" t="n">
+        <v>68</v>
+      </c>
+      <c r="D38" t="s">
+        <v>61</v>
+      </c>
+      <c r="E38" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="E38" t="s">
-        <v>65</v>
+      <c r="F38" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="39">
@@ -48253,13 +48383,16 @@
         <v>43831</v>
       </c>
       <c r="C39" t="s">
-        <v>61</v>
-      </c>
-      <c r="D39" s="1" t="n">
+        <v>68</v>
+      </c>
+      <c r="D39" t="s">
+        <v>63</v>
+      </c>
+      <c r="E39" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="E39" t="s">
-        <v>64</v>
+      <c r="F39" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="40">
@@ -48270,13 +48403,16 @@
         <v>43831</v>
       </c>
       <c r="C40" t="s">
-        <v>59</v>
-      </c>
-      <c r="D40" s="1" t="n">
-        <v>44927</v>
-      </c>
-      <c r="E40" t="s">
-        <v>77</v>
+        <v>60</v>
+      </c>
+      <c r="D40" t="s">
+        <v>61</v>
+      </c>
+      <c r="E40" s="1" t="n">
+        <v>45078</v>
+      </c>
+      <c r="F40" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="41">
@@ -48287,13 +48423,16 @@
         <v>43831</v>
       </c>
       <c r="C41" t="s">
-        <v>61</v>
-      </c>
-      <c r="D41" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D41" t="s">
+        <v>63</v>
+      </c>
+      <c r="E41" s="1" t="n">
         <v>45413</v>
       </c>
-      <c r="E41" t="s">
-        <v>81</v>
+      <c r="F41" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="42">
@@ -48304,13 +48443,16 @@
         <v>43831</v>
       </c>
       <c r="C42" t="s">
-        <v>59</v>
-      </c>
-      <c r="D42" s="1" t="n">
-        <v>45047</v>
-      </c>
-      <c r="E42" t="s">
-        <v>82</v>
+        <v>60</v>
+      </c>
+      <c r="D42" t="s">
+        <v>61</v>
+      </c>
+      <c r="E42" s="1" t="n">
+        <v>45139</v>
+      </c>
+      <c r="F42" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="43">
@@ -48321,13 +48463,16 @@
         <v>43831</v>
       </c>
       <c r="C43" t="s">
-        <v>61</v>
-      </c>
-      <c r="D43" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D43" t="s">
+        <v>63</v>
+      </c>
+      <c r="E43" s="1" t="n">
         <v>45536</v>
       </c>
-      <c r="E43" t="s">
-        <v>66</v>
+      <c r="F43" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="44">
@@ -48338,13 +48483,16 @@
         <v>43831</v>
       </c>
       <c r="C44" t="s">
-        <v>59</v>
-      </c>
-      <c r="D44" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D44" t="s">
+        <v>61</v>
+      </c>
+      <c r="E44" s="1" t="n">
         <v>44927</v>
       </c>
-      <c r="E44" t="s">
-        <v>77</v>
+      <c r="F44" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="45">
@@ -48355,13 +48503,16 @@
         <v>43831</v>
       </c>
       <c r="C45" t="s">
-        <v>61</v>
-      </c>
-      <c r="D45" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D45" t="s">
+        <v>63</v>
+      </c>
+      <c r="E45" s="1" t="n">
         <v>45383</v>
       </c>
-      <c r="E45" t="s">
-        <v>83</v>
+      <c r="F45" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="46">
@@ -48372,13 +48523,16 @@
         <v>43831</v>
       </c>
       <c r="C46" t="s">
-        <v>59</v>
-      </c>
-      <c r="D46" s="1" t="n">
-        <v>45170</v>
-      </c>
-      <c r="E46" t="s">
-        <v>84</v>
+        <v>65</v>
+      </c>
+      <c r="D46" t="s">
+        <v>61</v>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="F46" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="47">
@@ -48389,13 +48543,16 @@
         <v>43831</v>
       </c>
       <c r="C47" t="s">
-        <v>61</v>
-      </c>
-      <c r="D47" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="D47" t="s">
+        <v>63</v>
+      </c>
+      <c r="E47" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="E47" t="s">
-        <v>64</v>
+      <c r="F47" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="48">
@@ -48406,13 +48563,16 @@
         <v>43831</v>
       </c>
       <c r="C48" t="s">
-        <v>59</v>
-      </c>
-      <c r="D48" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D48" t="s">
+        <v>61</v>
+      </c>
+      <c r="E48" s="1" t="n">
         <v>44682</v>
       </c>
-      <c r="E48" t="s">
-        <v>85</v>
+      <c r="F48" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="49">
@@ -48423,13 +48583,16 @@
         <v>43831</v>
       </c>
       <c r="C49" t="s">
-        <v>61</v>
-      </c>
-      <c r="D49" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D49" t="s">
+        <v>63</v>
+      </c>
+      <c r="E49" s="1" t="n">
         <v>44866</v>
       </c>
-      <c r="E49" t="s">
-        <v>60</v>
+      <c r="F49" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/Outcome/Publish/figure_data/fig3.xlsx
+++ b/Outcome/Publish/figure_data/fig3.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
   <si>
     <t xml:space="preserve">Group</t>
   </si>
@@ -225,19 +225,19 @@
     <t xml:space="preserve">Recovery</t>
   </si>
   <si>
-    <t xml:space="preserve">34m</t>
+    <t xml:space="preserve">31m</t>
   </si>
   <si>
     <t xml:space="preserve">Balance</t>
   </si>
   <si>
-    <t xml:space="preserve">61m</t>
+    <t xml:space="preserve">58m</t>
   </si>
   <si>
     <t xml:space="preserve">Recovered</t>
   </si>
   <si>
-    <t xml:space="preserve">43m</t>
+    <t xml:space="preserve">41m</t>
   </si>
   <si>
     <t xml:space="preserve">Not balanced</t>
@@ -249,10 +249,10 @@
     <t xml:space="preserve">Not recovered</t>
   </si>
   <si>
-    <t xml:space="preserve">58m</t>
+    <t xml:space="preserve">61m</t>
   </si>
   <si>
-    <t xml:space="preserve">35m</t>
+    <t xml:space="preserve">34m</t>
   </si>
   <si>
     <t xml:space="preserve">No Deficit</t>
@@ -261,37 +261,40 @@
     <t xml:space="preserve">No deficit</t>
   </si>
   <si>
+    <t xml:space="preserve">22m</t>
+  </si>
+  <si>
     <t xml:space="preserve">27m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9m</t>
   </si>
   <si>
     <t xml:space="preserve">32m</t>
   </si>
   <si>
-    <t xml:space="preserve">28m</t>
+    <t xml:space="preserve">11m</t>
   </si>
   <si>
-    <t xml:space="preserve">33m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9m</t>
+    <t xml:space="preserve">18m</t>
   </si>
   <si>
     <t xml:space="preserve">29m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31m</t>
   </si>
   <si>
     <t xml:space="preserve">30m</t>
@@ -303,16 +306,19 @@
     <t xml:space="preserve">46m</t>
   </si>
   <si>
-    <t xml:space="preserve">52m</t>
+    <t xml:space="preserve">36m</t>
   </si>
   <si>
-    <t xml:space="preserve">56m</t>
+    <t xml:space="preserve">39m</t>
   </si>
   <si>
-    <t xml:space="preserve">51m</t>
+    <t xml:space="preserve">50m</t>
   </si>
   <si>
-    <t xml:space="preserve">48m</t>
+    <t xml:space="preserve">35m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28m</t>
   </si>
 </sst>
 </file>
@@ -47640,7 +47646,7 @@
         <v>42</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>43831</v>
+        <v>43922</v>
       </c>
       <c r="C2" t="s">
         <v>60</v>
@@ -47660,7 +47666,7 @@
         <v>42</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>43831</v>
+        <v>43922</v>
       </c>
       <c r="C3" t="s">
         <v>60</v>
@@ -47680,7 +47686,7 @@
         <v>41</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>43831</v>
+        <v>43891</v>
       </c>
       <c r="C4" t="s">
         <v>65</v>
@@ -47700,7 +47706,7 @@
         <v>41</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>43831</v>
+        <v>43891</v>
       </c>
       <c r="C5" t="s">
         <v>65</v>
@@ -47720,7 +47726,7 @@
         <v>40</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>43831</v>
+        <v>43862</v>
       </c>
       <c r="C6" t="s">
         <v>68</v>
@@ -47740,7 +47746,7 @@
         <v>40</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>43831</v>
+        <v>43862</v>
       </c>
       <c r="C7" t="s">
         <v>68</v>
@@ -47772,7 +47778,7 @@
         <v>45597</v>
       </c>
       <c r="F8" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9">
@@ -47812,7 +47818,7 @@
         <v>45689</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11">
@@ -47880,7 +47886,7 @@
         <v>35</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>43831</v>
+        <v>43862</v>
       </c>
       <c r="C14" t="s">
         <v>65</v>
@@ -47900,7 +47906,7 @@
         <v>35</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>43831</v>
+        <v>43862</v>
       </c>
       <c r="C15" t="s">
         <v>65</v>
@@ -47960,7 +47966,7 @@
         <v>33</v>
       </c>
       <c r="B18" s="1" t="n">
-        <v>43831</v>
+        <v>43983</v>
       </c>
       <c r="C18" t="s">
         <v>60</v>
@@ -47980,7 +47986,7 @@
         <v>33</v>
       </c>
       <c r="B19" s="1" t="n">
-        <v>43831</v>
+        <v>43983</v>
       </c>
       <c r="C19" t="s">
         <v>60</v>
@@ -48000,7 +48006,7 @@
         <v>32</v>
       </c>
       <c r="B20" s="1" t="n">
-        <v>43831</v>
+        <v>43891</v>
       </c>
       <c r="C20" t="s">
         <v>60</v>
@@ -48020,7 +48026,7 @@
         <v>32</v>
       </c>
       <c r="B21" s="1" t="n">
-        <v>43831</v>
+        <v>43891</v>
       </c>
       <c r="C21" t="s">
         <v>60</v>
@@ -48032,7 +48038,7 @@
         <v>44835</v>
       </c>
       <c r="F21" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22">
@@ -48040,7 +48046,7 @@
         <v>31</v>
       </c>
       <c r="B22" s="1" t="n">
-        <v>43831</v>
+        <v>43922</v>
       </c>
       <c r="C22" t="s">
         <v>60</v>
@@ -48052,7 +48058,7 @@
         <v>44682</v>
       </c>
       <c r="F22" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23">
@@ -48060,7 +48066,7 @@
         <v>31</v>
       </c>
       <c r="B23" s="1" t="n">
-        <v>43831</v>
+        <v>43922</v>
       </c>
       <c r="C23" t="s">
         <v>60</v>
@@ -48080,7 +48086,7 @@
         <v>30</v>
       </c>
       <c r="B24" s="1" t="n">
-        <v>43831</v>
+        <v>43862</v>
       </c>
       <c r="C24" t="s">
         <v>60</v>
@@ -48100,7 +48106,7 @@
         <v>30</v>
       </c>
       <c r="B25" s="1" t="n">
-        <v>43831</v>
+        <v>43862</v>
       </c>
       <c r="C25" t="s">
         <v>60</v>
@@ -48152,7 +48158,7 @@
         <v>44805</v>
       </c>
       <c r="F27" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28">
@@ -48160,7 +48166,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="n">
-        <v>43831</v>
+        <v>44378</v>
       </c>
       <c r="C28" t="s">
         <v>60</v>
@@ -48172,7 +48178,7 @@
         <v>44713</v>
       </c>
       <c r="F28" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29">
@@ -48180,7 +48186,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="1" t="n">
-        <v>43831</v>
+        <v>44378</v>
       </c>
       <c r="C29" t="s">
         <v>60</v>
@@ -48192,7 +48198,7 @@
         <v>44927</v>
       </c>
       <c r="F29" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30">
@@ -48200,7 +48206,7 @@
         <v>26</v>
       </c>
       <c r="B30" s="1" t="n">
-        <v>43831</v>
+        <v>43891</v>
       </c>
       <c r="C30" t="s">
         <v>65</v>
@@ -48212,7 +48218,7 @@
         <v>44774</v>
       </c>
       <c r="F30" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31">
@@ -48220,7 +48226,7 @@
         <v>26</v>
       </c>
       <c r="B31" s="1" t="n">
-        <v>43831</v>
+        <v>43891</v>
       </c>
       <c r="C31" t="s">
         <v>65</v>
@@ -48252,7 +48258,7 @@
         <v>44743</v>
       </c>
       <c r="F32" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33">
@@ -48272,7 +48278,7 @@
         <v>45474</v>
       </c>
       <c r="F33" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34">
@@ -48292,7 +48298,7 @@
         <v>45231</v>
       </c>
       <c r="F34" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35">
@@ -48332,7 +48338,7 @@
         <v>44927</v>
       </c>
       <c r="F36" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37">
@@ -48352,7 +48358,7 @@
         <v>45689</v>
       </c>
       <c r="F37" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="38">
@@ -48360,7 +48366,7 @@
         <v>21</v>
       </c>
       <c r="B38" s="1" t="n">
-        <v>43831</v>
+        <v>43952</v>
       </c>
       <c r="C38" t="s">
         <v>68</v>
@@ -48380,7 +48386,7 @@
         <v>21</v>
       </c>
       <c r="B39" s="1" t="n">
-        <v>43831</v>
+        <v>43952</v>
       </c>
       <c r="C39" t="s">
         <v>68</v>
@@ -48400,7 +48406,7 @@
         <v>20</v>
       </c>
       <c r="B40" s="1" t="n">
-        <v>43831</v>
+        <v>43891</v>
       </c>
       <c r="C40" t="s">
         <v>60</v>
@@ -48412,7 +48418,7 @@
         <v>45078</v>
       </c>
       <c r="F40" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
     </row>
     <row r="41">
@@ -48420,7 +48426,7 @@
         <v>20</v>
       </c>
       <c r="B41" s="1" t="n">
-        <v>43831</v>
+        <v>43891</v>
       </c>
       <c r="C41" t="s">
         <v>60</v>
@@ -48432,7 +48438,7 @@
         <v>45413</v>
       </c>
       <c r="F41" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="42">
@@ -48440,7 +48446,7 @@
         <v>19</v>
       </c>
       <c r="B42" s="1" t="n">
-        <v>43831</v>
+        <v>43891</v>
       </c>
       <c r="C42" t="s">
         <v>60</v>
@@ -48460,7 +48466,7 @@
         <v>19</v>
       </c>
       <c r="B43" s="1" t="n">
-        <v>43831</v>
+        <v>43891</v>
       </c>
       <c r="C43" t="s">
         <v>60</v>
@@ -48472,7 +48478,7 @@
         <v>45536</v>
       </c>
       <c r="F43" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="44">
@@ -48480,7 +48486,7 @@
         <v>18</v>
       </c>
       <c r="B44" s="1" t="n">
-        <v>43831</v>
+        <v>43862</v>
       </c>
       <c r="C44" t="s">
         <v>60</v>
@@ -48492,7 +48498,7 @@
         <v>44927</v>
       </c>
       <c r="F44" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
     </row>
     <row r="45">
@@ -48500,7 +48506,7 @@
         <v>18</v>
       </c>
       <c r="B45" s="1" t="n">
-        <v>43831</v>
+        <v>43862</v>
       </c>
       <c r="C45" t="s">
         <v>60</v>
@@ -48512,7 +48518,7 @@
         <v>45383</v>
       </c>
       <c r="F45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="46">
@@ -48520,7 +48526,7 @@
         <v>17</v>
       </c>
       <c r="B46" s="1" t="n">
-        <v>43831</v>
+        <v>43891</v>
       </c>
       <c r="C46" t="s">
         <v>65</v>
@@ -48532,7 +48538,7 @@
         <v>45292</v>
       </c>
       <c r="F46" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="47">
@@ -48540,7 +48546,7 @@
         <v>17</v>
       </c>
       <c r="B47" s="1" t="n">
-        <v>43831</v>
+        <v>43891</v>
       </c>
       <c r="C47" t="s">
         <v>65</v>
@@ -48572,7 +48578,7 @@
         <v>44682</v>
       </c>
       <c r="F48" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
     </row>
     <row r="49">
@@ -48592,7 +48598,7 @@
         <v>44866</v>
       </c>
       <c r="F49" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
